--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>57166289</v>
       </c>
       <c r="B2" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105594</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>350682.9782685409</v>
+        <v>350683</v>
       </c>
       <c r="R2" t="n">
-        <v>6532586.251828447</v>
+        <v>6532586</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1974-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1974-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>57166289</v>
       </c>
       <c r="B2" t="n">
-        <v>105594</v>
+        <v>105606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>57166289</v>
       </c>
       <c r="B2" t="n">
-        <v>105606</v>
+        <v>105615</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>57166289</v>
       </c>
       <c r="B2" t="n">
-        <v>105615</v>
+        <v>105627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>57166289</v>
       </c>
       <c r="B2" t="n">
-        <v>105627</v>
+        <v>105636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>57166289</v>
       </c>
       <c r="B2" t="n">
-        <v>105636</v>
+        <v>105639</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>57166289</v>
       </c>
       <c r="B2" t="n">
-        <v>105639</v>
+        <v>105667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -773,6 +773,1265 @@
           <t>Flora över Dal 1981</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128831484</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100807</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>350642</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6532386</v>
+      </c>
+      <c r="S3" t="n">
+        <v>8</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128837146</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92818</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>350556</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6532301</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Växer här relativt allmänt i äldre barrskog.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128836713</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92802</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>350682</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6532579</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar (minst 25 st) med tydlig kumarin/anisdoft som växer i avlångt stråk/häxring i äldre granskog med stor dimensionspridning hos stammarna.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128829084</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100807</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Källan, Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>350656</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6532655</v>
+      </c>
+      <c r="S6" t="n">
+        <v>11</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128830471</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100807</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Källan, Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>350669</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6532592</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128831345</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58086</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>350684</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6532442</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Minst 2 individer, kanske fler.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128837030</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92818</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>350674</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6532611</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växer här relativt allmänt i äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128830810</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>350667</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6532520</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 2 talltitor (ev. flera individer) hördes med lockläten i flerskiktad äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128831251</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100807</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>350678</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6532445</v>
+      </c>
+      <c r="S11" t="n">
+        <v>8</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128832520</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100807</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>350537</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6532319</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128832131</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100807</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>350583</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6532348</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,36 +883,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128837146</v>
+        <v>128836713</v>
       </c>
       <c r="B4" t="n">
-        <v>92818</v>
+        <v>92802</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -925,13 +933,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>350556</v>
+        <v>350682</v>
       </c>
       <c r="R4" t="n">
-        <v>6532301</v>
+        <v>6532579</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Växer här relativt allmänt i äldre barrskog.</t>
+          <t>Gott om fruktkroppar (minst 25 st) med tydlig kumarin/anisdoft som växer i avlångt stråk/häxring i äldre granskog med stor dimensionspridning hos stammarna.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,7 +988,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -998,44 +1006,36 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128836713</v>
+        <v>128837146</v>
       </c>
       <c r="B5" t="n">
-        <v>92802</v>
+        <v>92818</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>350682</v>
+        <v>350556</v>
       </c>
       <c r="R5" t="n">
-        <v>6532579</v>
+        <v>6532301</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar (minst 25 st) med tydlig kumarin/anisdoft som växer i avlångt stråk/häxring i äldre granskog med stor dimensionspridning hos stammarna.</t>
+          <t>Växer här relativt allmänt i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -2033,6 +2033,945 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128864268</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92818</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>350703</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6532526</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128864568</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100807</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>350581</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6532373</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128864191</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92818</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>350673</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6532521</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128864631</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92429</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>350556</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6532301</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128864345</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92429</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>350592</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6532382</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128864417</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92818</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>350581</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6532373</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128863610</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92818</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>350664</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6532520</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128863382</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92429</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>350686</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6532651</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>57166289</v>
       </c>
       <c r="B2" t="n">
-        <v>105667</v>
+        <v>105673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128831484</v>
       </c>
       <c r="B3" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128836713</v>
       </c>
       <c r="B4" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>128837146</v>
       </c>
       <c r="B5" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>128829084</v>
       </c>
       <c r="B6" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>128830471</v>
       </c>
       <c r="B7" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128837030</v>
       </c>
       <c r="B9" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>128831251</v>
       </c>
       <c r="B11" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>128832520</v>
       </c>
       <c r="B12" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>128832131</v>
       </c>
       <c r="B13" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>128864268</v>
       </c>
       <c r="B14" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128864568</v>
       </c>
       <c r="B15" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,10 +2264,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128864191</v>
+        <v>128864417</v>
       </c>
       <c r="B16" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2314,13 +2314,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>350673</v>
+        <v>350581</v>
       </c>
       <c r="R16" t="n">
-        <v>6532521</v>
+        <v>6532373</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2350,11 +2350,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,10 +2382,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128864631</v>
+        <v>128864191</v>
       </c>
       <c r="B17" t="n">
-        <v>92429</v>
+        <v>92823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2398,26 +2393,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2437,13 +2432,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>350556</v>
+        <v>350673</v>
       </c>
       <c r="R17" t="n">
-        <v>6532301</v>
+        <v>6532521</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2473,6 +2468,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,10 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128864345</v>
+        <v>128864631</v>
       </c>
       <c r="B18" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>350592</v>
+        <v>350556</v>
       </c>
       <c r="R18" t="n">
-        <v>6532382</v>
+        <v>6532301</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128864417</v>
+        <v>128864345</v>
       </c>
       <c r="B19" t="n">
-        <v>92818</v>
+        <v>92434</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>350581</v>
+        <v>350592</v>
       </c>
       <c r="R19" t="n">
-        <v>6532373</v>
+        <v>6532382</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
         <v>128863610</v>
       </c>
       <c r="B20" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>128863382</v>
       </c>
       <c r="B21" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2971,6 +2971,2886 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128876148</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>350624</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6532525</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128878422</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Källan, Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>350651</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6532577</v>
+      </c>
+      <c r="S23" t="n">
+        <v>11</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar i häxring på ca 10 meter.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128876650</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>350619</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6532546</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128877974</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92434</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>350602</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6532394</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128874644</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Källan, Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>350638</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6532616</v>
+      </c>
+      <c r="S26" t="n">
+        <v>12</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128878114</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>350572</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6532383</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Växer delvis ihalv hägring.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128878002</v>
+      </c>
+      <c r="B28" t="n">
+        <v>100813</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>350594</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6532414</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128875354</v>
+      </c>
+      <c r="B29" t="n">
+        <v>100813</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>350609</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6532560</v>
+      </c>
+      <c r="S29" t="n">
+        <v>11</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128877739</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>350592</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6532454</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128877592</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>350717</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6532577</v>
+      </c>
+      <c r="S31" t="n">
+        <v>11</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128877600</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>350701</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6532566</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128877139</v>
+      </c>
+      <c r="B33" t="n">
+        <v>110752</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>350754</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6532572</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128876850</v>
+      </c>
+      <c r="B34" t="n">
+        <v>100813</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>350652</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6532542</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128877309</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>350752</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6532559</v>
+      </c>
+      <c r="S35" t="n">
+        <v>11</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128877462</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>350726</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6532586</v>
+      </c>
+      <c r="S36" t="n">
+        <v>11</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128877664</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>350697</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6532548</v>
+      </c>
+      <c r="S37" t="n">
+        <v>14</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128873652</v>
+      </c>
+      <c r="B38" t="n">
+        <v>100813</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Källan, Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>350627</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6532599</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128875600</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>350590</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6532525</v>
+      </c>
+      <c r="S39" t="n">
+        <v>9</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128876017</v>
+      </c>
+      <c r="B40" t="n">
+        <v>110752</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>350614</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6532523</v>
+      </c>
+      <c r="S40" t="n">
+        <v>9</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i äldre granskog där även andra kalkgynnade arter växer.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128877867</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>350590</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6532384</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Minst 2 talltitor, kanske fler, i flerskiktad äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128875778</v>
+      </c>
+      <c r="B42" t="n">
+        <v>100813</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>350613</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6532522</v>
+      </c>
+      <c r="S42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Växer allmänt i skogsbeståndet där fyndplatsen ligger.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128878172</v>
+      </c>
+      <c r="B43" t="n">
+        <v>110752</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>350562</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6532383</v>
+      </c>
+      <c r="S43" t="n">
+        <v>16</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Växer relativt rikligt på fyndplatsen.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128876585</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92801</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>350632</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6532513</v>
+      </c>
+      <c r="S44" t="n">
+        <v>11</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128876816</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>350632</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6532521</v>
+      </c>
+      <c r="S45" t="n">
+        <v>11</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128877087</v>
+      </c>
+      <c r="B46" t="n">
+        <v>100813</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Långkasen, Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>350761</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6532577</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>57166289</v>
       </c>
       <c r="B2" t="n">
-        <v>105673</v>
+        <v>105680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128831484</v>
       </c>
       <c r="B3" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128836713</v>
       </c>
       <c r="B4" t="n">
-        <v>92807</v>
+        <v>92812</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>128837146</v>
       </c>
       <c r="B5" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>128829084</v>
       </c>
       <c r="B6" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>128830471</v>
       </c>
       <c r="B7" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128837030</v>
       </c>
       <c r="B9" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>128831251</v>
       </c>
       <c r="B11" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>128832520</v>
       </c>
       <c r="B12" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>128832131</v>
       </c>
       <c r="B13" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>128864268</v>
       </c>
       <c r="B14" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128864568</v>
       </c>
       <c r="B15" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,10 +2264,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128864417</v>
+        <v>128864345</v>
       </c>
       <c r="B16" t="n">
-        <v>92823</v>
+        <v>92439</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>350581</v>
+        <v>350592</v>
       </c>
       <c r="R16" t="n">
-        <v>6532373</v>
+        <v>6532382</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2385,7 +2385,7 @@
         <v>128864191</v>
       </c>
       <c r="B17" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128864631</v>
+        <v>128864417</v>
       </c>
       <c r="B18" t="n">
-        <v>92434</v>
+        <v>92830</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,21 +2516,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>350556</v>
+        <v>350581</v>
       </c>
       <c r="R18" t="n">
-        <v>6532301</v>
+        <v>6532373</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128864345</v>
+        <v>128863610</v>
       </c>
       <c r="B19" t="n">
-        <v>92434</v>
+        <v>92830</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,33 +2634,25 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -2673,10 +2665,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>350592</v>
+        <v>350664</v>
       </c>
       <c r="R19" t="n">
-        <v>6532382</v>
+        <v>6532520</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2709,6 +2701,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2741,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128863610</v>
+        <v>128863382</v>
       </c>
       <c r="B20" t="n">
-        <v>92823</v>
+        <v>92439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,25 +2749,33 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -2779,17 +2784,17 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>350664</v>
+        <v>350686</v>
       </c>
       <c r="R20" t="n">
-        <v>6532520</v>
+        <v>6532651</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2819,11 +2824,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2856,10 +2856,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128863382</v>
+        <v>128876148</v>
       </c>
       <c r="B21" t="n">
-        <v>92434</v>
+        <v>92830</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2867,26 +2867,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2899,20 +2899,19 @@
           <t>teleomorf</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>350686</v>
+        <v>350624</v>
       </c>
       <c r="R21" t="n">
-        <v>6532651</v>
+        <v>6532525</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2936,12 +2935,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2950,7 +2949,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2974,10 +2972,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128876148</v>
+        <v>128878422</v>
       </c>
       <c r="B22" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3004,7 +3002,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3019,17 +3017,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långkasen, Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>350624</v>
+        <v>350651</v>
       </c>
       <c r="R22" t="n">
-        <v>6532525</v>
+        <v>6532577</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3061,6 +3059,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar i häxring på ca 10 meter.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3072,7 +3075,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3090,10 +3093,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128878422</v>
+        <v>128876650</v>
       </c>
       <c r="B23" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3118,16 +3121,7 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -3135,17 +3129,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>350651</v>
+        <v>350619</v>
       </c>
       <c r="R23" t="n">
-        <v>6532577</v>
+        <v>6532546</v>
       </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3177,11 +3171,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar i häxring på ca 10 meter.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3193,7 +3182,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3211,10 +3200,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128876650</v>
+        <v>128878114</v>
       </c>
       <c r="B24" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3239,7 +3228,16 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -3251,10 +3249,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>350619</v>
+        <v>350572</v>
       </c>
       <c r="R24" t="n">
-        <v>6532546</v>
+        <v>6532383</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3289,6 +3287,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växer delvis ihalv hägring.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3300,7 +3303,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3318,10 +3321,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128877974</v>
+        <v>128874644</v>
       </c>
       <c r="B25" t="n">
-        <v>92434</v>
+        <v>92830</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3329,33 +3332,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -3363,17 +3357,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långkasen, Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>350602</v>
+        <v>350638</v>
       </c>
       <c r="R25" t="n">
-        <v>6532394</v>
+        <v>6532616</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3416,7 +3410,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3434,10 +3428,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128874644</v>
+        <v>128878002</v>
       </c>
       <c r="B26" t="n">
-        <v>92823</v>
+        <v>100820</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3445,42 +3439,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>350638</v>
+        <v>350594</v>
       </c>
       <c r="R26" t="n">
-        <v>6532616</v>
+        <v>6532414</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3523,7 +3517,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3541,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128878114</v>
+        <v>128875354</v>
       </c>
       <c r="B27" t="n">
-        <v>92823</v>
+        <v>100820</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3552,36 +3546,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3590,13 +3575,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>350572</v>
+        <v>350609</v>
       </c>
       <c r="R27" t="n">
-        <v>6532383</v>
+        <v>6532560</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3626,11 +3611,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Växer delvis ihalv hägring.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3662,38 +3642,47 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128878002</v>
+        <v>128877739</v>
       </c>
       <c r="B28" t="n">
-        <v>100813</v>
+        <v>57876</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3702,13 +3691,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>350594</v>
+        <v>350592</v>
       </c>
       <c r="R28" t="n">
-        <v>6532414</v>
+        <v>6532454</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3735,11 +3724,26 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3751,7 +3755,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3769,10 +3773,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128875354</v>
+        <v>128877592</v>
       </c>
       <c r="B29" t="n">
-        <v>100813</v>
+        <v>92830</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3780,27 +3784,36 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3809,10 +3822,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>350609</v>
+        <v>350717</v>
       </c>
       <c r="R29" t="n">
-        <v>6532560</v>
+        <v>6532577</v>
       </c>
       <c r="S29" t="n">
         <v>11</v>
@@ -3845,6 +3858,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3876,47 +3894,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128877739</v>
+        <v>128877600</v>
       </c>
       <c r="B30" t="n">
-        <v>57876</v>
+        <v>92830</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3925,13 +3938,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>350592</v>
+        <v>350701</v>
       </c>
       <c r="R30" t="n">
-        <v>6532454</v>
+        <v>6532566</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3958,24 +3971,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4007,10 +4005,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128877592</v>
+        <v>128877139</v>
       </c>
       <c r="B31" t="n">
-        <v>92823</v>
+        <v>110759</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4018,36 +4016,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5964</v>
+        <v>219711</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4056,13 +4045,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>350717</v>
+        <v>350754</v>
       </c>
       <c r="R31" t="n">
-        <v>6532577</v>
+        <v>6532572</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4094,11 +4083,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4110,7 +4094,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4128,10 +4112,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128877600</v>
+        <v>128876850</v>
       </c>
       <c r="B32" t="n">
-        <v>92823</v>
+        <v>100820</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4139,31 +4123,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4172,13 +4152,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>350701</v>
+        <v>350652</v>
       </c>
       <c r="R32" t="n">
-        <v>6532566</v>
+        <v>6532542</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4210,6 +4190,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4221,7 +4206,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4239,10 +4224,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128877139</v>
+        <v>128877309</v>
       </c>
       <c r="B33" t="n">
-        <v>110752</v>
+        <v>92830</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4250,27 +4235,36 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219711</v>
+        <v>5964</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4279,13 +4273,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>350754</v>
+        <v>350752</v>
       </c>
       <c r="R33" t="n">
-        <v>6532572</v>
+        <v>6532559</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4346,10 +4340,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128876850</v>
+        <v>128877462</v>
       </c>
       <c r="B34" t="n">
-        <v>100813</v>
+        <v>92830</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4357,27 +4351,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4386,13 +4380,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>350652</v>
+        <v>350726</v>
       </c>
       <c r="R34" t="n">
-        <v>6532542</v>
+        <v>6532586</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4424,11 +4418,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4440,7 +4429,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4458,10 +4447,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128877309</v>
+        <v>128877664</v>
       </c>
       <c r="B35" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4488,7 +4477,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4507,13 +4496,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>350752</v>
+        <v>350697</v>
       </c>
       <c r="R35" t="n">
-        <v>6532559</v>
+        <v>6532548</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4556,7 +4545,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4574,10 +4563,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128877462</v>
+        <v>128873652</v>
       </c>
       <c r="B36" t="n">
-        <v>92823</v>
+        <v>100820</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4585,42 +4574,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långkasen, Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>350726</v>
+        <v>350627</v>
       </c>
       <c r="R36" t="n">
-        <v>6532586</v>
+        <v>6532599</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4681,10 +4670,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128877664</v>
+        <v>128875600</v>
       </c>
       <c r="B37" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4711,7 +4700,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4730,13 +4719,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>350697</v>
+        <v>350590</v>
       </c>
       <c r="R37" t="n">
-        <v>6532548</v>
+        <v>6532525</v>
       </c>
       <c r="S37" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4797,10 +4786,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128873652</v>
+        <v>128876017</v>
       </c>
       <c r="B38" t="n">
-        <v>100813</v>
+        <v>110759</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4808,42 +4797,51 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>350627</v>
+        <v>350614</v>
       </c>
       <c r="R38" t="n">
-        <v>6532599</v>
+        <v>6532523</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4875,6 +4873,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i äldre granskog där även andra kalkgynnade arter växer.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4886,7 +4889,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4904,47 +4907,47 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128875600</v>
+        <v>128877867</v>
       </c>
       <c r="B39" t="n">
-        <v>92823</v>
+        <v>57876</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4956,10 +4959,10 @@
         <v>350590</v>
       </c>
       <c r="R39" t="n">
-        <v>6532525</v>
+        <v>6532384</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4986,11 +4989,26 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Minst 2 talltitor, kanske fler, i flerskiktad äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5002,7 +5020,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5020,10 +5038,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128876017</v>
+        <v>128875778</v>
       </c>
       <c r="B40" t="n">
-        <v>110752</v>
+        <v>100820</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5031,36 +5049,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5069,13 +5078,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>350614</v>
+        <v>350613</v>
       </c>
       <c r="R40" t="n">
-        <v>6532523</v>
+        <v>6532522</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5109,7 +5118,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i äldre granskog där även andra kalkgynnade arter växer.</t>
+          <t>Växer allmänt i skogsbeståndet där fyndplatsen ligger.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5141,42 +5150,47 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128877867</v>
+        <v>128878172</v>
       </c>
       <c r="B41" t="n">
-        <v>57876</v>
+        <v>110759</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>219711</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5190,13 +5204,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>350590</v>
+        <v>350562</v>
       </c>
       <c r="R41" t="n">
-        <v>6532384</v>
+        <v>6532383</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5223,24 +5237,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Minst 2 talltitor, kanske fler, i flerskiktad äldre granskog.</t>
+          <t>Växer relativt rikligt på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5254,7 +5258,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5272,10 +5276,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128875778</v>
+        <v>128876585</v>
       </c>
       <c r="B42" t="n">
-        <v>100813</v>
+        <v>92806</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,27 +5287,36 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>4366</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5312,13 +5325,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>350613</v>
+        <v>350632</v>
       </c>
       <c r="R42" t="n">
-        <v>6532522</v>
+        <v>6532513</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5352,7 +5365,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Växer allmänt i skogsbeståndet där fyndplatsen ligger.</t>
+          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5384,10 +5397,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128878172</v>
+        <v>128876816</v>
       </c>
       <c r="B43" t="n">
-        <v>110752</v>
+        <v>92830</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,41 +5408,36 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219711</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5438,13 +5446,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>350562</v>
+        <v>350632</v>
       </c>
       <c r="R43" t="n">
-        <v>6532383</v>
+        <v>6532521</v>
       </c>
       <c r="S43" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5476,11 +5484,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Växer relativt rikligt på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5492,7 +5495,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5510,10 +5513,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128876585</v>
+        <v>128877087</v>
       </c>
       <c r="B44" t="n">
-        <v>92801</v>
+        <v>100820</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5521,36 +5524,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4366</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5559,13 +5553,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>350632</v>
+        <v>350761</v>
       </c>
       <c r="R44" t="n">
-        <v>6532513</v>
+        <v>6532577</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5595,11 +5589,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5631,10 +5620,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128876816</v>
+        <v>128877974</v>
       </c>
       <c r="B45" t="n">
-        <v>92823</v>
+        <v>92439</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5642,26 +5631,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5680,13 +5669,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>350632</v>
+        <v>350602</v>
       </c>
       <c r="R45" t="n">
-        <v>6532521</v>
+        <v>6532394</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5747,10 +5736,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128877087</v>
+        <v>128864631</v>
       </c>
       <c r="B46" t="n">
-        <v>100813</v>
+        <v>92439</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5758,39 +5747,49 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Långkasen, Långkasen, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>350761</v>
+        <v>350556</v>
       </c>
       <c r="R46" t="n">
-        <v>6532577</v>
+        <v>6532301</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5817,12 +5816,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5831,6 +5830,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5851,6 +5851,129 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128898374</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91277</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>350636</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6532606</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Fyndplatsen ligger vid kanten av ett stråk med sumpskog och i samma skogsområde finns ett flertal andra arter som signalerar kalkhaltig mark.</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -2264,10 +2264,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128864345</v>
+        <v>128864417</v>
       </c>
       <c r="B16" t="n">
-        <v>92439</v>
+        <v>92830</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>350592</v>
+        <v>350581</v>
       </c>
       <c r="R16" t="n">
-        <v>6532382</v>
+        <v>6532373</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128864417</v>
+        <v>128864345</v>
       </c>
       <c r="B18" t="n">
-        <v>92830</v>
+        <v>92439</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,21 +2516,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>350581</v>
+        <v>350592</v>
       </c>
       <c r="R18" t="n">
-        <v>6532373</v>
+        <v>6532382</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3200,10 +3200,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128878114</v>
+        <v>128878002</v>
       </c>
       <c r="B24" t="n">
-        <v>92830</v>
+        <v>100820</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,36 +3211,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3249,10 +3240,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>350572</v>
+        <v>350594</v>
       </c>
       <c r="R24" t="n">
-        <v>6532383</v>
+        <v>6532414</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3287,11 +3278,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Växer delvis ihalv hägring.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3303,7 +3289,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3321,10 +3307,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128874644</v>
+        <v>128875354</v>
       </c>
       <c r="B25" t="n">
-        <v>92830</v>
+        <v>100820</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3332,42 +3318,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>350638</v>
+        <v>350609</v>
       </c>
       <c r="R25" t="n">
-        <v>6532616</v>
+        <v>6532560</v>
       </c>
       <c r="S25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3428,10 +3414,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128878002</v>
+        <v>128878114</v>
       </c>
       <c r="B26" t="n">
-        <v>100820</v>
+        <v>92830</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3439,27 +3425,36 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3468,10 +3463,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>350594</v>
+        <v>350572</v>
       </c>
       <c r="R26" t="n">
-        <v>6532414</v>
+        <v>6532383</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3506,6 +3501,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Växer delvis ihalv hägring.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128875354</v>
+        <v>128874644</v>
       </c>
       <c r="B27" t="n">
-        <v>100820</v>
+        <v>92830</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3546,42 +3546,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långkasen, Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>350609</v>
+        <v>350638</v>
       </c>
       <c r="R27" t="n">
-        <v>6532560</v>
+        <v>6532616</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128877592</v>
+        <v>128877600</v>
       </c>
       <c r="B29" t="n">
         <v>92830</v>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3811,24 +3811,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>350717</v>
+        <v>350701</v>
       </c>
       <c r="R29" t="n">
-        <v>6532577</v>
+        <v>6532566</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3858,11 +3853,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3894,7 +3884,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128877600</v>
+        <v>128877592</v>
       </c>
       <c r="B30" t="n">
         <v>92830</v>
@@ -3924,7 +3914,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3932,19 +3922,24 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>350701</v>
+        <v>350717</v>
       </c>
       <c r="R30" t="n">
-        <v>6532566</v>
+        <v>6532577</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3974,6 +3969,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4340,7 +4340,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128877462</v>
+        <v>128877664</v>
       </c>
       <c r="B34" t="n">
         <v>92830</v>
@@ -4368,7 +4368,16 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -4380,13 +4389,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>350726</v>
+        <v>350697</v>
       </c>
       <c r="R34" t="n">
-        <v>6532586</v>
+        <v>6532548</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4447,7 +4456,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128877664</v>
+        <v>128877462</v>
       </c>
       <c r="B35" t="n">
         <v>92830</v>
@@ -4475,16 +4484,7 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>350697</v>
+        <v>350726</v>
       </c>
       <c r="R35" t="n">
-        <v>6532548</v>
+        <v>6532586</v>
       </c>
       <c r="S35" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -2264,10 +2264,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128864417</v>
+        <v>128864345</v>
       </c>
       <c r="B16" t="n">
-        <v>92830</v>
+        <v>92439</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>350581</v>
+        <v>350592</v>
       </c>
       <c r="R16" t="n">
-        <v>6532373</v>
+        <v>6532382</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128864345</v>
+        <v>128864417</v>
       </c>
       <c r="B18" t="n">
-        <v>92439</v>
+        <v>92830</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,21 +2516,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>350592</v>
+        <v>350581</v>
       </c>
       <c r="R18" t="n">
-        <v>6532382</v>
+        <v>6532373</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3200,10 +3200,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128878002</v>
+        <v>128878114</v>
       </c>
       <c r="B24" t="n">
-        <v>100820</v>
+        <v>92830</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,27 +3211,36 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3240,10 +3249,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>350594</v>
+        <v>350572</v>
       </c>
       <c r="R24" t="n">
-        <v>6532414</v>
+        <v>6532383</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3278,6 +3287,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växer delvis ihalv hägring.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3289,7 +3303,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3307,10 +3321,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128875354</v>
+        <v>128874644</v>
       </c>
       <c r="B25" t="n">
-        <v>100820</v>
+        <v>92830</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3318,42 +3332,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långkasen, Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>350609</v>
+        <v>350638</v>
       </c>
       <c r="R25" t="n">
-        <v>6532560</v>
+        <v>6532616</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3414,10 +3428,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128878114</v>
+        <v>128878002</v>
       </c>
       <c r="B26" t="n">
-        <v>92830</v>
+        <v>100820</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,36 +3439,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3463,10 +3468,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>350572</v>
+        <v>350594</v>
       </c>
       <c r="R26" t="n">
-        <v>6532383</v>
+        <v>6532414</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3501,11 +3506,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Växer delvis ihalv hägring.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128874644</v>
+        <v>128875354</v>
       </c>
       <c r="B27" t="n">
-        <v>92830</v>
+        <v>100820</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3546,42 +3546,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>350638</v>
+        <v>350609</v>
       </c>
       <c r="R27" t="n">
-        <v>6532616</v>
+        <v>6532560</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128877600</v>
+        <v>128877139</v>
       </c>
       <c r="B29" t="n">
-        <v>92830</v>
+        <v>110759</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,31 +3784,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5964</v>
+        <v>219711</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3817,13 +3813,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>350701</v>
+        <v>350754</v>
       </c>
       <c r="R29" t="n">
-        <v>6532566</v>
+        <v>6532572</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3866,7 +3862,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4005,10 +4001,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128877139</v>
+        <v>128877600</v>
       </c>
       <c r="B31" t="n">
-        <v>110759</v>
+        <v>92830</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4016,27 +4012,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219711</v>
+        <v>5964</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4045,13 +4045,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>350754</v>
+        <v>350701</v>
       </c>
       <c r="R31" t="n">
-        <v>6532572</v>
+        <v>6532566</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4340,7 +4340,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128877664</v>
+        <v>128877462</v>
       </c>
       <c r="B34" t="n">
         <v>92830</v>
@@ -4368,16 +4368,7 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -4389,13 +4380,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>350697</v>
+        <v>350726</v>
       </c>
       <c r="R34" t="n">
-        <v>6532548</v>
+        <v>6532586</v>
       </c>
       <c r="S34" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4456,7 +4447,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128877462</v>
+        <v>128877664</v>
       </c>
       <c r="B35" t="n">
         <v>92830</v>
@@ -4484,7 +4475,16 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>350726</v>
+        <v>350697</v>
       </c>
       <c r="R35" t="n">
-        <v>6532586</v>
+        <v>6532548</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>57166289</v>
       </c>
       <c r="B2" t="n">
-        <v>105680</v>
+        <v>105684</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128831484</v>
       </c>
       <c r="B3" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128836713</v>
       </c>
       <c r="B4" t="n">
-        <v>92812</v>
+        <v>92816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>128837146</v>
       </c>
       <c r="B5" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>128829084</v>
       </c>
       <c r="B6" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>128830471</v>
       </c>
       <c r="B7" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128831345</v>
       </c>
       <c r="B8" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128837030</v>
       </c>
       <c r="B9" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>128830810</v>
       </c>
       <c r="B10" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>128831251</v>
       </c>
       <c r="B11" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>128832520</v>
       </c>
       <c r="B12" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>128832131</v>
       </c>
       <c r="B13" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>128864268</v>
       </c>
       <c r="B14" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128864568</v>
       </c>
       <c r="B15" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>128864345</v>
       </c>
       <c r="B16" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>128864191</v>
       </c>
       <c r="B17" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>128864417</v>
       </c>
       <c r="B18" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>128863610</v>
       </c>
       <c r="B19" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>128863382</v>
       </c>
       <c r="B20" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>128876148</v>
       </c>
       <c r="B21" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>128878422</v>
       </c>
       <c r="B22" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>128876650</v>
       </c>
       <c r="B23" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>128878114</v>
       </c>
       <c r="B24" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>128874644</v>
       </c>
       <c r="B25" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>128878002</v>
       </c>
       <c r="B26" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>128875354</v>
       </c>
       <c r="B27" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>128877739</v>
       </c>
       <c r="B28" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128877139</v>
+        <v>128877592</v>
       </c>
       <c r="B29" t="n">
-        <v>110759</v>
+        <v>92834</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,27 +3784,36 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219711</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3813,13 +3822,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>350754</v>
+        <v>350717</v>
       </c>
       <c r="R29" t="n">
-        <v>6532572</v>
+        <v>6532577</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3851,6 +3860,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3862,7 +3876,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3880,10 +3894,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128877592</v>
+        <v>128877600</v>
       </c>
       <c r="B30" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3910,7 +3924,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3918,24 +3932,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>350717</v>
+        <v>350701</v>
       </c>
       <c r="R30" t="n">
-        <v>6532577</v>
+        <v>6532566</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3965,11 +3974,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4001,10 +4005,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128877600</v>
+        <v>128877139</v>
       </c>
       <c r="B31" t="n">
-        <v>92830</v>
+        <v>110763</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4012,31 +4016,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5964</v>
+        <v>219711</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4045,13 +4045,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>350701</v>
+        <v>350754</v>
       </c>
       <c r="R31" t="n">
-        <v>6532566</v>
+        <v>6532572</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4115,7 +4115,7 @@
         <v>128876850</v>
       </c>
       <c r="B32" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>128877309</v>
       </c>
       <c r="B33" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>128877462</v>
       </c>
       <c r="B34" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>128877664</v>
       </c>
       <c r="B35" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128873652</v>
       </c>
       <c r="B36" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>128875600</v>
       </c>
       <c r="B37" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>128876017</v>
       </c>
       <c r="B38" t="n">
-        <v>110759</v>
+        <v>110763</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>128877867</v>
       </c>
       <c r="B39" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>128875778</v>
       </c>
       <c r="B40" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>128878172</v>
       </c>
       <c r="B41" t="n">
-        <v>110759</v>
+        <v>110763</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>128876585</v>
       </c>
       <c r="B42" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>128876816</v>
       </c>
       <c r="B43" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>128877087</v>
       </c>
       <c r="B44" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>128877974</v>
       </c>
       <c r="B45" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>128864631</v>
       </c>
       <c r="B46" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>128898374</v>
       </c>
       <c r="B47" t="n">
-        <v>91277</v>
+        <v>91281</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -883,44 +883,36 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128836713</v>
+        <v>128837146</v>
       </c>
       <c r="B4" t="n">
-        <v>92816</v>
+        <v>92834</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -933,13 +925,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>350682</v>
+        <v>350556</v>
       </c>
       <c r="R4" t="n">
-        <v>6532579</v>
+        <v>6532301</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,7 +965,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar (minst 25 st) med tydlig kumarin/anisdoft som växer i avlångt stråk/häxring i äldre granskog med stor dimensionspridning hos stammarna.</t>
+          <t>Växer här relativt allmänt i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,7 +980,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1006,36 +998,44 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128837146</v>
+        <v>128836713</v>
       </c>
       <c r="B5" t="n">
-        <v>92834</v>
+        <v>92816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>350556</v>
+        <v>350682</v>
       </c>
       <c r="R5" t="n">
-        <v>6532301</v>
+        <v>6532579</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer här relativt allmänt i äldre barrskog.</t>
+          <t>Gott om fruktkroppar (minst 25 st) med tydlig kumarin/anisdoft som växer i avlångt stråk/häxring i äldre granskog med stor dimensionspridning hos stammarna.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -5150,10 +5150,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128878172</v>
+        <v>128876585</v>
       </c>
       <c r="B41" t="n">
-        <v>110763</v>
+        <v>92810</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5161,41 +5161,36 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219711</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5204,13 +5199,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>350562</v>
+        <v>350632</v>
       </c>
       <c r="R41" t="n">
-        <v>6532383</v>
+        <v>6532513</v>
       </c>
       <c r="S41" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5244,7 +5239,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Växer relativt rikligt på fyndplatsen.</t>
+          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5258,7 +5253,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5276,10 +5271,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128876585</v>
+        <v>128878172</v>
       </c>
       <c r="B42" t="n">
-        <v>92810</v>
+        <v>110763</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5287,36 +5282,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>219711</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5325,13 +5325,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>350632</v>
+        <v>350562</v>
       </c>
       <c r="R42" t="n">
-        <v>6532513</v>
+        <v>6532383</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
+          <t>Växer relativt rikligt på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -2382,7 +2382,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128864191</v>
+        <v>128864417</v>
       </c>
       <c r="B17" t="n">
         <v>92834</v>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2432,13 +2432,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>350673</v>
+        <v>350581</v>
       </c>
       <c r="R17" t="n">
-        <v>6532521</v>
+        <v>6532373</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2468,11 +2468,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,7 +2500,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128864417</v>
+        <v>128864191</v>
       </c>
       <c r="B18" t="n">
         <v>92834</v>
@@ -2535,7 +2530,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2555,13 +2550,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>350581</v>
+        <v>350673</v>
       </c>
       <c r="R18" t="n">
-        <v>6532373</v>
+        <v>6532521</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2591,6 +2586,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3773,7 +3773,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128877592</v>
+        <v>128877600</v>
       </c>
       <c r="B29" t="n">
         <v>92834</v>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3811,24 +3811,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>350717</v>
+        <v>350701</v>
       </c>
       <c r="R29" t="n">
-        <v>6532577</v>
+        <v>6532566</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3858,11 +3853,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3894,7 +3884,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128877600</v>
+        <v>128877592</v>
       </c>
       <c r="B30" t="n">
         <v>92834</v>
@@ -3924,7 +3914,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3932,19 +3922,24 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>350701</v>
+        <v>350717</v>
       </c>
       <c r="R30" t="n">
-        <v>6532566</v>
+        <v>6532577</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3974,6 +3969,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4340,7 +4340,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128877462</v>
+        <v>128877664</v>
       </c>
       <c r="B34" t="n">
         <v>92834</v>
@@ -4368,7 +4368,16 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -4380,13 +4389,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>350726</v>
+        <v>350697</v>
       </c>
       <c r="R34" t="n">
-        <v>6532586</v>
+        <v>6532548</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4447,7 +4456,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128877664</v>
+        <v>128877462</v>
       </c>
       <c r="B35" t="n">
         <v>92834</v>
@@ -4475,16 +4484,7 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>350697</v>
+        <v>350726</v>
       </c>
       <c r="R35" t="n">
-        <v>6532548</v>
+        <v>6532586</v>
       </c>
       <c r="S35" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128876585</v>
+        <v>128878172</v>
       </c>
       <c r="B41" t="n">
-        <v>92810</v>
+        <v>110763</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5161,36 +5161,41 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>219711</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5199,13 +5204,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>350632</v>
+        <v>350562</v>
       </c>
       <c r="R41" t="n">
-        <v>6532513</v>
+        <v>6532383</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5239,7 +5244,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
+          <t>Växer relativt rikligt på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5253,7 +5258,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5271,10 +5276,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128878172</v>
+        <v>128876585</v>
       </c>
       <c r="B42" t="n">
-        <v>110763</v>
+        <v>92810</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5282,41 +5287,36 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219711</v>
+        <v>4366</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5325,13 +5325,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>350562</v>
+        <v>350632</v>
       </c>
       <c r="R42" t="n">
-        <v>6532383</v>
+        <v>6532513</v>
       </c>
       <c r="S42" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Växer relativt rikligt på fyndplatsen.</t>
+          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>57166289</v>
       </c>
       <c r="B2" t="n">
-        <v>105684</v>
+        <v>105691</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128831484</v>
       </c>
       <c r="B3" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,36 +883,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128837146</v>
+        <v>128836713</v>
       </c>
       <c r="B4" t="n">
-        <v>92834</v>
+        <v>92821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -925,13 +933,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>350556</v>
+        <v>350682</v>
       </c>
       <c r="R4" t="n">
-        <v>6532301</v>
+        <v>6532579</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Växer här relativt allmänt i äldre barrskog.</t>
+          <t>Gott om fruktkroppar (minst 25 st) med tydlig kumarin/anisdoft som växer i avlångt stråk/häxring i äldre granskog med stor dimensionspridning hos stammarna.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,7 +988,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -998,44 +1006,36 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128836713</v>
+        <v>128837146</v>
       </c>
       <c r="B5" t="n">
-        <v>92816</v>
+        <v>92839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>350682</v>
+        <v>350556</v>
       </c>
       <c r="R5" t="n">
-        <v>6532579</v>
+        <v>6532301</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar (minst 25 st) med tydlig kumarin/anisdoft som växer i avlångt stråk/häxring i äldre granskog med stor dimensionspridning hos stammarna.</t>
+          <t>Växer här relativt allmänt i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1124,7 +1124,7 @@
         <v>128829084</v>
       </c>
       <c r="B6" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>128830471</v>
       </c>
       <c r="B7" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128831345</v>
       </c>
       <c r="B8" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128837030</v>
       </c>
       <c r="B9" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>128830810</v>
       </c>
       <c r="B10" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>128831251</v>
       </c>
       <c r="B11" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>128832520</v>
       </c>
       <c r="B12" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>128832131</v>
       </c>
       <c r="B13" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>128864268</v>
       </c>
       <c r="B14" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128864568</v>
       </c>
       <c r="B15" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>128864345</v>
       </c>
       <c r="B16" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128864417</v>
+        <v>128864191</v>
       </c>
       <c r="B17" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2432,13 +2432,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>350581</v>
+        <v>350673</v>
       </c>
       <c r="R17" t="n">
-        <v>6532373</v>
+        <v>6532521</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2468,6 +2468,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,10 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128864191</v>
+        <v>128864417</v>
       </c>
       <c r="B18" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2535,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2550,13 +2555,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>350673</v>
+        <v>350581</v>
       </c>
       <c r="R18" t="n">
-        <v>6532521</v>
+        <v>6532373</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2586,11 +2591,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,7 +2626,7 @@
         <v>128863610</v>
       </c>
       <c r="B19" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>128863382</v>
       </c>
       <c r="B20" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>128876148</v>
       </c>
       <c r="B21" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>128878422</v>
       </c>
       <c r="B22" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>128876650</v>
       </c>
       <c r="B23" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3200,10 +3200,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128878114</v>
+        <v>128878002</v>
       </c>
       <c r="B24" t="n">
-        <v>92834</v>
+        <v>100831</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,36 +3211,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3249,10 +3240,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>350572</v>
+        <v>350594</v>
       </c>
       <c r="R24" t="n">
-        <v>6532383</v>
+        <v>6532414</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3287,11 +3278,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Växer delvis ihalv hägring.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3303,7 +3289,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3321,10 +3307,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128874644</v>
+        <v>128875354</v>
       </c>
       <c r="B25" t="n">
-        <v>92834</v>
+        <v>100831</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3332,42 +3318,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>350638</v>
+        <v>350609</v>
       </c>
       <c r="R25" t="n">
-        <v>6532616</v>
+        <v>6532560</v>
       </c>
       <c r="S25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3428,10 +3414,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128878002</v>
+        <v>128878114</v>
       </c>
       <c r="B26" t="n">
-        <v>100824</v>
+        <v>92839</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3439,27 +3425,36 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3468,10 +3463,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>350594</v>
+        <v>350572</v>
       </c>
       <c r="R26" t="n">
-        <v>6532414</v>
+        <v>6532383</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3506,6 +3501,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Växer delvis ihalv hägring.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128875354</v>
+        <v>128874644</v>
       </c>
       <c r="B27" t="n">
-        <v>100824</v>
+        <v>92839</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3546,42 +3546,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långkasen, Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>350609</v>
+        <v>350638</v>
       </c>
       <c r="R27" t="n">
-        <v>6532560</v>
+        <v>6532616</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>128877739</v>
       </c>
       <c r="B28" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128877600</v>
+        <v>128877592</v>
       </c>
       <c r="B29" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3811,19 +3811,24 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>350701</v>
+        <v>350717</v>
       </c>
       <c r="R29" t="n">
-        <v>6532566</v>
+        <v>6532577</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3853,6 +3858,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3884,10 +3894,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128877592</v>
+        <v>128877600</v>
       </c>
       <c r="B30" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3914,7 +3924,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3922,24 +3932,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>350717</v>
+        <v>350701</v>
       </c>
       <c r="R30" t="n">
-        <v>6532577</v>
+        <v>6532566</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3969,11 +3974,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4008,7 +4008,7 @@
         <v>128877139</v>
       </c>
       <c r="B31" t="n">
-        <v>110763</v>
+        <v>110771</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>128876850</v>
       </c>
       <c r="B32" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>128877309</v>
       </c>
       <c r="B33" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4340,10 +4340,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128877664</v>
+        <v>128877462</v>
       </c>
       <c r="B34" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4368,16 +4368,7 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -4389,13 +4380,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>350697</v>
+        <v>350726</v>
       </c>
       <c r="R34" t="n">
-        <v>6532548</v>
+        <v>6532586</v>
       </c>
       <c r="S34" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4456,10 +4447,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128877462</v>
+        <v>128877664</v>
       </c>
       <c r="B35" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4475,16 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>350726</v>
+        <v>350697</v>
       </c>
       <c r="R35" t="n">
-        <v>6532586</v>
+        <v>6532548</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128873652</v>
       </c>
       <c r="B36" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4670,10 +4670,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128875600</v>
+        <v>128876017</v>
       </c>
       <c r="B37" t="n">
-        <v>92834</v>
+        <v>110771</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4681,36 +4681,36 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5964</v>
+        <v>219711</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>350590</v>
+        <v>350614</v>
       </c>
       <c r="R37" t="n">
-        <v>6532525</v>
+        <v>6532523</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -4757,6 +4757,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i äldre granskog där även andra kalkgynnade arter växer.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4768,7 +4773,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4786,10 +4791,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128876017</v>
+        <v>128875600</v>
       </c>
       <c r="B38" t="n">
-        <v>110763</v>
+        <v>92839</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4797,36 +4802,36 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219711</v>
+        <v>5964</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4835,10 +4840,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>350614</v>
+        <v>350590</v>
       </c>
       <c r="R38" t="n">
-        <v>6532523</v>
+        <v>6532525</v>
       </c>
       <c r="S38" t="n">
         <v>9</v>
@@ -4873,11 +4878,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i äldre granskog där även andra kalkgynnade arter växer.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4910,7 +4910,7 @@
         <v>128877867</v>
       </c>
       <c r="B39" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>128875778</v>
       </c>
       <c r="B40" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128878172</v>
+        <v>128876585</v>
       </c>
       <c r="B41" t="n">
-        <v>110763</v>
+        <v>92815</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5161,41 +5161,36 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219711</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5204,13 +5199,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>350562</v>
+        <v>350632</v>
       </c>
       <c r="R41" t="n">
-        <v>6532383</v>
+        <v>6532513</v>
       </c>
       <c r="S41" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5244,7 +5239,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Växer relativt rikligt på fyndplatsen.</t>
+          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5258,7 +5253,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5276,10 +5271,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128876585</v>
+        <v>128878172</v>
       </c>
       <c r="B42" t="n">
-        <v>92810</v>
+        <v>110771</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5287,36 +5282,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>219711</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5325,13 +5325,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>350632</v>
+        <v>350562</v>
       </c>
       <c r="R42" t="n">
-        <v>6532513</v>
+        <v>6532383</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
+          <t>Växer relativt rikligt på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5400,7 +5400,7 @@
         <v>128876816</v>
       </c>
       <c r="B43" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>128877087</v>
       </c>
       <c r="B44" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>128877974</v>
       </c>
       <c r="B45" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>128864631</v>
       </c>
       <c r="B46" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>128898374</v>
       </c>
       <c r="B47" t="n">
-        <v>91281</v>
+        <v>91286</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -3200,10 +3200,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128878002</v>
+        <v>128878114</v>
       </c>
       <c r="B24" t="n">
-        <v>100839</v>
+        <v>92847</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,27 +3211,36 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3240,10 +3249,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>350594</v>
+        <v>350572</v>
       </c>
       <c r="R24" t="n">
-        <v>6532414</v>
+        <v>6532383</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3278,6 +3287,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växer delvis ihalv hägring.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3289,7 +3303,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3307,10 +3321,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128875354</v>
+        <v>128874644</v>
       </c>
       <c r="B25" t="n">
-        <v>100839</v>
+        <v>92847</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3318,42 +3332,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långkasen, Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>350609</v>
+        <v>350638</v>
       </c>
       <c r="R25" t="n">
-        <v>6532560</v>
+        <v>6532616</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3414,10 +3428,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128878114</v>
+        <v>128878002</v>
       </c>
       <c r="B26" t="n">
-        <v>92847</v>
+        <v>100839</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,36 +3439,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3463,10 +3468,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>350572</v>
+        <v>350594</v>
       </c>
       <c r="R26" t="n">
-        <v>6532383</v>
+        <v>6532414</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3501,11 +3506,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Växer delvis ihalv hägring.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128874644</v>
+        <v>128875354</v>
       </c>
       <c r="B27" t="n">
-        <v>92847</v>
+        <v>100839</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3546,42 +3546,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>350638</v>
+        <v>350609</v>
       </c>
       <c r="R27" t="n">
-        <v>6532616</v>
+        <v>6532560</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128878172</v>
+        <v>128876585</v>
       </c>
       <c r="B41" t="n">
-        <v>110779</v>
+        <v>92823</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5161,41 +5161,36 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219711</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5204,13 +5199,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>350562</v>
+        <v>350632</v>
       </c>
       <c r="R41" t="n">
-        <v>6532383</v>
+        <v>6532513</v>
       </c>
       <c r="S41" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5244,7 +5239,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Växer relativt rikligt på fyndplatsen.</t>
+          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5258,7 +5253,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5276,10 +5271,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128876585</v>
+        <v>128878172</v>
       </c>
       <c r="B42" t="n">
-        <v>92823</v>
+        <v>110779</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5287,36 +5282,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>219711</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5325,13 +5325,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>350632</v>
+        <v>350562</v>
       </c>
       <c r="R42" t="n">
-        <v>6532513</v>
+        <v>6532383</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
+          <t>Växer relativt rikligt på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128877087</v>
+        <v>128876816</v>
       </c>
       <c r="B43" t="n">
-        <v>100839</v>
+        <v>92847</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5408,27 +5408,36 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5437,13 +5446,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>350761</v>
+        <v>350632</v>
       </c>
       <c r="R43" t="n">
-        <v>6532577</v>
+        <v>6532521</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5504,10 +5513,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128876816</v>
+        <v>128877087</v>
       </c>
       <c r="B44" t="n">
-        <v>92847</v>
+        <v>100839</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5515,36 +5524,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>350632</v>
+        <v>350761</v>
       </c>
       <c r="R44" t="n">
-        <v>6532521</v>
+        <v>6532577</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128831484</v>
       </c>
       <c r="B3" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,44 +883,36 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128836713</v>
+        <v>128837146</v>
       </c>
       <c r="B4" t="n">
-        <v>92829</v>
+        <v>92852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -933,13 +925,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>350682</v>
+        <v>350556</v>
       </c>
       <c r="R4" t="n">
-        <v>6532579</v>
+        <v>6532301</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,7 +965,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar (minst 25 st) med tydlig kumarin/anisdoft som växer i avlångt stråk/häxring i äldre granskog med stor dimensionspridning hos stammarna.</t>
+          <t>Växer här relativt allmänt i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,7 +980,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1006,36 +998,44 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128837146</v>
+        <v>128836713</v>
       </c>
       <c r="B5" t="n">
-        <v>92847</v>
+        <v>92834</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>350556</v>
+        <v>350682</v>
       </c>
       <c r="R5" t="n">
-        <v>6532301</v>
+        <v>6532579</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer här relativt allmänt i äldre barrskog.</t>
+          <t>Gott om fruktkroppar (minst 25 st) med tydlig kumarin/anisdoft som växer i avlångt stråk/häxring i äldre granskog med stor dimensionspridning hos stammarna.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1124,7 +1124,7 @@
         <v>128829084</v>
       </c>
       <c r="B6" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>128830471</v>
       </c>
       <c r="B7" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128837030</v>
       </c>
       <c r="B9" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,49 +1571,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128830810</v>
+        <v>128831251</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>100844</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1622,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>350667</v>
+        <v>350678</v>
       </c>
       <c r="R10" t="n">
-        <v>6532520</v>
+        <v>6532445</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1657,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1667,12 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:40</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 2 talltitor (ev. flera individer) hördes med lockläten i flerskiktad äldre granskog.</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,7 +1670,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1704,38 +1688,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128831251</v>
+        <v>128830810</v>
       </c>
       <c r="B11" t="n">
-        <v>100839</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1744,13 +1739,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>350678</v>
+        <v>350667</v>
       </c>
       <c r="R11" t="n">
-        <v>6532445</v>
+        <v>6532520</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1779,7 +1774,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,7 +1784,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Minst 2 talltitor (ev. flera individer) hördes med lockläten i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1824,7 +1824,7 @@
         <v>128832520</v>
       </c>
       <c r="B12" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>128832131</v>
       </c>
       <c r="B13" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>128864268</v>
       </c>
       <c r="B14" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128864568</v>
       </c>
       <c r="B15" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>128864345</v>
       </c>
       <c r="B16" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>128864191</v>
       </c>
       <c r="B17" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>128864417</v>
       </c>
       <c r="B18" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>128863610</v>
       </c>
       <c r="B19" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>128863382</v>
       </c>
       <c r="B20" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>128876148</v>
       </c>
       <c r="B21" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>128878422</v>
       </c>
       <c r="B22" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>128876650</v>
       </c>
       <c r="B23" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>128878114</v>
       </c>
       <c r="B24" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>128874644</v>
       </c>
       <c r="B25" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>128878002</v>
       </c>
       <c r="B26" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>128875354</v>
       </c>
       <c r="B27" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>128877592</v>
       </c>
       <c r="B29" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>128877600</v>
       </c>
       <c r="B30" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>128877139</v>
       </c>
       <c r="B31" t="n">
-        <v>110779</v>
+        <v>110784</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>128876850</v>
       </c>
       <c r="B32" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>128877309</v>
       </c>
       <c r="B33" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>128877462</v>
       </c>
       <c r="B34" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>128877664</v>
       </c>
       <c r="B35" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128873652</v>
       </c>
       <c r="B36" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>128875600</v>
       </c>
       <c r="B37" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>128876017</v>
       </c>
       <c r="B38" t="n">
-        <v>110779</v>
+        <v>110784</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>128875778</v>
       </c>
       <c r="B40" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>128876585</v>
       </c>
       <c r="B41" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>128878172</v>
       </c>
       <c r="B42" t="n">
-        <v>110779</v>
+        <v>110784</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>128876816</v>
       </c>
       <c r="B43" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>128877087</v>
       </c>
       <c r="B44" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>128877974</v>
       </c>
       <c r="B45" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>128864631</v>
       </c>
       <c r="B46" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>128898374</v>
       </c>
       <c r="B47" t="n">
-        <v>91293</v>
+        <v>91296</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128831484</v>
       </c>
       <c r="B3" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,36 +883,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128837146</v>
+        <v>128836713</v>
       </c>
       <c r="B4" t="n">
-        <v>92852</v>
+        <v>92837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -925,13 +933,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>350556</v>
+        <v>350682</v>
       </c>
       <c r="R4" t="n">
-        <v>6532301</v>
+        <v>6532579</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Växer här relativt allmänt i äldre barrskog.</t>
+          <t>Gott om fruktkroppar (minst 25 st) med tydlig kumarin/anisdoft som växer i avlångt stråk/häxring i äldre granskog med stor dimensionspridning hos stammarna.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,7 +988,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -998,44 +1006,36 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128836713</v>
+        <v>128837146</v>
       </c>
       <c r="B5" t="n">
-        <v>92834</v>
+        <v>92855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>350682</v>
+        <v>350556</v>
       </c>
       <c r="R5" t="n">
-        <v>6532579</v>
+        <v>6532301</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar (minst 25 st) med tydlig kumarin/anisdoft som växer i avlångt stråk/häxring i äldre granskog med stor dimensionspridning hos stammarna.</t>
+          <t>Växer här relativt allmänt i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1124,7 +1124,7 @@
         <v>128829084</v>
       </c>
       <c r="B6" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>128830471</v>
       </c>
       <c r="B7" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128837030</v>
       </c>
       <c r="B9" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>128831251</v>
       </c>
       <c r="B10" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>128832520</v>
       </c>
       <c r="B12" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>128832131</v>
       </c>
       <c r="B13" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>128864268</v>
       </c>
       <c r="B14" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128864568</v>
       </c>
       <c r="B15" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>128864345</v>
       </c>
       <c r="B16" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>128864191</v>
       </c>
       <c r="B17" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>128864417</v>
       </c>
       <c r="B18" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>128863610</v>
       </c>
       <c r="B19" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>128863382</v>
       </c>
       <c r="B20" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>128876148</v>
       </c>
       <c r="B21" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>128878422</v>
       </c>
       <c r="B22" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>128876650</v>
       </c>
       <c r="B23" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>128878114</v>
       </c>
       <c r="B24" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>128874644</v>
       </c>
       <c r="B25" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>128878002</v>
       </c>
       <c r="B26" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>128875354</v>
       </c>
       <c r="B27" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>128877592</v>
       </c>
       <c r="B29" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>128877600</v>
       </c>
       <c r="B30" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>128877139</v>
       </c>
       <c r="B31" t="n">
-        <v>110784</v>
+        <v>110787</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>128876850</v>
       </c>
       <c r="B32" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>128877309</v>
       </c>
       <c r="B33" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>128877462</v>
       </c>
       <c r="B34" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>128877664</v>
       </c>
       <c r="B35" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128873652</v>
       </c>
       <c r="B36" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4670,10 +4670,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128875600</v>
+        <v>128876017</v>
       </c>
       <c r="B37" t="n">
-        <v>92852</v>
+        <v>110787</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4681,36 +4681,36 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5964</v>
+        <v>219711</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>350590</v>
+        <v>350614</v>
       </c>
       <c r="R37" t="n">
-        <v>6532525</v>
+        <v>6532523</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -4757,6 +4757,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i äldre granskog där även andra kalkgynnade arter växer.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4768,7 +4773,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4786,10 +4791,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128876017</v>
+        <v>128875600</v>
       </c>
       <c r="B38" t="n">
-        <v>110784</v>
+        <v>92855</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4797,36 +4802,36 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219711</v>
+        <v>5964</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4835,10 +4840,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>350614</v>
+        <v>350590</v>
       </c>
       <c r="R38" t="n">
-        <v>6532523</v>
+        <v>6532525</v>
       </c>
       <c r="S38" t="n">
         <v>9</v>
@@ -4873,11 +4878,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i äldre granskog där även andra kalkgynnade arter växer.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5041,7 +5041,7 @@
         <v>128875778</v>
       </c>
       <c r="B40" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>128876585</v>
       </c>
       <c r="B41" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>128878172</v>
       </c>
       <c r="B42" t="n">
-        <v>110784</v>
+        <v>110787</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128876816</v>
+        <v>128877087</v>
       </c>
       <c r="B43" t="n">
-        <v>92852</v>
+        <v>100847</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5408,36 +5408,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5446,13 +5437,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>350632</v>
+        <v>350761</v>
       </c>
       <c r="R43" t="n">
-        <v>6532521</v>
+        <v>6532577</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5513,10 +5504,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128877087</v>
+        <v>128876816</v>
       </c>
       <c r="B44" t="n">
-        <v>100844</v>
+        <v>92855</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5524,27 +5515,36 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>350761</v>
+        <v>350632</v>
       </c>
       <c r="R44" t="n">
-        <v>6532577</v>
+        <v>6532521</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>128877974</v>
       </c>
       <c r="B45" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>128864631</v>
       </c>
       <c r="B46" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>128898374</v>
       </c>
       <c r="B47" t="n">
-        <v>91296</v>
+        <v>91299</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -1571,38 +1571,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128831251</v>
+        <v>128830810</v>
       </c>
       <c r="B10" t="n">
-        <v>100847</v>
+        <v>57883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1611,13 +1622,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>350678</v>
+        <v>350667</v>
       </c>
       <c r="R10" t="n">
-        <v>6532445</v>
+        <v>6532520</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1657,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1667,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 2 talltitor (ev. flera individer) hördes med lockläten i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,7 +1686,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1688,49 +1704,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128830810</v>
+        <v>128831251</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>100847</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1739,13 +1744,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>350667</v>
+        <v>350678</v>
       </c>
       <c r="R11" t="n">
-        <v>6532520</v>
+        <v>6532445</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,7 +1779,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1784,12 +1789,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:40</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Minst 2 talltitor (ev. flera individer) hördes med lockläten i flerskiktad äldre granskog.</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128864345</v>
+        <v>128864191</v>
       </c>
       <c r="B16" t="n">
-        <v>92464</v>
+        <v>92855</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2275,26 +2275,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2314,13 +2314,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>350592</v>
+        <v>350673</v>
       </c>
       <c r="R16" t="n">
-        <v>6532382</v>
+        <v>6532521</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2350,6 +2350,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,7 +2387,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128864191</v>
+        <v>128864417</v>
       </c>
       <c r="B17" t="n">
         <v>92855</v>
@@ -2412,7 +2417,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2432,13 +2437,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>350673</v>
+        <v>350581</v>
       </c>
       <c r="R17" t="n">
-        <v>6532521</v>
+        <v>6532373</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2468,11 +2473,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,10 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128864417</v>
+        <v>128864345</v>
       </c>
       <c r="B18" t="n">
-        <v>92855</v>
+        <v>92464</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,21 +2516,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>350581</v>
+        <v>350592</v>
       </c>
       <c r="R18" t="n">
-        <v>6532373</v>
+        <v>6532382</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -4670,10 +4670,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128876017</v>
+        <v>128875600</v>
       </c>
       <c r="B37" t="n">
-        <v>110787</v>
+        <v>92855</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4681,36 +4681,36 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219711</v>
+        <v>5964</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>350614</v>
+        <v>350590</v>
       </c>
       <c r="R37" t="n">
-        <v>6532523</v>
+        <v>6532525</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -4757,11 +4757,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i äldre granskog där även andra kalkgynnade arter växer.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4773,7 +4768,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4791,10 +4786,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128875600</v>
+        <v>128876017</v>
       </c>
       <c r="B38" t="n">
-        <v>92855</v>
+        <v>110787</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4802,36 +4797,36 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5964</v>
+        <v>219711</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4840,10 +4835,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>350590</v>
+        <v>350614</v>
       </c>
       <c r="R38" t="n">
-        <v>6532525</v>
+        <v>6532523</v>
       </c>
       <c r="S38" t="n">
         <v>9</v>
@@ -4878,6 +4873,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i äldre granskog där även andra kalkgynnade arter växer.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -5397,10 +5397,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128877087</v>
+        <v>128876816</v>
       </c>
       <c r="B43" t="n">
-        <v>100847</v>
+        <v>92855</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5408,27 +5408,36 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5437,13 +5446,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>350761</v>
+        <v>350632</v>
       </c>
       <c r="R43" t="n">
-        <v>6532577</v>
+        <v>6532521</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5504,10 +5513,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128876816</v>
+        <v>128877087</v>
       </c>
       <c r="B44" t="n">
-        <v>92855</v>
+        <v>100847</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5515,36 +5524,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>350632</v>
+        <v>350761</v>
       </c>
       <c r="R44" t="n">
-        <v>6532521</v>
+        <v>6532577</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -1571,49 +1571,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128830810</v>
+        <v>128831251</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>100847</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1622,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>350667</v>
+        <v>350678</v>
       </c>
       <c r="R10" t="n">
-        <v>6532520</v>
+        <v>6532445</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1657,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1667,12 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:40</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 2 talltitor (ev. flera individer) hördes med lockläten i flerskiktad äldre granskog.</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,7 +1670,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1704,38 +1688,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128831251</v>
+        <v>128830810</v>
       </c>
       <c r="B11" t="n">
-        <v>100847</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1744,13 +1739,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>350678</v>
+        <v>350667</v>
       </c>
       <c r="R11" t="n">
-        <v>6532445</v>
+        <v>6532520</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1779,7 +1774,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,7 +1784,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Minst 2 talltitor (ev. flera individer) hördes med lockläten i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128877592</v>
+        <v>128877139</v>
       </c>
       <c r="B29" t="n">
-        <v>92855</v>
+        <v>110787</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,36 +3784,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5964</v>
+        <v>219711</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3822,13 +3813,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>350717</v>
+        <v>350754</v>
       </c>
       <c r="R29" t="n">
-        <v>6532577</v>
+        <v>6532572</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3860,11 +3851,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3876,7 +3862,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3894,7 +3880,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128877600</v>
+        <v>128877592</v>
       </c>
       <c r="B30" t="n">
         <v>92855</v>
@@ -3924,7 +3910,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3932,19 +3918,24 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>350701</v>
+        <v>350717</v>
       </c>
       <c r="R30" t="n">
-        <v>6532566</v>
+        <v>6532577</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3974,6 +3965,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4005,10 +4001,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128877139</v>
+        <v>128877600</v>
       </c>
       <c r="B31" t="n">
-        <v>110787</v>
+        <v>92855</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4016,27 +4012,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219711</v>
+        <v>5964</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4045,13 +4045,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>350754</v>
+        <v>350701</v>
       </c>
       <c r="R31" t="n">
-        <v>6532572</v>
+        <v>6532566</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4670,10 +4670,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128875600</v>
+        <v>128876017</v>
       </c>
       <c r="B37" t="n">
-        <v>92855</v>
+        <v>110787</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4681,36 +4681,36 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5964</v>
+        <v>219711</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>350590</v>
+        <v>350614</v>
       </c>
       <c r="R37" t="n">
-        <v>6532525</v>
+        <v>6532523</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -4757,6 +4757,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i äldre granskog där även andra kalkgynnade arter växer.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4768,7 +4773,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4786,10 +4791,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128876017</v>
+        <v>128875600</v>
       </c>
       <c r="B38" t="n">
-        <v>110787</v>
+        <v>92855</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4797,36 +4802,36 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219711</v>
+        <v>5964</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4835,10 +4840,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>350614</v>
+        <v>350590</v>
       </c>
       <c r="R38" t="n">
-        <v>6532523</v>
+        <v>6532525</v>
       </c>
       <c r="S38" t="n">
         <v>9</v>
@@ -4873,11 +4878,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i äldre granskog där även andra kalkgynnade arter växer.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128831484</v>
       </c>
       <c r="B3" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128836713</v>
       </c>
       <c r="B4" t="n">
-        <v>92837</v>
+        <v>92844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>128837146</v>
       </c>
       <c r="B5" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>128829084</v>
       </c>
       <c r="B6" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>128830471</v>
       </c>
       <c r="B7" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128831345</v>
       </c>
       <c r="B8" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128837030</v>
       </c>
       <c r="B9" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,38 +1571,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128831251</v>
+        <v>128830810</v>
       </c>
       <c r="B10" t="n">
-        <v>100847</v>
+        <v>57885</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1611,13 +1622,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>350678</v>
+        <v>350667</v>
       </c>
       <c r="R10" t="n">
-        <v>6532445</v>
+        <v>6532520</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1657,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1667,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 2 talltitor (ev. flera individer) hördes med lockläten i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,7 +1686,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1688,49 +1704,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128830810</v>
+        <v>128831251</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>100857</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1739,13 +1744,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>350667</v>
+        <v>350678</v>
       </c>
       <c r="R11" t="n">
-        <v>6532520</v>
+        <v>6532445</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,7 +1779,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1784,12 +1789,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:40</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Minst 2 talltitor (ev. flera individer) hördes med lockläten i flerskiktad äldre granskog.</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1824,7 +1824,7 @@
         <v>128832520</v>
       </c>
       <c r="B12" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>128832131</v>
       </c>
       <c r="B13" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>128864268</v>
       </c>
       <c r="B14" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128864568</v>
       </c>
       <c r="B15" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,10 +2264,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128864191</v>
+        <v>128864345</v>
       </c>
       <c r="B16" t="n">
-        <v>92855</v>
+        <v>92471</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2275,26 +2275,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2314,13 +2314,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>350673</v>
+        <v>350592</v>
       </c>
       <c r="R16" t="n">
-        <v>6532521</v>
+        <v>6532382</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2350,11 +2350,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,10 +2382,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128864417</v>
+        <v>128864191</v>
       </c>
       <c r="B17" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,7 +2412,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2437,13 +2432,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>350581</v>
+        <v>350673</v>
       </c>
       <c r="R17" t="n">
-        <v>6532373</v>
+        <v>6532521</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2473,6 +2468,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,10 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128864345</v>
+        <v>128864417</v>
       </c>
       <c r="B18" t="n">
-        <v>92464</v>
+        <v>92862</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,21 +2516,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>350592</v>
+        <v>350581</v>
       </c>
       <c r="R18" t="n">
-        <v>6532382</v>
+        <v>6532373</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2626,7 +2626,7 @@
         <v>128863610</v>
       </c>
       <c r="B19" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>128863382</v>
       </c>
       <c r="B20" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>128876148</v>
       </c>
       <c r="B21" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>128878422</v>
       </c>
       <c r="B22" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>128876650</v>
       </c>
       <c r="B23" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3200,10 +3200,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128878114</v>
+        <v>128878002</v>
       </c>
       <c r="B24" t="n">
-        <v>92855</v>
+        <v>100857</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,36 +3211,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3249,10 +3240,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>350572</v>
+        <v>350594</v>
       </c>
       <c r="R24" t="n">
-        <v>6532383</v>
+        <v>6532414</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3287,11 +3278,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Växer delvis ihalv hägring.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3303,7 +3289,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3321,10 +3307,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128874644</v>
+        <v>128875354</v>
       </c>
       <c r="B25" t="n">
-        <v>92855</v>
+        <v>100857</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3332,42 +3318,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>350638</v>
+        <v>350609</v>
       </c>
       <c r="R25" t="n">
-        <v>6532616</v>
+        <v>6532560</v>
       </c>
       <c r="S25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3428,10 +3414,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128878002</v>
+        <v>128878114</v>
       </c>
       <c r="B26" t="n">
-        <v>100847</v>
+        <v>92862</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3439,27 +3425,36 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3468,10 +3463,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>350594</v>
+        <v>350572</v>
       </c>
       <c r="R26" t="n">
-        <v>6532414</v>
+        <v>6532383</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3506,6 +3501,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Växer delvis ihalv hägring.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128875354</v>
+        <v>128874644</v>
       </c>
       <c r="B27" t="n">
-        <v>100847</v>
+        <v>92862</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3546,42 +3546,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långkasen, Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>350609</v>
+        <v>350638</v>
       </c>
       <c r="R27" t="n">
-        <v>6532560</v>
+        <v>6532616</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>128877739</v>
       </c>
       <c r="B28" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128877139</v>
+        <v>128877592</v>
       </c>
       <c r="B29" t="n">
-        <v>110787</v>
+        <v>92862</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,27 +3784,36 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219711</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3813,13 +3822,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>350754</v>
+        <v>350717</v>
       </c>
       <c r="R29" t="n">
-        <v>6532572</v>
+        <v>6532577</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3851,6 +3860,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3862,7 +3876,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3880,10 +3894,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128877592</v>
+        <v>128877600</v>
       </c>
       <c r="B30" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3910,7 +3924,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3918,24 +3932,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>350717</v>
+        <v>350701</v>
       </c>
       <c r="R30" t="n">
-        <v>6532577</v>
+        <v>6532566</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3965,11 +3974,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4001,10 +4005,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128877600</v>
+        <v>128877139</v>
       </c>
       <c r="B31" t="n">
-        <v>92855</v>
+        <v>110797</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4012,31 +4016,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5964</v>
+        <v>219711</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4045,13 +4045,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>350701</v>
+        <v>350754</v>
       </c>
       <c r="R31" t="n">
-        <v>6532566</v>
+        <v>6532572</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4115,7 +4115,7 @@
         <v>128876850</v>
       </c>
       <c r="B32" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>128877309</v>
       </c>
       <c r="B33" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>128877462</v>
       </c>
       <c r="B34" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>128877664</v>
       </c>
       <c r="B35" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128873652</v>
       </c>
       <c r="B36" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4670,10 +4670,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128876017</v>
+        <v>128875600</v>
       </c>
       <c r="B37" t="n">
-        <v>110787</v>
+        <v>92862</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4681,36 +4681,36 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219711</v>
+        <v>5964</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>350614</v>
+        <v>350590</v>
       </c>
       <c r="R37" t="n">
-        <v>6532523</v>
+        <v>6532525</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -4757,11 +4757,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i äldre granskog där även andra kalkgynnade arter växer.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4773,7 +4768,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4791,10 +4786,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128875600</v>
+        <v>128876017</v>
       </c>
       <c r="B38" t="n">
-        <v>92855</v>
+        <v>110797</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4802,36 +4797,36 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5964</v>
+        <v>219711</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4840,10 +4835,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>350590</v>
+        <v>350614</v>
       </c>
       <c r="R38" t="n">
-        <v>6532525</v>
+        <v>6532523</v>
       </c>
       <c r="S38" t="n">
         <v>9</v>
@@ -4878,6 +4873,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i äldre granskog där även andra kalkgynnade arter växer.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4910,7 +4910,7 @@
         <v>128877867</v>
       </c>
       <c r="B39" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>128875778</v>
       </c>
       <c r="B40" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>128876585</v>
       </c>
       <c r="B41" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>128878172</v>
       </c>
       <c r="B42" t="n">
-        <v>110787</v>
+        <v>110797</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>128876816</v>
       </c>
       <c r="B43" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>128877087</v>
       </c>
       <c r="B44" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>128877974</v>
       </c>
       <c r="B45" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>128864631</v>
       </c>
       <c r="B46" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>128898374</v>
       </c>
       <c r="B47" t="n">
-        <v>91299</v>
+        <v>91305</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -883,44 +883,36 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128836713</v>
+        <v>128837146</v>
       </c>
       <c r="B4" t="n">
-        <v>92844</v>
+        <v>92862</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -933,13 +925,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>350682</v>
+        <v>350556</v>
       </c>
       <c r="R4" t="n">
-        <v>6532579</v>
+        <v>6532301</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,7 +965,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar (minst 25 st) med tydlig kumarin/anisdoft som växer i avlångt stråk/häxring i äldre granskog med stor dimensionspridning hos stammarna.</t>
+          <t>Växer här relativt allmänt i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,7 +980,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1006,36 +998,44 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128837146</v>
+        <v>128836713</v>
       </c>
       <c r="B5" t="n">
-        <v>92862</v>
+        <v>92844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>350556</v>
+        <v>350682</v>
       </c>
       <c r="R5" t="n">
-        <v>6532301</v>
+        <v>6532579</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer här relativt allmänt i äldre barrskog.</t>
+          <t>Gott om fruktkroppar (minst 25 st) med tydlig kumarin/anisdoft som växer i avlångt stråk/häxring i äldre granskog med stor dimensionspridning hos stammarna.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128864345</v>
+        <v>128864191</v>
       </c>
       <c r="B16" t="n">
-        <v>92471</v>
+        <v>92862</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2275,26 +2275,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2314,13 +2314,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>350592</v>
+        <v>350673</v>
       </c>
       <c r="R16" t="n">
-        <v>6532382</v>
+        <v>6532521</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2350,6 +2350,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,7 +2387,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128864191</v>
+        <v>128864417</v>
       </c>
       <c r="B17" t="n">
         <v>92862</v>
@@ -2412,7 +2417,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2432,13 +2437,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>350673</v>
+        <v>350581</v>
       </c>
       <c r="R17" t="n">
-        <v>6532521</v>
+        <v>6532373</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2468,11 +2473,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,10 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128864417</v>
+        <v>128864345</v>
       </c>
       <c r="B18" t="n">
-        <v>92862</v>
+        <v>92471</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,21 +2516,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>350581</v>
+        <v>350592</v>
       </c>
       <c r="R18" t="n">
-        <v>6532373</v>
+        <v>6532382</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3200,10 +3200,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128878002</v>
+        <v>128874644</v>
       </c>
       <c r="B24" t="n">
-        <v>100857</v>
+        <v>92862</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,42 +3211,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långkasen, Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>350594</v>
+        <v>350638</v>
       </c>
       <c r="R24" t="n">
-        <v>6532414</v>
+        <v>6532616</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128875354</v>
+        <v>128878114</v>
       </c>
       <c r="B25" t="n">
-        <v>100857</v>
+        <v>92862</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3318,27 +3318,36 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3347,13 +3356,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>350609</v>
+        <v>350572</v>
       </c>
       <c r="R25" t="n">
-        <v>6532560</v>
+        <v>6532383</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3383,6 +3392,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Växer delvis ihalv hägring.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3414,10 +3428,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128878114</v>
+        <v>128878002</v>
       </c>
       <c r="B26" t="n">
-        <v>92862</v>
+        <v>100857</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,36 +3439,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3463,10 +3468,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>350572</v>
+        <v>350594</v>
       </c>
       <c r="R26" t="n">
-        <v>6532383</v>
+        <v>6532414</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3501,11 +3506,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Växer delvis ihalv hägring.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128874644</v>
+        <v>128875354</v>
       </c>
       <c r="B27" t="n">
-        <v>92862</v>
+        <v>100857</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3546,42 +3546,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>350638</v>
+        <v>350609</v>
       </c>
       <c r="R27" t="n">
-        <v>6532616</v>
+        <v>6532560</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128831484</v>
       </c>
       <c r="B3" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,36 +883,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128837146</v>
+        <v>128836713</v>
       </c>
       <c r="B4" t="n">
-        <v>92862</v>
+        <v>92851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -925,13 +933,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>350556</v>
+        <v>350682</v>
       </c>
       <c r="R4" t="n">
-        <v>6532301</v>
+        <v>6532579</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Växer här relativt allmänt i äldre barrskog.</t>
+          <t>Gott om fruktkroppar (minst 25 st) med tydlig kumarin/anisdoft som växer i avlångt stråk/häxring i äldre granskog med stor dimensionspridning hos stammarna.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,7 +988,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -998,44 +1006,36 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128836713</v>
+        <v>128837146</v>
       </c>
       <c r="B5" t="n">
-        <v>92844</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>350682</v>
+        <v>350556</v>
       </c>
       <c r="R5" t="n">
-        <v>6532579</v>
+        <v>6532301</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar (minst 25 st) med tydlig kumarin/anisdoft som växer i avlångt stråk/häxring i äldre granskog med stor dimensionspridning hos stammarna.</t>
+          <t>Växer här relativt allmänt i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1124,7 +1124,7 @@
         <v>128829084</v>
       </c>
       <c r="B6" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>128830471</v>
       </c>
       <c r="B7" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128837030</v>
       </c>
       <c r="B9" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>128831251</v>
       </c>
       <c r="B11" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>128832520</v>
       </c>
       <c r="B12" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>128832131</v>
       </c>
       <c r="B13" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>128864268</v>
       </c>
       <c r="B14" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128864568</v>
       </c>
       <c r="B15" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>128864191</v>
       </c>
       <c r="B16" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>128864417</v>
       </c>
       <c r="B17" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>128864345</v>
       </c>
       <c r="B18" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>128863610</v>
       </c>
       <c r="B19" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>128863382</v>
       </c>
       <c r="B20" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>128876148</v>
       </c>
       <c r="B21" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>128878422</v>
       </c>
       <c r="B22" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>128876650</v>
       </c>
       <c r="B23" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3200,10 +3200,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128874644</v>
+        <v>128878114</v>
       </c>
       <c r="B24" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3228,7 +3228,16 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -3236,17 +3245,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>350638</v>
+        <v>350572</v>
       </c>
       <c r="R24" t="n">
-        <v>6532616</v>
+        <v>6532383</v>
       </c>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3276,6 +3285,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växer delvis ihalv hägring.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3307,10 +3321,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128878114</v>
+        <v>128874644</v>
       </c>
       <c r="B25" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3335,16 +3349,7 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -3352,17 +3357,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långkasen, Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>350572</v>
+        <v>350638</v>
       </c>
       <c r="R25" t="n">
-        <v>6532383</v>
+        <v>6532616</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3392,11 +3397,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Växer delvis ihalv hägring.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3431,7 +3431,7 @@
         <v>128878002</v>
       </c>
       <c r="B26" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>128875354</v>
       </c>
       <c r="B27" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>128877592</v>
       </c>
       <c r="B29" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>128877600</v>
       </c>
       <c r="B30" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>128877139</v>
       </c>
       <c r="B31" t="n">
-        <v>110797</v>
+        <v>110804</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>128876850</v>
       </c>
       <c r="B32" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>128877309</v>
       </c>
       <c r="B33" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>128877462</v>
       </c>
       <c r="B34" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>128877664</v>
       </c>
       <c r="B35" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128873652</v>
       </c>
       <c r="B36" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>128875600</v>
       </c>
       <c r="B37" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>128876017</v>
       </c>
       <c r="B38" t="n">
-        <v>110797</v>
+        <v>110804</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>128875778</v>
       </c>
       <c r="B40" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128876585</v>
+        <v>128878172</v>
       </c>
       <c r="B41" t="n">
-        <v>92838</v>
+        <v>110804</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5161,36 +5161,41 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>219711</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5199,13 +5204,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>350632</v>
+        <v>350562</v>
       </c>
       <c r="R41" t="n">
-        <v>6532513</v>
+        <v>6532383</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5239,7 +5244,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
+          <t>Växer relativt rikligt på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5253,7 +5258,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5271,10 +5276,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128878172</v>
+        <v>128876585</v>
       </c>
       <c r="B42" t="n">
-        <v>110797</v>
+        <v>92845</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5282,41 +5287,36 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219711</v>
+        <v>4366</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5325,13 +5325,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>350562</v>
+        <v>350632</v>
       </c>
       <c r="R42" t="n">
-        <v>6532383</v>
+        <v>6532513</v>
       </c>
       <c r="S42" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Växer relativt rikligt på fyndplatsen.</t>
+          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128876816</v>
+        <v>128877087</v>
       </c>
       <c r="B43" t="n">
-        <v>92862</v>
+        <v>100864</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5408,36 +5408,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5446,13 +5437,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>350632</v>
+        <v>350761</v>
       </c>
       <c r="R43" t="n">
-        <v>6532521</v>
+        <v>6532577</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5513,10 +5504,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128877087</v>
+        <v>128876816</v>
       </c>
       <c r="B44" t="n">
-        <v>100857</v>
+        <v>92869</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5524,27 +5515,36 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>350761</v>
+        <v>350632</v>
       </c>
       <c r="R44" t="n">
-        <v>6532577</v>
+        <v>6532521</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>128877974</v>
       </c>
       <c r="B45" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>128864631</v>
       </c>
       <c r="B46" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>128898374</v>
       </c>
       <c r="B47" t="n">
-        <v>91305</v>
+        <v>91312</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128831484</v>
       </c>
       <c r="B3" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128836713</v>
       </c>
       <c r="B4" t="n">
-        <v>92851</v>
+        <v>92853</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>128837146</v>
       </c>
       <c r="B5" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>128829084</v>
       </c>
       <c r="B6" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>128830471</v>
       </c>
       <c r="B7" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128831345</v>
       </c>
       <c r="B8" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128837030</v>
       </c>
       <c r="B9" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>128830810</v>
       </c>
       <c r="B10" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>128831251</v>
       </c>
       <c r="B11" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>128832520</v>
       </c>
       <c r="B12" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>128832131</v>
       </c>
       <c r="B13" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>128864268</v>
       </c>
       <c r="B14" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128864568</v>
       </c>
       <c r="B15" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,10 +2264,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128864191</v>
+        <v>128864345</v>
       </c>
       <c r="B16" t="n">
-        <v>92869</v>
+        <v>92480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2275,26 +2275,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2314,13 +2314,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>350673</v>
+        <v>350592</v>
       </c>
       <c r="R16" t="n">
-        <v>6532521</v>
+        <v>6532382</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2350,11 +2350,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2390,7 +2385,7 @@
         <v>128864417</v>
       </c>
       <c r="B17" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2505,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128864345</v>
+        <v>128864191</v>
       </c>
       <c r="B18" t="n">
-        <v>92478</v>
+        <v>92871</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,26 +2511,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2555,13 +2550,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>350592</v>
+        <v>350673</v>
       </c>
       <c r="R18" t="n">
-        <v>6532382</v>
+        <v>6532521</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2591,6 +2586,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,7 +2626,7 @@
         <v>128863610</v>
       </c>
       <c r="B19" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>128863382</v>
       </c>
       <c r="B20" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>128876148</v>
       </c>
       <c r="B21" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>128878422</v>
       </c>
       <c r="B22" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>128876650</v>
       </c>
       <c r="B23" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3200,10 +3200,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128878114</v>
+        <v>128878002</v>
       </c>
       <c r="B24" t="n">
-        <v>92869</v>
+        <v>100866</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,36 +3211,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3249,10 +3240,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>350572</v>
+        <v>350594</v>
       </c>
       <c r="R24" t="n">
-        <v>6532383</v>
+        <v>6532414</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3287,11 +3278,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Växer delvis ihalv hägring.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3303,7 +3289,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3321,10 +3307,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128874644</v>
+        <v>128875354</v>
       </c>
       <c r="B25" t="n">
-        <v>92869</v>
+        <v>100866</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3332,42 +3318,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>350638</v>
+        <v>350609</v>
       </c>
       <c r="R25" t="n">
-        <v>6532616</v>
+        <v>6532560</v>
       </c>
       <c r="S25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3428,10 +3414,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128878002</v>
+        <v>128878114</v>
       </c>
       <c r="B26" t="n">
-        <v>100864</v>
+        <v>92871</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3439,27 +3425,36 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3468,10 +3463,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>350594</v>
+        <v>350572</v>
       </c>
       <c r="R26" t="n">
-        <v>6532414</v>
+        <v>6532383</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3506,6 +3501,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Växer delvis ihalv hägring.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128875354</v>
+        <v>128874644</v>
       </c>
       <c r="B27" t="n">
-        <v>100864</v>
+        <v>92871</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3546,42 +3546,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långkasen, Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>350609</v>
+        <v>350638</v>
       </c>
       <c r="R27" t="n">
-        <v>6532560</v>
+        <v>6532616</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>128877739</v>
       </c>
       <c r="B28" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128877592</v>
+        <v>128877600</v>
       </c>
       <c r="B29" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3811,24 +3811,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>350717</v>
+        <v>350701</v>
       </c>
       <c r="R29" t="n">
-        <v>6532577</v>
+        <v>6532566</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3858,11 +3853,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3894,10 +3884,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128877600</v>
+        <v>128877592</v>
       </c>
       <c r="B30" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3914,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3932,19 +3922,24 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>350701</v>
+        <v>350717</v>
       </c>
       <c r="R30" t="n">
-        <v>6532566</v>
+        <v>6532577</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3974,6 +3969,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4008,7 +4008,7 @@
         <v>128877139</v>
       </c>
       <c r="B31" t="n">
-        <v>110804</v>
+        <v>110806</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>128876850</v>
       </c>
       <c r="B32" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>128877309</v>
       </c>
       <c r="B33" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4340,10 +4340,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128877462</v>
+        <v>128877664</v>
       </c>
       <c r="B34" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4368,7 +4368,16 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -4380,13 +4389,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>350726</v>
+        <v>350697</v>
       </c>
       <c r="R34" t="n">
-        <v>6532586</v>
+        <v>6532548</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4447,10 +4456,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128877664</v>
+        <v>128877462</v>
       </c>
       <c r="B35" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4475,16 +4484,7 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>350697</v>
+        <v>350726</v>
       </c>
       <c r="R35" t="n">
-        <v>6532548</v>
+        <v>6532586</v>
       </c>
       <c r="S35" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128873652</v>
       </c>
       <c r="B36" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>128875600</v>
       </c>
       <c r="B37" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>128876017</v>
       </c>
       <c r="B38" t="n">
-        <v>110804</v>
+        <v>110806</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>128877867</v>
       </c>
       <c r="B39" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>128875778</v>
       </c>
       <c r="B40" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128878172</v>
+        <v>128876585</v>
       </c>
       <c r="B41" t="n">
-        <v>110804</v>
+        <v>92847</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5161,41 +5161,36 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219711</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5204,13 +5199,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>350562</v>
+        <v>350632</v>
       </c>
       <c r="R41" t="n">
-        <v>6532383</v>
+        <v>6532513</v>
       </c>
       <c r="S41" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5244,7 +5239,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Växer relativt rikligt på fyndplatsen.</t>
+          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5258,7 +5253,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5276,10 +5271,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128876585</v>
+        <v>128878172</v>
       </c>
       <c r="B42" t="n">
-        <v>92845</v>
+        <v>110806</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5287,36 +5282,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>219711</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5325,13 +5325,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>350632</v>
+        <v>350562</v>
       </c>
       <c r="R42" t="n">
-        <v>6532513</v>
+        <v>6532383</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
+          <t>Växer relativt rikligt på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128877087</v>
+        <v>128876816</v>
       </c>
       <c r="B43" t="n">
-        <v>100864</v>
+        <v>92871</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5408,27 +5408,36 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5437,13 +5446,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>350761</v>
+        <v>350632</v>
       </c>
       <c r="R43" t="n">
-        <v>6532577</v>
+        <v>6532521</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5504,10 +5513,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128876816</v>
+        <v>128877087</v>
       </c>
       <c r="B44" t="n">
-        <v>92869</v>
+        <v>100866</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5515,36 +5524,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>350632</v>
+        <v>350761</v>
       </c>
       <c r="R44" t="n">
-        <v>6532521</v>
+        <v>6532577</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>128877974</v>
       </c>
       <c r="B45" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>128864631</v>
       </c>
       <c r="B46" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>128898374</v>
       </c>
       <c r="B47" t="n">
-        <v>91312</v>
+        <v>91314</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -2382,7 +2382,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128864417</v>
+        <v>128864191</v>
       </c>
       <c r="B17" t="n">
         <v>92871</v>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2432,13 +2432,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>350581</v>
+        <v>350673</v>
       </c>
       <c r="R17" t="n">
-        <v>6532373</v>
+        <v>6532521</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2468,6 +2468,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,7 +2505,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128864191</v>
+        <v>128864417</v>
       </c>
       <c r="B18" t="n">
         <v>92871</v>
@@ -2530,7 +2535,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2550,13 +2555,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>350673</v>
+        <v>350581</v>
       </c>
       <c r="R18" t="n">
-        <v>6532521</v>
+        <v>6532373</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2586,11 +2591,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3773,7 +3773,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128877600</v>
+        <v>128877592</v>
       </c>
       <c r="B29" t="n">
         <v>92871</v>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3811,19 +3811,24 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>350701</v>
+        <v>350717</v>
       </c>
       <c r="R29" t="n">
-        <v>6532566</v>
+        <v>6532577</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3853,6 +3858,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3884,7 +3894,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128877592</v>
+        <v>128877600</v>
       </c>
       <c r="B30" t="n">
         <v>92871</v>
@@ -3914,7 +3924,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3922,24 +3932,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>350717</v>
+        <v>350701</v>
       </c>
       <c r="R30" t="n">
-        <v>6532577</v>
+        <v>6532566</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3969,11 +3974,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4340,7 +4340,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128877664</v>
+        <v>128877462</v>
       </c>
       <c r="B34" t="n">
         <v>92871</v>
@@ -4368,16 +4368,7 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -4389,13 +4380,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>350697</v>
+        <v>350726</v>
       </c>
       <c r="R34" t="n">
-        <v>6532548</v>
+        <v>6532586</v>
       </c>
       <c r="S34" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4456,7 +4447,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128877462</v>
+        <v>128877664</v>
       </c>
       <c r="B35" t="n">
         <v>92871</v>
@@ -4484,7 +4475,16 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>350726</v>
+        <v>350697</v>
       </c>
       <c r="R35" t="n">
-        <v>6532586</v>
+        <v>6532548</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -1571,49 +1571,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128830810</v>
+        <v>128831251</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>100866</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1622,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>350667</v>
+        <v>350678</v>
       </c>
       <c r="R10" t="n">
-        <v>6532520</v>
+        <v>6532445</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1657,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1667,12 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:40</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 2 talltitor (ev. flera individer) hördes med lockläten i flerskiktad äldre granskog.</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,7 +1670,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1704,38 +1688,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128831251</v>
+        <v>128830810</v>
       </c>
       <c r="B11" t="n">
-        <v>100866</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1744,13 +1739,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>350678</v>
+        <v>350667</v>
       </c>
       <c r="R11" t="n">
-        <v>6532445</v>
+        <v>6532520</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1779,7 +1774,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,7 +1784,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Minst 2 talltitor (ev. flera individer) hördes med lockläten i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -3414,7 +3414,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128878114</v>
+        <v>128874644</v>
       </c>
       <c r="B26" t="n">
         <v>92871</v>
@@ -3442,16 +3442,7 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -3459,17 +3450,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långkasen, Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>350572</v>
+        <v>350638</v>
       </c>
       <c r="R26" t="n">
-        <v>6532383</v>
+        <v>6532616</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3499,11 +3490,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Växer delvis ihalv hägring.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3535,7 +3521,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128874644</v>
+        <v>128878114</v>
       </c>
       <c r="B27" t="n">
         <v>92871</v>
@@ -3563,7 +3549,16 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -3571,17 +3566,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>350638</v>
+        <v>350572</v>
       </c>
       <c r="R27" t="n">
-        <v>6532616</v>
+        <v>6532383</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3611,6 +3606,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Växer delvis ihalv hägring.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3773,10 +3773,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128877592</v>
+        <v>128877139</v>
       </c>
       <c r="B29" t="n">
-        <v>92871</v>
+        <v>110806</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,36 +3784,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5964</v>
+        <v>219711</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3822,13 +3813,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>350717</v>
+        <v>350754</v>
       </c>
       <c r="R29" t="n">
-        <v>6532577</v>
+        <v>6532572</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3860,11 +3851,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3876,7 +3862,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3894,7 +3880,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128877600</v>
+        <v>128877592</v>
       </c>
       <c r="B30" t="n">
         <v>92871</v>
@@ -3924,7 +3910,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3932,19 +3918,24 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>350701</v>
+        <v>350717</v>
       </c>
       <c r="R30" t="n">
-        <v>6532566</v>
+        <v>6532577</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3974,6 +3965,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4005,10 +4001,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128877139</v>
+        <v>128877600</v>
       </c>
       <c r="B31" t="n">
-        <v>110806</v>
+        <v>92871</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4016,27 +4012,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219711</v>
+        <v>5964</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4045,13 +4045,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>350754</v>
+        <v>350701</v>
       </c>
       <c r="R31" t="n">
-        <v>6532572</v>
+        <v>6532566</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -5150,10 +5150,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128876585</v>
+        <v>128878172</v>
       </c>
       <c r="B41" t="n">
-        <v>92847</v>
+        <v>110806</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5161,36 +5161,41 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>219711</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5199,13 +5204,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>350632</v>
+        <v>350562</v>
       </c>
       <c r="R41" t="n">
-        <v>6532513</v>
+        <v>6532383</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5239,7 +5244,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
+          <t>Växer relativt rikligt på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5253,7 +5258,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5271,10 +5276,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128878172</v>
+        <v>128876585</v>
       </c>
       <c r="B42" t="n">
-        <v>110806</v>
+        <v>92847</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5282,41 +5287,36 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219711</v>
+        <v>4366</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5325,13 +5325,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>350562</v>
+        <v>350632</v>
       </c>
       <c r="R42" t="n">
-        <v>6532383</v>
+        <v>6532513</v>
       </c>
       <c r="S42" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Växer relativt rikligt på fyndplatsen.</t>
+          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128831484</v>
       </c>
       <c r="B3" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128836713</v>
       </c>
       <c r="B4" t="n">
-        <v>92853</v>
+        <v>92839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>128837146</v>
       </c>
       <c r="B5" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>128829084</v>
       </c>
       <c r="B6" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>128830471</v>
       </c>
       <c r="B7" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128837030</v>
       </c>
       <c r="B9" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>128831251</v>
       </c>
       <c r="B10" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>128832520</v>
       </c>
       <c r="B12" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>128832131</v>
       </c>
       <c r="B13" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>128864268</v>
       </c>
       <c r="B14" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128864568</v>
       </c>
       <c r="B15" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,10 +2264,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128864345</v>
+        <v>128864191</v>
       </c>
       <c r="B16" t="n">
-        <v>92480</v>
+        <v>92857</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2275,26 +2275,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2314,13 +2314,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>350592</v>
+        <v>350673</v>
       </c>
       <c r="R16" t="n">
-        <v>6532382</v>
+        <v>6532521</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2350,6 +2350,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128864191</v>
+        <v>128864417</v>
       </c>
       <c r="B17" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2412,7 +2417,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2432,13 +2437,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>350673</v>
+        <v>350581</v>
       </c>
       <c r="R17" t="n">
-        <v>6532521</v>
+        <v>6532373</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2468,11 +2473,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,10 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128864417</v>
+        <v>128864345</v>
       </c>
       <c r="B18" t="n">
-        <v>92871</v>
+        <v>92494</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,21 +2516,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>350581</v>
+        <v>350592</v>
       </c>
       <c r="R18" t="n">
-        <v>6532373</v>
+        <v>6532382</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2626,7 +2626,7 @@
         <v>128863610</v>
       </c>
       <c r="B19" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>128863382</v>
       </c>
       <c r="B20" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>128876148</v>
       </c>
       <c r="B21" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>128878422</v>
       </c>
       <c r="B22" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>128876650</v>
       </c>
       <c r="B23" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3200,10 +3200,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128878002</v>
+        <v>128878114</v>
       </c>
       <c r="B24" t="n">
-        <v>100866</v>
+        <v>92857</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,27 +3211,36 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3240,10 +3249,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>350594</v>
+        <v>350572</v>
       </c>
       <c r="R24" t="n">
-        <v>6532414</v>
+        <v>6532383</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3278,6 +3287,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växer delvis ihalv hägring.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3289,7 +3303,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3307,10 +3321,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128875354</v>
+        <v>128874644</v>
       </c>
       <c r="B25" t="n">
-        <v>100866</v>
+        <v>92857</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3318,42 +3332,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långkasen, Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>350609</v>
+        <v>350638</v>
       </c>
       <c r="R25" t="n">
-        <v>6532560</v>
+        <v>6532616</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3414,10 +3428,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128874644</v>
+        <v>128878002</v>
       </c>
       <c r="B26" t="n">
-        <v>92871</v>
+        <v>100892</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,42 +3439,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>350638</v>
+        <v>350594</v>
       </c>
       <c r="R26" t="n">
-        <v>6532616</v>
+        <v>6532414</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3503,7 +3517,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3521,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128878114</v>
+        <v>128875354</v>
       </c>
       <c r="B27" t="n">
-        <v>92871</v>
+        <v>100892</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3532,36 +3546,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3570,13 +3575,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>350572</v>
+        <v>350609</v>
       </c>
       <c r="R27" t="n">
-        <v>6532383</v>
+        <v>6532560</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3606,11 +3611,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Växer delvis ihalv hägring.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3776,7 +3776,7 @@
         <v>128877139</v>
       </c>
       <c r="B29" t="n">
-        <v>110806</v>
+        <v>110832</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>128877592</v>
       </c>
       <c r="B30" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>128877600</v>
       </c>
       <c r="B31" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>128876850</v>
       </c>
       <c r="B32" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>128877309</v>
       </c>
       <c r="B33" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>128877462</v>
       </c>
       <c r="B34" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>128877664</v>
       </c>
       <c r="B35" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128873652</v>
       </c>
       <c r="B36" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>128875600</v>
       </c>
       <c r="B37" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>128876017</v>
       </c>
       <c r="B38" t="n">
-        <v>110806</v>
+        <v>110832</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>128875778</v>
       </c>
       <c r="B40" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128878172</v>
+        <v>128876585</v>
       </c>
       <c r="B41" t="n">
-        <v>110806</v>
+        <v>92833</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5161,41 +5161,36 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219711</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5204,13 +5199,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>350562</v>
+        <v>350632</v>
       </c>
       <c r="R41" t="n">
-        <v>6532383</v>
+        <v>6532513</v>
       </c>
       <c r="S41" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5244,7 +5239,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Växer relativt rikligt på fyndplatsen.</t>
+          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5258,7 +5253,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5276,10 +5271,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128876585</v>
+        <v>128878172</v>
       </c>
       <c r="B42" t="n">
-        <v>92847</v>
+        <v>110832</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5287,36 +5282,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>219711</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5325,13 +5325,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>350632</v>
+        <v>350562</v>
       </c>
       <c r="R42" t="n">
-        <v>6532513</v>
+        <v>6532383</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
+          <t>Växer relativt rikligt på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128876816</v>
+        <v>128877087</v>
       </c>
       <c r="B43" t="n">
-        <v>92871</v>
+        <v>100892</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5408,36 +5408,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5446,13 +5437,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>350632</v>
+        <v>350761</v>
       </c>
       <c r="R43" t="n">
-        <v>6532521</v>
+        <v>6532577</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5513,10 +5504,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128877087</v>
+        <v>128876816</v>
       </c>
       <c r="B44" t="n">
-        <v>100866</v>
+        <v>92857</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5524,27 +5515,36 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>350761</v>
+        <v>350632</v>
       </c>
       <c r="R44" t="n">
-        <v>6532577</v>
+        <v>6532521</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>128877974</v>
       </c>
       <c r="B45" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>128864631</v>
       </c>
       <c r="B46" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>128898374</v>
       </c>
       <c r="B47" t="n">
-        <v>91314</v>
+        <v>91313</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128831484</v>
       </c>
       <c r="B3" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128836713</v>
       </c>
       <c r="B4" t="n">
-        <v>92839</v>
+        <v>92840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>128837146</v>
       </c>
       <c r="B5" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>128829084</v>
       </c>
       <c r="B6" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>128830471</v>
       </c>
       <c r="B7" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128837030</v>
       </c>
       <c r="B9" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,38 +1571,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128831251</v>
+        <v>128830810</v>
       </c>
       <c r="B10" t="n">
-        <v>100892</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1611,13 +1622,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>350678</v>
+        <v>350667</v>
       </c>
       <c r="R10" t="n">
-        <v>6532445</v>
+        <v>6532520</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1657,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1667,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 2 talltitor (ev. flera individer) hördes med lockläten i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,7 +1686,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1688,49 +1704,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128830810</v>
+        <v>128831251</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>100894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1739,13 +1744,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>350667</v>
+        <v>350678</v>
       </c>
       <c r="R11" t="n">
-        <v>6532520</v>
+        <v>6532445</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,7 +1779,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1784,12 +1789,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:40</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Minst 2 talltitor (ev. flera individer) hördes med lockläten i flerskiktad äldre granskog.</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1824,7 +1824,7 @@
         <v>128832520</v>
       </c>
       <c r="B12" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>128832131</v>
       </c>
       <c r="B13" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>128864268</v>
       </c>
       <c r="B14" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128864568</v>
       </c>
       <c r="B15" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,10 +2264,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128864191</v>
+        <v>128864417</v>
       </c>
       <c r="B16" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2314,13 +2314,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>350673</v>
+        <v>350581</v>
       </c>
       <c r="R16" t="n">
-        <v>6532521</v>
+        <v>6532373</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2350,11 +2350,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,10 +2382,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128864417</v>
+        <v>128864345</v>
       </c>
       <c r="B17" t="n">
-        <v>92857</v>
+        <v>92495</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2398,21 +2393,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2437,10 +2432,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>350581</v>
+        <v>350592</v>
       </c>
       <c r="R17" t="n">
-        <v>6532373</v>
+        <v>6532382</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2505,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128864345</v>
+        <v>128864191</v>
       </c>
       <c r="B18" t="n">
-        <v>92494</v>
+        <v>92858</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,26 +2511,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2555,13 +2550,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>350592</v>
+        <v>350673</v>
       </c>
       <c r="R18" t="n">
-        <v>6532382</v>
+        <v>6532521</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2591,6 +2586,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,7 +2626,7 @@
         <v>128863610</v>
       </c>
       <c r="B19" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>128863382</v>
       </c>
       <c r="B20" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>128876148</v>
       </c>
       <c r="B21" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>128878422</v>
       </c>
       <c r="B22" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>128876650</v>
       </c>
       <c r="B23" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>128878114</v>
       </c>
       <c r="B24" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>128874644</v>
       </c>
       <c r="B25" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3428,10 +3428,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128878002</v>
+        <v>128875354</v>
       </c>
       <c r="B26" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3468,13 +3468,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>350594</v>
+        <v>350609</v>
       </c>
       <c r="R26" t="n">
-        <v>6532414</v>
+        <v>6532560</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128875354</v>
+        <v>128878002</v>
       </c>
       <c r="B27" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3575,13 +3575,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>350609</v>
+        <v>350594</v>
       </c>
       <c r="R27" t="n">
-        <v>6532560</v>
+        <v>6532414</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3776,7 +3776,7 @@
         <v>128877139</v>
       </c>
       <c r="B29" t="n">
-        <v>110832</v>
+        <v>110834</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>128877592</v>
       </c>
       <c r="B30" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>128877600</v>
       </c>
       <c r="B31" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>128876850</v>
       </c>
       <c r="B32" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>128877309</v>
       </c>
       <c r="B33" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>128877462</v>
       </c>
       <c r="B34" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>128877664</v>
       </c>
       <c r="B35" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128873652</v>
       </c>
       <c r="B36" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>128875600</v>
       </c>
       <c r="B37" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>128876017</v>
       </c>
       <c r="B38" t="n">
-        <v>110832</v>
+        <v>110834</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>128875778</v>
       </c>
       <c r="B40" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128876585</v>
+        <v>128878172</v>
       </c>
       <c r="B41" t="n">
-        <v>92833</v>
+        <v>110834</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5161,36 +5161,41 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>219711</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5199,13 +5204,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>350632</v>
+        <v>350562</v>
       </c>
       <c r="R41" t="n">
-        <v>6532513</v>
+        <v>6532383</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5239,7 +5244,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
+          <t>Växer relativt rikligt på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5253,7 +5258,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5271,10 +5276,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128878172</v>
+        <v>128876585</v>
       </c>
       <c r="B42" t="n">
-        <v>110832</v>
+        <v>92834</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5282,41 +5287,36 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219711</v>
+        <v>4366</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5325,13 +5325,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>350562</v>
+        <v>350632</v>
       </c>
       <c r="R42" t="n">
-        <v>6532383</v>
+        <v>6532513</v>
       </c>
       <c r="S42" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Växer relativt rikligt på fyndplatsen.</t>
+          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128877087</v>
+        <v>128876816</v>
       </c>
       <c r="B43" t="n">
-        <v>100892</v>
+        <v>92858</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5408,27 +5408,36 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5437,13 +5446,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>350761</v>
+        <v>350632</v>
       </c>
       <c r="R43" t="n">
-        <v>6532577</v>
+        <v>6532521</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5504,10 +5513,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128876816</v>
+        <v>128877087</v>
       </c>
       <c r="B44" t="n">
-        <v>92857</v>
+        <v>100894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5515,36 +5524,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>350632</v>
+        <v>350761</v>
       </c>
       <c r="R44" t="n">
-        <v>6532521</v>
+        <v>6532577</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>128877974</v>
       </c>
       <c r="B45" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>128864631</v>
       </c>
       <c r="B46" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128831484</v>
       </c>
       <c r="B3" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,44 +883,36 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128836713</v>
+        <v>128837146</v>
       </c>
       <c r="B4" t="n">
-        <v>92840</v>
+        <v>92858</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -933,13 +925,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>350682</v>
+        <v>350556</v>
       </c>
       <c r="R4" t="n">
-        <v>6532579</v>
+        <v>6532301</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,7 +965,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar (minst 25 st) med tydlig kumarin/anisdoft som växer i avlångt stråk/häxring i äldre granskog med stor dimensionspridning hos stammarna.</t>
+          <t>Växer här relativt allmänt i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,7 +980,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1006,36 +998,44 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128837146</v>
+        <v>128836713</v>
       </c>
       <c r="B5" t="n">
-        <v>92858</v>
+        <v>92840</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>350556</v>
+        <v>350682</v>
       </c>
       <c r="R5" t="n">
-        <v>6532301</v>
+        <v>6532579</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer här relativt allmänt i äldre barrskog.</t>
+          <t>Gott om fruktkroppar (minst 25 st) med tydlig kumarin/anisdoft som växer i avlångt stråk/häxring i äldre granskog med stor dimensionspridning hos stammarna.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1124,7 +1124,7 @@
         <v>128829084</v>
       </c>
       <c r="B6" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>128830471</v>
       </c>
       <c r="B7" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1571,49 +1571,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128830810</v>
+        <v>128831251</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>100895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1622,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>350667</v>
+        <v>350678</v>
       </c>
       <c r="R10" t="n">
-        <v>6532520</v>
+        <v>6532445</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1657,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1667,12 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:40</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 2 talltitor (ev. flera individer) hördes med lockläten i flerskiktad äldre granskog.</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,7 +1670,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1704,38 +1688,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128831251</v>
+        <v>128830810</v>
       </c>
       <c r="B11" t="n">
-        <v>100894</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1744,13 +1739,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>350678</v>
+        <v>350667</v>
       </c>
       <c r="R11" t="n">
-        <v>6532445</v>
+        <v>6532520</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1779,7 +1774,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,7 +1784,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Minst 2 talltitor (ev. flera individer) hördes med lockläten i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1824,7 +1824,7 @@
         <v>128832520</v>
       </c>
       <c r="B12" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>128832131</v>
       </c>
       <c r="B13" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128864568</v>
       </c>
       <c r="B15" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,10 +2264,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128864417</v>
+        <v>128864345</v>
       </c>
       <c r="B16" t="n">
-        <v>92858</v>
+        <v>92495</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>350581</v>
+        <v>350592</v>
       </c>
       <c r="R16" t="n">
-        <v>6532373</v>
+        <v>6532382</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128864345</v>
+        <v>128864191</v>
       </c>
       <c r="B17" t="n">
-        <v>92495</v>
+        <v>92858</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2393,26 +2393,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2432,13 +2432,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>350592</v>
+        <v>350673</v>
       </c>
       <c r="R17" t="n">
-        <v>6532382</v>
+        <v>6532521</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2468,6 +2468,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,7 +2505,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128864191</v>
+        <v>128864417</v>
       </c>
       <c r="B18" t="n">
         <v>92858</v>
@@ -2530,7 +2535,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2550,13 +2555,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>350673</v>
+        <v>350581</v>
       </c>
       <c r="R18" t="n">
-        <v>6532521</v>
+        <v>6532373</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2586,11 +2591,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Minst 5 fruktkroppar delvis i häxring-formation.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3200,10 +3200,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128878114</v>
+        <v>128875354</v>
       </c>
       <c r="B24" t="n">
-        <v>92858</v>
+        <v>100895</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,36 +3211,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3249,13 +3240,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>350572</v>
+        <v>350609</v>
       </c>
       <c r="R24" t="n">
-        <v>6532383</v>
+        <v>6532560</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3285,11 +3276,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Växer delvis ihalv hägring.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3321,10 +3307,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128874644</v>
+        <v>128878002</v>
       </c>
       <c r="B25" t="n">
-        <v>92858</v>
+        <v>100895</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3332,42 +3318,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>350638</v>
+        <v>350594</v>
       </c>
       <c r="R25" t="n">
-        <v>6532616</v>
+        <v>6532414</v>
       </c>
       <c r="S25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3410,7 +3396,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3428,10 +3414,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128875354</v>
+        <v>128878114</v>
       </c>
       <c r="B26" t="n">
-        <v>100894</v>
+        <v>92858</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3439,27 +3425,36 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3468,13 +3463,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>350609</v>
+        <v>350572</v>
       </c>
       <c r="R26" t="n">
-        <v>6532560</v>
+        <v>6532383</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3504,6 +3499,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Växer delvis ihalv hägring.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128878002</v>
+        <v>128874644</v>
       </c>
       <c r="B27" t="n">
-        <v>100894</v>
+        <v>92858</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3546,42 +3546,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långkasen, Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>350594</v>
+        <v>350638</v>
       </c>
       <c r="R27" t="n">
-        <v>6532414</v>
+        <v>6532616</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3776,7 +3776,7 @@
         <v>128877139</v>
       </c>
       <c r="B29" t="n">
-        <v>110834</v>
+        <v>110835</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>128876850</v>
       </c>
       <c r="B32" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128873652</v>
       </c>
       <c r="B36" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>128876017</v>
       </c>
       <c r="B38" t="n">
-        <v>110834</v>
+        <v>110835</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>128875778</v>
       </c>
       <c r="B40" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>128878172</v>
       </c>
       <c r="B41" t="n">
-        <v>110834</v>
+        <v>110835</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>128877087</v>
       </c>
       <c r="B44" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -2038,7 +2038,7 @@
         <v>128864268</v>
       </c>
       <c r="B14" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128864568</v>
       </c>
       <c r="B15" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>128864345</v>
       </c>
       <c r="B16" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>128864191</v>
       </c>
       <c r="B17" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>128864417</v>
       </c>
       <c r="B18" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>128863610</v>
       </c>
       <c r="B19" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>128863382</v>
       </c>
       <c r="B20" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>128876148</v>
       </c>
       <c r="B21" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>128878422</v>
       </c>
       <c r="B22" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>128876650</v>
       </c>
       <c r="B23" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3200,10 +3200,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128875354</v>
+        <v>128878114</v>
       </c>
       <c r="B24" t="n">
-        <v>100895</v>
+        <v>92861</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,27 +3211,36 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3240,13 +3249,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>350609</v>
+        <v>350572</v>
       </c>
       <c r="R24" t="n">
-        <v>6532560</v>
+        <v>6532383</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3276,6 +3285,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växer delvis ihalv hägring.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3307,10 +3321,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128878002</v>
+        <v>128874644</v>
       </c>
       <c r="B25" t="n">
-        <v>100895</v>
+        <v>92861</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3318,42 +3332,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långkasen, Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>350594</v>
+        <v>350638</v>
       </c>
       <c r="R25" t="n">
-        <v>6532414</v>
+        <v>6532616</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3396,7 +3410,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3414,10 +3428,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128878114</v>
+        <v>128878002</v>
       </c>
       <c r="B26" t="n">
-        <v>92858</v>
+        <v>100899</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,36 +3439,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3463,10 +3468,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>350572</v>
+        <v>350594</v>
       </c>
       <c r="R26" t="n">
-        <v>6532383</v>
+        <v>6532414</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3501,11 +3506,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Växer delvis ihalv hägring.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128874644</v>
+        <v>128875354</v>
       </c>
       <c r="B27" t="n">
-        <v>92858</v>
+        <v>100899</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3546,42 +3546,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>350638</v>
+        <v>350609</v>
       </c>
       <c r="R27" t="n">
-        <v>6532616</v>
+        <v>6532560</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128877139</v>
+        <v>128877592</v>
       </c>
       <c r="B29" t="n">
-        <v>110835</v>
+        <v>92861</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,27 +3784,36 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219711</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3813,13 +3822,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>350754</v>
+        <v>350717</v>
       </c>
       <c r="R29" t="n">
-        <v>6532572</v>
+        <v>6532577</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3851,6 +3860,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3862,7 +3876,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3880,10 +3894,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128877592</v>
+        <v>128877600</v>
       </c>
       <c r="B30" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3910,7 +3924,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3918,24 +3932,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långkasen, Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>350717</v>
+        <v>350701</v>
       </c>
       <c r="R30" t="n">
-        <v>6532577</v>
+        <v>6532566</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3965,11 +3974,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 24 fruktkroppar i halv häxring intill flera granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4001,10 +4005,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128877600</v>
+        <v>128877139</v>
       </c>
       <c r="B31" t="n">
-        <v>92858</v>
+        <v>110839</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4012,31 +4016,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5964</v>
+        <v>219711</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4045,13 +4045,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>350701</v>
+        <v>350754</v>
       </c>
       <c r="R31" t="n">
-        <v>6532566</v>
+        <v>6532572</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4115,7 +4115,7 @@
         <v>128876850</v>
       </c>
       <c r="B32" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>128877309</v>
       </c>
       <c r="B33" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>128877462</v>
       </c>
       <c r="B34" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>128877664</v>
       </c>
       <c r="B35" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>128873652</v>
       </c>
       <c r="B36" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>128875600</v>
       </c>
       <c r="B37" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>128876017</v>
       </c>
       <c r="B38" t="n">
-        <v>110835</v>
+        <v>110839</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>128875778</v>
       </c>
       <c r="B40" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>128878172</v>
       </c>
       <c r="B41" t="n">
-        <v>110835</v>
+        <v>110839</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>128876585</v>
       </c>
       <c r="B42" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128876816</v>
+        <v>128877087</v>
       </c>
       <c r="B43" t="n">
-        <v>92858</v>
+        <v>100899</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5408,36 +5408,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5446,13 +5437,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>350632</v>
+        <v>350761</v>
       </c>
       <c r="R43" t="n">
-        <v>6532521</v>
+        <v>6532577</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5513,10 +5504,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128877087</v>
+        <v>128876816</v>
       </c>
       <c r="B44" t="n">
-        <v>100895</v>
+        <v>92861</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5524,27 +5515,36 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>350761</v>
+        <v>350632</v>
       </c>
       <c r="R44" t="n">
-        <v>6532577</v>
+        <v>6532521</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>128877974</v>
       </c>
       <c r="B45" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>128864631</v>
       </c>
       <c r="B46" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>128898374</v>
       </c>
       <c r="B47" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -5150,10 +5150,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128878172</v>
+        <v>128876585</v>
       </c>
       <c r="B41" t="n">
-        <v>110839</v>
+        <v>92837</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5161,41 +5161,36 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219711</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5204,13 +5199,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>350562</v>
+        <v>350632</v>
       </c>
       <c r="R41" t="n">
-        <v>6532383</v>
+        <v>6532513</v>
       </c>
       <c r="S41" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5244,7 +5239,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Växer relativt rikligt på fyndplatsen.</t>
+          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5258,7 +5253,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5276,10 +5271,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128876585</v>
+        <v>128878172</v>
       </c>
       <c r="B42" t="n">
-        <v>92837</v>
+        <v>110839</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5287,36 +5282,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>219711</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5325,13 +5325,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>350632</v>
+        <v>350562</v>
       </c>
       <c r="R42" t="n">
-        <v>6532513</v>
+        <v>6532383</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Växer intill fjällig taggsvamp och blåsippa i äldre flerskiktad granskog.</t>
+          <t>Växer relativt rikligt på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128877087</v>
+        <v>128876816</v>
       </c>
       <c r="B43" t="n">
-        <v>100899</v>
+        <v>92861</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5408,27 +5408,36 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5437,13 +5446,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>350761</v>
+        <v>350632</v>
       </c>
       <c r="R43" t="n">
-        <v>6532577</v>
+        <v>6532521</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5504,10 +5513,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128876816</v>
+        <v>128877087</v>
       </c>
       <c r="B44" t="n">
-        <v>92861</v>
+        <v>100899</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5515,36 +5524,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>350632</v>
+        <v>350761</v>
       </c>
       <c r="R44" t="n">
-        <v>6532521</v>
+        <v>6532577</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -5623,7 +5623,7 @@
         <v>128877974</v>
       </c>
       <c r="B45" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>128864631</v>
       </c>
       <c r="B46" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>128898374</v>
       </c>
       <c r="B47" t="n">
-        <v>91316</v>
+        <v>91318</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5975,6 +5975,142 @@
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129602112</v>
+      </c>
+      <c r="B48" t="n">
+        <v>110858</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Källan, Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>350772</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6532666</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt med blad av sårläka och gott om fröställningar på ca 2 m2 yta strax under kraftledningen.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5977,10 +5977,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129602112</v>
+        <v>129624004</v>
       </c>
       <c r="B48" t="n">
-        <v>110858</v>
+        <v>100916</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5988,38 +5988,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6027,14 +6020,14 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>350772</v>
+        <v>350639</v>
       </c>
       <c r="R48" t="n">
-        <v>6532666</v>
+        <v>6532442</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6066,7 +6059,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6076,12 +6069,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rikligt med blad av sårläka och gott om fröställningar på ca 2 m2 yta strax under kraftledningen.</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6090,12 +6078,13 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6110,6 +6099,4499 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129610899</v>
+      </c>
+      <c r="B49" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>350713</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6532571</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129602112</v>
+      </c>
+      <c r="B50" t="n">
+        <v>110858</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Källan, Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>350772</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6532666</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt med blad av sårläka och gott om fröställningar på ca 2 m2 yta strax under kraftledningen.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129624719</v>
+      </c>
+      <c r="B51" t="n">
+        <v>92508</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>350681</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6532544</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129621322</v>
+      </c>
+      <c r="B52" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>350500</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6532306</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129624476</v>
+      </c>
+      <c r="B53" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>350698</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6532504</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129610901</v>
+      </c>
+      <c r="B54" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>350704</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6532603</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129626202</v>
+      </c>
+      <c r="B55" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>350886</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6532805</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129618156</v>
+      </c>
+      <c r="B56" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>350773</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6532648</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129620583</v>
+      </c>
+      <c r="B57" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>350764</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6532613</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129620964</v>
+      </c>
+      <c r="B58" t="n">
+        <v>110858</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>350563</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6532299</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Sårläka förekommer relativt allmänt i skogsbeståndet där fyndplatsen ligger och arten har troligen funnits i området mycket länge.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129621973</v>
+      </c>
+      <c r="B59" t="n">
+        <v>110858</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>350525</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6532325</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt med vintergröna blad av sårläka på fyndplatsen.</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med stor dimensionsspridning bland stammarna.</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129617882</v>
+      </c>
+      <c r="B60" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>350809</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6532638</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129625617</v>
+      </c>
+      <c r="B61" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>350820</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6532734</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129624940</v>
+      </c>
+      <c r="B62" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>350786</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6532704</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129622093</v>
+      </c>
+      <c r="B63" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>350525</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6532325</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129623862</v>
+      </c>
+      <c r="B64" t="n">
+        <v>110858</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>350602</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6532393</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns intill en stig där det även växer blåsippa och örnbräken.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129621217</v>
+      </c>
+      <c r="B65" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>350534</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6532292</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129610906</v>
+      </c>
+      <c r="B66" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>350706</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6532674</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129610910</v>
+      </c>
+      <c r="B67" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>350756</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6532668</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129622188</v>
+      </c>
+      <c r="B68" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>350455</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6532318</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På fyndplatsen finns rikligt med blåsippa.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129620774</v>
+      </c>
+      <c r="B69" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>350751</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6532634</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129617827</v>
+      </c>
+      <c r="B70" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>350825</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6532643</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129621165</v>
+      </c>
+      <c r="B71" t="n">
+        <v>110858</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>350534</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6532292</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129624665</v>
+      </c>
+      <c r="B72" t="n">
+        <v>110858</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>350682</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6532570</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129610909</v>
+      </c>
+      <c r="B73" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>350738</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6532692</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129620970</v>
+      </c>
+      <c r="B74" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>350563</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6532299</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129610894</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Långkasen, Tisselskog, Dls</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>350716</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6532562</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Minst 1 talltita hördes men ev. var det två individer. Fyndplatsen finns i äldre flerskiktad granskog.</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Äldre granskog med olikåldriga träd med stor dimensionsspridning. Inslag av partier med tall och enstaka björk, lönn, rönn, sälg och ek.</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129624906</v>
+      </c>
+      <c r="B76" t="n">
+        <v>110858</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>350786</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6532704</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Sårläka förekommer allmänt i skogsbeståndet omkring fyndplatsen.</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129623874</v>
+      </c>
+      <c r="B77" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>350602</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6532393</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>129622650</v>
+      </c>
+      <c r="B78" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>350557</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6532357</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>129620718</v>
+      </c>
+      <c r="B79" t="n">
+        <v>110858</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>350751</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6532634</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>129624198</v>
+      </c>
+      <c r="B80" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Långkasen, Dls</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>350658</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6532492</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>129610904</v>
+      </c>
+      <c r="B81" t="n">
+        <v>110858</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>350697</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6532630</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Gott om blad av sårläka på fyndplatsen.</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>129610907</v>
+      </c>
+      <c r="B82" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>350725</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6532715</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129620537</v>
+      </c>
+      <c r="B83" t="n">
+        <v>110858</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>350764</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6532613</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Sårläka finns relativt allmänt i skogsbeståndet omkring fyndplatsen.</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>129624823</v>
+      </c>
+      <c r="B84" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Källan, Dls</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>350814</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6532706</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -6223,10 +6223,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129602112</v>
+        <v>129624719</v>
       </c>
       <c r="B50" t="n">
-        <v>110858</v>
+        <v>92508</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6234,53 +6234,41 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219711</v>
+        <v>4769</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>350772</v>
+        <v>350681</v>
       </c>
       <c r="R50" t="n">
-        <v>6532666</v>
+        <v>6532544</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6312,7 +6300,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6322,12 +6310,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt med blad av sårläka och gott om fröställningar på ca 2 m2 yta strax under kraftledningen.</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6336,12 +6319,13 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6359,10 +6343,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129624719</v>
+        <v>129602112</v>
       </c>
       <c r="B51" t="n">
-        <v>92508</v>
+        <v>110858</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6370,41 +6354,53 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4769</v>
+        <v>219711</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>350681</v>
+        <v>350772</v>
       </c>
       <c r="R51" t="n">
-        <v>6532544</v>
+        <v>6532666</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6436,7 +6432,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6446,7 +6442,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt med blad av sårläka och gott om fröställningar på ca 2 m2 yta strax under kraftledningen.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6455,13 +6456,12 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6725,7 +6725,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129610901</v>
+        <v>129626202</v>
       </c>
       <c r="B54" t="n">
         <v>100916</v>
@@ -6761,17 +6761,21 @@
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>350704</v>
+        <v>350886</v>
       </c>
       <c r="R54" t="n">
-        <v>6532603</v>
+        <v>6532805</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6803,7 +6807,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6813,7 +6817,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6828,7 +6832,7 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6846,7 +6850,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129626202</v>
+        <v>129610901</v>
       </c>
       <c r="B55" t="n">
         <v>100916</v>
@@ -6882,21 +6886,17 @@
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>350886</v>
+        <v>350704</v>
       </c>
       <c r="R55" t="n">
-        <v>6532805</v>
+        <v>6532603</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6971,7 +6971,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129618156</v>
+        <v>129620583</v>
       </c>
       <c r="B56" t="n">
         <v>100916</v>
@@ -7014,10 +7014,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>350773</v>
+        <v>350764</v>
       </c>
       <c r="R56" t="n">
-        <v>6532648</v>
+        <v>6532613</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7092,7 +7092,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129620583</v>
+        <v>129618156</v>
       </c>
       <c r="B57" t="n">
         <v>100916</v>
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>350764</v>
+        <v>350773</v>
       </c>
       <c r="R57" t="n">
-        <v>6532613</v>
+        <v>6532648</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7718,7 +7718,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129624940</v>
+        <v>129622093</v>
       </c>
       <c r="B62" t="n">
         <v>100916</v>
@@ -7754,21 +7754,17 @@
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>350786</v>
+        <v>350525</v>
       </c>
       <c r="R62" t="n">
-        <v>6532704</v>
+        <v>6532325</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7800,7 +7796,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7810,7 +7806,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7843,7 +7839,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129622093</v>
+        <v>129624940</v>
       </c>
       <c r="B63" t="n">
         <v>100916</v>
@@ -7879,17 +7875,21 @@
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>350525</v>
+        <v>350786</v>
       </c>
       <c r="R63" t="n">
-        <v>6532325</v>
+        <v>6532704</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8728,10 +8728,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129617827</v>
+        <v>129621165</v>
       </c>
       <c r="B70" t="n">
-        <v>100916</v>
+        <v>110858</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8739,21 +8739,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8764,21 +8764,17 @@
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>350825</v>
+        <v>350534</v>
       </c>
       <c r="R70" t="n">
-        <v>6532643</v>
+        <v>6532292</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8810,7 +8806,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8820,7 +8816,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8853,10 +8849,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129621165</v>
+        <v>129610909</v>
       </c>
       <c r="B71" t="n">
-        <v>110858</v>
+        <v>100916</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8864,21 +8860,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8892,14 +8888,14 @@
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>350534</v>
+        <v>350738</v>
       </c>
       <c r="R71" t="n">
-        <v>6532292</v>
+        <v>6532692</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8929,19 +8925,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8956,7 +8942,7 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8974,10 +8960,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129624665</v>
+        <v>129617827</v>
       </c>
       <c r="B72" t="n">
-        <v>110858</v>
+        <v>100916</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8985,21 +8971,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9017,14 +9003,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>350682</v>
+        <v>350825</v>
       </c>
       <c r="R72" t="n">
-        <v>6532570</v>
+        <v>6532643</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9056,7 +9042,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9066,7 +9052,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9081,7 +9067,7 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9099,10 +9085,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129610909</v>
+        <v>129624665</v>
       </c>
       <c r="B73" t="n">
-        <v>100916</v>
+        <v>110858</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9110,21 +9096,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9135,17 +9121,21 @@
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>350738</v>
+        <v>350682</v>
       </c>
       <c r="R73" t="n">
-        <v>6532692</v>
+        <v>6532570</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9175,9 +9165,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9603,10 +9603,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129623874</v>
+        <v>129620718</v>
       </c>
       <c r="B77" t="n">
-        <v>100916</v>
+        <v>110858</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9614,21 +9614,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9646,14 +9646,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>350602</v>
+        <v>350751</v>
       </c>
       <c r="R77" t="n">
-        <v>6532393</v>
+        <v>6532634</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9728,7 +9728,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129622650</v>
+        <v>129623874</v>
       </c>
       <c r="B78" t="n">
         <v>100916</v>
@@ -9775,10 +9775,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>350557</v>
+        <v>350602</v>
       </c>
       <c r="R78" t="n">
-        <v>6532357</v>
+        <v>6532393</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9853,10 +9853,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129620718</v>
+        <v>129622650</v>
       </c>
       <c r="B79" t="n">
-        <v>110858</v>
+        <v>100916</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9864,21 +9864,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9896,14 +9896,14 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>350751</v>
+        <v>350557</v>
       </c>
       <c r="R79" t="n">
-        <v>6532634</v>
+        <v>6532357</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9978,10 +9978,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129624198</v>
+        <v>129610904</v>
       </c>
       <c r="B80" t="n">
-        <v>100916</v>
+        <v>110858</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9989,21 +9989,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10021,14 +10021,14 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>350658</v>
+        <v>350697</v>
       </c>
       <c r="R80" t="n">
-        <v>6532492</v>
+        <v>6532630</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10070,7 +10070,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Gott om blad av sårläka på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10103,7 +10108,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129610904</v>
+        <v>129620537</v>
       </c>
       <c r="B81" t="n">
         <v>110858</v>
@@ -10139,21 +10144,17 @@
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>350697</v>
+        <v>350764</v>
       </c>
       <c r="R81" t="n">
-        <v>6532630</v>
+        <v>6532613</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10185,7 +10186,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10195,12 +10196,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Gott om blad av sårläka på fyndplatsen.</t>
+          <t>Sårläka finns relativt allmänt i skogsbeståndet omkring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10348,10 +10349,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129620537</v>
+        <v>129624198</v>
       </c>
       <c r="B83" t="n">
-        <v>110858</v>
+        <v>100916</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10359,21 +10360,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10384,17 +10385,21 @@
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>350764</v>
+        <v>350658</v>
       </c>
       <c r="R83" t="n">
-        <v>6532613</v>
+        <v>6532492</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10426,7 +10431,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10436,12 +10441,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Sårläka finns relativt allmänt i skogsbeståndet omkring fyndplatsen.</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -6223,10 +6223,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129624719</v>
+        <v>129602112</v>
       </c>
       <c r="B50" t="n">
-        <v>92508</v>
+        <v>110858</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6234,41 +6234,53 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4769</v>
+        <v>219711</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>350681</v>
+        <v>350772</v>
       </c>
       <c r="R50" t="n">
-        <v>6532544</v>
+        <v>6532666</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6300,7 +6312,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6310,7 +6322,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt med blad av sårläka och gott om fröställningar på ca 2 m2 yta strax under kraftledningen.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6319,13 +6336,12 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6343,10 +6359,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129602112</v>
+        <v>129624719</v>
       </c>
       <c r="B51" t="n">
-        <v>110858</v>
+        <v>92508</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6354,53 +6370,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219711</v>
+        <v>4769</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>350772</v>
+        <v>350681</v>
       </c>
       <c r="R51" t="n">
-        <v>6532666</v>
+        <v>6532544</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6432,7 +6436,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6442,12 +6446,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt med blad av sårläka och gott om fröställningar på ca 2 m2 yta strax under kraftledningen.</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6456,12 +6455,13 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7213,10 +7213,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129620964</v>
+        <v>129617882</v>
       </c>
       <c r="B58" t="n">
-        <v>110858</v>
+        <v>100916</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7224,21 +7224,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7256,14 +7256,14 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>350563</v>
+        <v>350809</v>
       </c>
       <c r="R58" t="n">
-        <v>6532299</v>
+        <v>6532638</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7293,24 +7293,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Sårläka förekommer relativt allmänt i skogsbeståndet där fyndplatsen ligger och arten har troligen funnits i området mycket länge.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7325,7 +7310,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7343,7 +7328,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129621973</v>
+        <v>129620964</v>
       </c>
       <c r="B59" t="n">
         <v>110858</v>
@@ -7390,10 +7375,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>350525</v>
+        <v>350563</v>
       </c>
       <c r="R59" t="n">
-        <v>6532325</v>
+        <v>6532299</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7425,7 +7410,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7435,12 +7420,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Rikligt med vintergröna blad av sårläka på fyndplatsen.</t>
+          <t>Sårläka förekommer relativt allmänt i skogsbeståndet där fyndplatsen ligger och arten har troligen funnits i området mycket länge.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7456,11 +7441,6 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med stor dimensionsspridning bland stammarna.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7478,10 +7458,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129617882</v>
+        <v>129621973</v>
       </c>
       <c r="B60" t="n">
-        <v>100916</v>
+        <v>110858</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7489,21 +7469,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7521,14 +7501,14 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>350809</v>
+        <v>350525</v>
       </c>
       <c r="R60" t="n">
-        <v>6532638</v>
+        <v>6532325</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7558,9 +7538,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt med vintergröna blad av sårläka på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7575,7 +7570,12 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med stor dimensionsspridning bland stammarna.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8728,10 +8728,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129621165</v>
+        <v>129610909</v>
       </c>
       <c r="B70" t="n">
-        <v>110858</v>
+        <v>100916</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8739,21 +8739,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8767,14 +8767,14 @@
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>350534</v>
+        <v>350738</v>
       </c>
       <c r="R70" t="n">
-        <v>6532292</v>
+        <v>6532692</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8804,19 +8804,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8831,7 +8821,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8849,7 +8839,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129610909</v>
+        <v>129617827</v>
       </c>
       <c r="B71" t="n">
         <v>100916</v>
@@ -8885,17 +8875,21 @@
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>350738</v>
+        <v>350825</v>
       </c>
       <c r="R71" t="n">
-        <v>6532692</v>
+        <v>6532643</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8925,9 +8919,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8942,7 +8946,7 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8960,10 +8964,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129617827</v>
+        <v>129624665</v>
       </c>
       <c r="B72" t="n">
-        <v>100916</v>
+        <v>110858</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8971,21 +8975,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9003,14 +9007,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>350825</v>
+        <v>350682</v>
       </c>
       <c r="R72" t="n">
-        <v>6532643</v>
+        <v>6532570</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9042,7 +9046,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9052,7 +9056,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9067,7 +9071,7 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9085,7 +9089,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129624665</v>
+        <v>129621165</v>
       </c>
       <c r="B73" t="n">
         <v>110858</v>
@@ -9121,21 +9125,17 @@
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>350682</v>
+        <v>350534</v>
       </c>
       <c r="R73" t="n">
-        <v>6532570</v>
+        <v>6532292</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9167,7 +9167,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9210,42 +9210,46 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129620970</v>
+        <v>129610894</v>
       </c>
       <c r="B74" t="n">
-        <v>100916</v>
+        <v>57887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9253,17 +9257,17 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Långkasen, Tisselskog, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>350563</v>
+        <v>350716</v>
       </c>
       <c r="R74" t="n">
-        <v>6532299</v>
+        <v>6532562</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9292,7 +9296,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9302,7 +9306,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Minst 1 talltita hördes men ev. var det två individer. Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9311,13 +9320,17 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Äldre granskog med olikåldriga träd med stor dimensionsspridning. Inslag av partier med tall och enstaka björk, lönn, rönn, sälg och ek.</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9335,46 +9348,42 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129610894</v>
+        <v>129620970</v>
       </c>
       <c r="B75" t="n">
-        <v>57887</v>
+        <v>100916</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9382,17 +9391,17 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Långkasen, Tisselskog, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>350716</v>
+        <v>350563</v>
       </c>
       <c r="R75" t="n">
-        <v>6532562</v>
+        <v>6532299</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9421,7 +9430,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9431,12 +9440,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Minst 1 talltita hördes men ev. var det två individer. Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9445,17 +9449,13 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>Äldre granskog med olikåldriga träd med stor dimensionsspridning. Inslag av partier med tall och enstaka björk, lönn, rönn, sälg och ek.</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129620718</v>
+        <v>129623874</v>
       </c>
       <c r="B77" t="n">
-        <v>110858</v>
+        <v>100916</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9614,21 +9614,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9646,14 +9646,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>350751</v>
+        <v>350602</v>
       </c>
       <c r="R77" t="n">
-        <v>6532634</v>
+        <v>6532393</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9728,7 +9728,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129623874</v>
+        <v>129622650</v>
       </c>
       <c r="B78" t="n">
         <v>100916</v>
@@ -9775,10 +9775,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>350602</v>
+        <v>350557</v>
       </c>
       <c r="R78" t="n">
-        <v>6532393</v>
+        <v>6532357</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9853,10 +9853,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129622650</v>
+        <v>129620718</v>
       </c>
       <c r="B79" t="n">
-        <v>100916</v>
+        <v>110858</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9864,21 +9864,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9896,14 +9896,14 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>350557</v>
+        <v>350751</v>
       </c>
       <c r="R79" t="n">
-        <v>6532357</v>
+        <v>6532634</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9978,10 +9978,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129610904</v>
+        <v>129610907</v>
       </c>
       <c r="B80" t="n">
-        <v>110858</v>
+        <v>100916</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9989,21 +9989,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10025,10 +10025,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>350697</v>
+        <v>350725</v>
       </c>
       <c r="R80" t="n">
-        <v>6532630</v>
+        <v>6532715</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10058,24 +10058,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Gott om blad av sårläka på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10108,10 +10093,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129620537</v>
+        <v>129624198</v>
       </c>
       <c r="B81" t="n">
-        <v>110858</v>
+        <v>100916</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10119,21 +10104,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10144,17 +10129,21 @@
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>350764</v>
+        <v>350658</v>
       </c>
       <c r="R81" t="n">
-        <v>6532613</v>
+        <v>6532492</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10186,7 +10175,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10196,12 +10185,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Sårläka finns relativt allmänt i skogsbeståndet omkring fyndplatsen.</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10234,10 +10218,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129610907</v>
+        <v>129610904</v>
       </c>
       <c r="B82" t="n">
-        <v>100916</v>
+        <v>110858</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10245,21 +10229,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10281,10 +10265,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>350725</v>
+        <v>350697</v>
       </c>
       <c r="R82" t="n">
-        <v>6532715</v>
+        <v>6532630</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10314,9 +10298,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Gott om blad av sårläka på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10349,10 +10348,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129624198</v>
+        <v>129620537</v>
       </c>
       <c r="B83" t="n">
-        <v>100916</v>
+        <v>110858</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10360,21 +10359,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10385,21 +10384,17 @@
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>350658</v>
+        <v>350764</v>
       </c>
       <c r="R83" t="n">
-        <v>6532492</v>
+        <v>6532613</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10431,7 +10426,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10441,7 +10436,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Sårläka finns relativt allmänt i skogsbeståndet omkring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -5977,7 +5977,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129624004</v>
+        <v>129610899</v>
       </c>
       <c r="B48" t="n">
         <v>100916</v>
@@ -6013,21 +6013,17 @@
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>350639</v>
+        <v>350713</v>
       </c>
       <c r="R48" t="n">
-        <v>6532442</v>
+        <v>6532571</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6059,7 +6055,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6069,7 +6065,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6102,7 +6098,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129610899</v>
+        <v>129624004</v>
       </c>
       <c r="B49" t="n">
         <v>100916</v>
@@ -6138,17 +6134,21 @@
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>350713</v>
+        <v>350639</v>
       </c>
       <c r="R49" t="n">
-        <v>6532571</v>
+        <v>6532442</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6223,10 +6223,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129602112</v>
+        <v>129624719</v>
       </c>
       <c r="B50" t="n">
-        <v>110858</v>
+        <v>92508</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6234,53 +6234,41 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219711</v>
+        <v>4769</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>350772</v>
+        <v>350681</v>
       </c>
       <c r="R50" t="n">
-        <v>6532666</v>
+        <v>6532544</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6312,7 +6300,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6322,12 +6310,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt med blad av sårläka och gott om fröställningar på ca 2 m2 yta strax under kraftledningen.</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6336,12 +6319,13 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6359,10 +6343,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129624719</v>
+        <v>129602112</v>
       </c>
       <c r="B51" t="n">
-        <v>92508</v>
+        <v>110858</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6370,41 +6354,53 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4769</v>
+        <v>219711</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>350681</v>
+        <v>350772</v>
       </c>
       <c r="R51" t="n">
-        <v>6532544</v>
+        <v>6532666</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6436,7 +6432,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6446,7 +6442,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt med blad av sårläka och gott om fröställningar på ca 2 m2 yta strax under kraftledningen.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6455,13 +6456,12 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6479,7 +6479,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129621322</v>
+        <v>129626202</v>
       </c>
       <c r="B52" t="n">
         <v>100916</v>
@@ -6515,17 +6515,21 @@
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>350500</v>
+        <v>350886</v>
       </c>
       <c r="R52" t="n">
-        <v>6532306</v>
+        <v>6532805</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6557,7 +6561,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6567,7 +6571,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6600,7 +6604,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129624476</v>
+        <v>129621322</v>
       </c>
       <c r="B53" t="n">
         <v>100916</v>
@@ -6636,21 +6640,17 @@
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>350698</v>
+        <v>350500</v>
       </c>
       <c r="R53" t="n">
-        <v>6532504</v>
+        <v>6532306</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6725,7 +6725,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129626202</v>
+        <v>129624476</v>
       </c>
       <c r="B54" t="n">
         <v>100916</v>
@@ -6768,14 +6768,14 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>350886</v>
+        <v>350698</v>
       </c>
       <c r="R54" t="n">
-        <v>6532805</v>
+        <v>6532504</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6971,7 +6971,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129620583</v>
+        <v>129618156</v>
       </c>
       <c r="B56" t="n">
         <v>100916</v>
@@ -7014,10 +7014,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>350764</v>
+        <v>350773</v>
       </c>
       <c r="R56" t="n">
-        <v>6532613</v>
+        <v>6532648</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7092,7 +7092,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129618156</v>
+        <v>129620583</v>
       </c>
       <c r="B57" t="n">
         <v>100916</v>
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>350773</v>
+        <v>350764</v>
       </c>
       <c r="R57" t="n">
-        <v>6532648</v>
+        <v>6532613</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7213,10 +7213,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129617882</v>
+        <v>129620964</v>
       </c>
       <c r="B58" t="n">
-        <v>100916</v>
+        <v>110858</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7224,21 +7224,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7256,14 +7256,14 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>350809</v>
+        <v>350563</v>
       </c>
       <c r="R58" t="n">
-        <v>6532638</v>
+        <v>6532299</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7293,9 +7293,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Sårläka förekommer relativt allmänt i skogsbeståndet där fyndplatsen ligger och arten har troligen funnits i området mycket länge.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7310,7 +7325,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7328,7 +7343,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129620964</v>
+        <v>129621973</v>
       </c>
       <c r="B59" t="n">
         <v>110858</v>
@@ -7375,10 +7390,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>350563</v>
+        <v>350525</v>
       </c>
       <c r="R59" t="n">
-        <v>6532299</v>
+        <v>6532325</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7410,7 +7425,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7420,12 +7435,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Sårläka förekommer relativt allmänt i skogsbeståndet där fyndplatsen ligger och arten har troligen funnits i området mycket länge.</t>
+          <t>Rikligt med vintergröna blad av sårläka på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7441,6 +7456,11 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med stor dimensionsspridning bland stammarna.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7458,10 +7478,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129621973</v>
+        <v>129617882</v>
       </c>
       <c r="B60" t="n">
-        <v>110858</v>
+        <v>100916</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7469,21 +7489,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7501,14 +7521,14 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>350525</v>
+        <v>350809</v>
       </c>
       <c r="R60" t="n">
-        <v>6532325</v>
+        <v>6532638</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7538,24 +7558,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt med vintergröna blad av sårläka på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7570,12 +7575,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med stor dimensionsspridning bland stammarna.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8728,10 +8728,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129610909</v>
+        <v>129624665</v>
       </c>
       <c r="B70" t="n">
-        <v>100916</v>
+        <v>110858</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8739,21 +8739,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8764,17 +8764,21 @@
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>350738</v>
+        <v>350682</v>
       </c>
       <c r="R70" t="n">
-        <v>6532692</v>
+        <v>6532570</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8804,9 +8808,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8839,10 +8853,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129617827</v>
+        <v>129621165</v>
       </c>
       <c r="B71" t="n">
-        <v>100916</v>
+        <v>110858</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8850,21 +8864,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8875,21 +8889,17 @@
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>350825</v>
+        <v>350534</v>
       </c>
       <c r="R71" t="n">
-        <v>6532643</v>
+        <v>6532292</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8921,7 +8931,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8931,7 +8941,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8964,10 +8974,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129624665</v>
+        <v>129617827</v>
       </c>
       <c r="B72" t="n">
-        <v>110858</v>
+        <v>100916</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8975,21 +8985,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9007,14 +9017,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>350682</v>
+        <v>350825</v>
       </c>
       <c r="R72" t="n">
-        <v>6532570</v>
+        <v>6532643</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9046,7 +9056,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9056,7 +9066,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9071,7 +9081,7 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9089,10 +9099,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129621165</v>
+        <v>129610909</v>
       </c>
       <c r="B73" t="n">
-        <v>110858</v>
+        <v>100916</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9100,21 +9110,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9128,14 +9138,14 @@
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>350534</v>
+        <v>350738</v>
       </c>
       <c r="R73" t="n">
-        <v>6532292</v>
+        <v>6532692</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9165,19 +9175,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9210,46 +9210,42 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129610894</v>
+        <v>129624906</v>
       </c>
       <c r="B74" t="n">
-        <v>57887</v>
+        <v>110858</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103021</v>
+        <v>219711</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9257,17 +9253,17 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Långkasen, Tisselskog, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>350716</v>
+        <v>350786</v>
       </c>
       <c r="R74" t="n">
-        <v>6532562</v>
+        <v>6532704</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9296,7 +9292,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9306,12 +9302,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 1 talltita hördes men ev. var det två individer. Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>Sårläka förekommer allmänt i skogsbeståndet omkring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9320,17 +9316,13 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>Äldre granskog med olikåldriga träd med stor dimensionsspridning. Inslag av partier med tall och enstaka björk, lönn, rönn, sälg och ek.</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9348,42 +9340,46 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129620970</v>
+        <v>129610894</v>
       </c>
       <c r="B75" t="n">
-        <v>100916</v>
+        <v>57887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9391,17 +9387,17 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Långkasen, Tisselskog, Dls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>350563</v>
+        <v>350716</v>
       </c>
       <c r="R75" t="n">
-        <v>6532299</v>
+        <v>6532562</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9430,7 +9426,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9440,7 +9436,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Minst 1 talltita hördes men ev. var det två individer. Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9449,13 +9450,17 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Äldre granskog med olikåldriga träd med stor dimensionsspridning. Inslag av partier med tall och enstaka björk, lönn, rönn, sälg och ek.</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9473,10 +9478,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129624906</v>
+        <v>129620970</v>
       </c>
       <c r="B76" t="n">
-        <v>110858</v>
+        <v>100916</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9484,21 +9489,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9516,14 +9521,14 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>350786</v>
+        <v>350563</v>
       </c>
       <c r="R76" t="n">
-        <v>6532704</v>
+        <v>6532299</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9555,7 +9560,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9565,12 +9570,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Sårläka förekommer allmänt i skogsbeståndet omkring fyndplatsen.</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10093,10 +10093,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129624198</v>
+        <v>129610904</v>
       </c>
       <c r="B81" t="n">
-        <v>100916</v>
+        <v>110858</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10104,21 +10104,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10136,14 +10136,14 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>350658</v>
+        <v>350697</v>
       </c>
       <c r="R81" t="n">
-        <v>6532492</v>
+        <v>6532630</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10185,7 +10185,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Gott om blad av sårläka på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10218,7 +10223,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129610904</v>
+        <v>129620537</v>
       </c>
       <c r="B82" t="n">
         <v>110858</v>
@@ -10254,21 +10259,17 @@
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>350697</v>
+        <v>350764</v>
       </c>
       <c r="R82" t="n">
-        <v>6532630</v>
+        <v>6532613</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10300,7 +10301,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10310,12 +10311,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Gott om blad av sårläka på fyndplatsen.</t>
+          <t>Sårläka finns relativt allmänt i skogsbeståndet omkring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10348,10 +10349,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129620537</v>
+        <v>129624198</v>
       </c>
       <c r="B83" t="n">
-        <v>110858</v>
+        <v>100916</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10359,21 +10360,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10384,17 +10385,21 @@
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>350764</v>
+        <v>350658</v>
       </c>
       <c r="R83" t="n">
-        <v>6532613</v>
+        <v>6532492</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10426,7 +10431,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10436,12 +10441,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Sårläka finns relativt allmänt i skogsbeståndet omkring fyndplatsen.</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -5977,10 +5977,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129610899</v>
+        <v>129624004</v>
       </c>
       <c r="B48" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6013,17 +6013,21 @@
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>350713</v>
+        <v>350639</v>
       </c>
       <c r="R48" t="n">
-        <v>6532571</v>
+        <v>6532442</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6055,7 +6059,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6065,7 +6069,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6098,10 +6102,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129624004</v>
+        <v>129610899</v>
       </c>
       <c r="B49" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6134,21 +6138,17 @@
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>350639</v>
+        <v>350713</v>
       </c>
       <c r="R49" t="n">
-        <v>6532442</v>
+        <v>6532571</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6226,7 +6226,7 @@
         <v>129624719</v>
       </c>
       <c r="B50" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>129602112</v>
       </c>
       <c r="B51" t="n">
-        <v>110858</v>
+        <v>110887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6479,10 +6479,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129626202</v>
+        <v>129621322</v>
       </c>
       <c r="B52" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6515,21 +6515,17 @@
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>350886</v>
+        <v>350500</v>
       </c>
       <c r="R52" t="n">
-        <v>6532805</v>
+        <v>6532306</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6561,7 +6557,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6571,7 +6567,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6604,10 +6600,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129621322</v>
+        <v>129624476</v>
       </c>
       <c r="B53" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6640,17 +6636,21 @@
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>350500</v>
+        <v>350698</v>
       </c>
       <c r="R53" t="n">
-        <v>6532306</v>
+        <v>6532504</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6725,10 +6725,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129624476</v>
+        <v>129626202</v>
       </c>
       <c r="B54" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6768,14 +6768,14 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>350698</v>
+        <v>350886</v>
       </c>
       <c r="R54" t="n">
-        <v>6532504</v>
+        <v>6532805</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6853,7 +6853,7 @@
         <v>129610901</v>
       </c>
       <c r="B55" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6971,10 +6971,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129618156</v>
+        <v>129620583</v>
       </c>
       <c r="B56" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7014,10 +7014,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>350773</v>
+        <v>350764</v>
       </c>
       <c r="R56" t="n">
-        <v>6532648</v>
+        <v>6532613</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7092,10 +7092,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129620583</v>
+        <v>129618156</v>
       </c>
       <c r="B57" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>350764</v>
+        <v>350773</v>
       </c>
       <c r="R57" t="n">
-        <v>6532613</v>
+        <v>6532648</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7216,7 +7216,7 @@
         <v>129620964</v>
       </c>
       <c r="B58" t="n">
-        <v>110858</v>
+        <v>110887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>129621973</v>
       </c>
       <c r="B59" t="n">
-        <v>110858</v>
+        <v>110887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>129617882</v>
       </c>
       <c r="B60" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>129625617</v>
       </c>
       <c r="B61" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>129622093</v>
       </c>
       <c r="B62" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>129624940</v>
       </c>
       <c r="B63" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>129623862</v>
       </c>
       <c r="B64" t="n">
-        <v>110858</v>
+        <v>110887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>129621217</v>
       </c>
       <c r="B65" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>129610906</v>
       </c>
       <c r="B66" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>129610910</v>
       </c>
       <c r="B67" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>129622188</v>
       </c>
       <c r="B68" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>129620774</v>
       </c>
       <c r="B69" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8728,10 +8728,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129624665</v>
+        <v>129617827</v>
       </c>
       <c r="B70" t="n">
-        <v>110858</v>
+        <v>100945</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8739,21 +8739,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8771,14 +8771,14 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>350682</v>
+        <v>350825</v>
       </c>
       <c r="R70" t="n">
-        <v>6532570</v>
+        <v>6532643</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8810,7 +8810,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8853,10 +8853,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129621165</v>
+        <v>129624665</v>
       </c>
       <c r="B71" t="n">
-        <v>110858</v>
+        <v>110887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8889,17 +8889,21 @@
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>350534</v>
+        <v>350682</v>
       </c>
       <c r="R71" t="n">
-        <v>6532292</v>
+        <v>6532570</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8931,7 +8935,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8941,7 +8945,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8956,7 +8960,7 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8974,10 +8978,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129617827</v>
+        <v>129621165</v>
       </c>
       <c r="B72" t="n">
-        <v>100916</v>
+        <v>110887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8985,21 +8989,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9010,21 +9014,17 @@
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>350825</v>
+        <v>350534</v>
       </c>
       <c r="R72" t="n">
-        <v>6532643</v>
+        <v>6532292</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9102,7 +9102,7 @@
         <v>129610909</v>
       </c>
       <c r="B73" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9210,42 +9210,46 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129624906</v>
+        <v>129610894</v>
       </c>
       <c r="B74" t="n">
-        <v>110858</v>
+        <v>57890</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219711</v>
+        <v>103021</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9253,17 +9257,17 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Tisselskog, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>350786</v>
+        <v>350716</v>
       </c>
       <c r="R74" t="n">
-        <v>6532704</v>
+        <v>6532562</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9292,7 +9296,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9302,12 +9306,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Sårläka förekommer allmänt i skogsbeståndet omkring fyndplatsen.</t>
+          <t>Minst 1 talltita hördes men ev. var det två individer. Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9316,13 +9320,17 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Äldre granskog med olikåldriga träd med stor dimensionsspridning. Inslag av partier med tall och enstaka björk, lönn, rönn, sälg och ek.</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9340,46 +9348,42 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129610894</v>
+        <v>129624906</v>
       </c>
       <c r="B75" t="n">
-        <v>57887</v>
+        <v>110887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>219711</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9387,17 +9391,17 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Långkasen, Tisselskog, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>350716</v>
+        <v>350786</v>
       </c>
       <c r="R75" t="n">
-        <v>6532562</v>
+        <v>6532704</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9426,7 +9430,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9436,12 +9440,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst 1 talltita hördes men ev. var det två individer. Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>Sårläka förekommer allmänt i skogsbeståndet omkring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9450,17 +9454,13 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>Äldre granskog med olikåldriga träd med stor dimensionsspridning. Inslag av partier med tall och enstaka björk, lönn, rönn, sälg och ek.</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9481,7 +9481,7 @@
         <v>129620970</v>
       </c>
       <c r="B76" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>129623874</v>
       </c>
       <c r="B77" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>129622650</v>
       </c>
       <c r="B78" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>129620718</v>
       </c>
       <c r="B79" t="n">
-        <v>110858</v>
+        <v>110887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>129610907</v>
       </c>
       <c r="B80" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10093,10 +10093,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129610904</v>
+        <v>129624198</v>
       </c>
       <c r="B81" t="n">
-        <v>110858</v>
+        <v>100945</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10104,21 +10104,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10136,14 +10136,14 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>350697</v>
+        <v>350658</v>
       </c>
       <c r="R81" t="n">
-        <v>6532630</v>
+        <v>6532492</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10185,12 +10185,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Gott om blad av sårläka på fyndplatsen.</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10223,10 +10218,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129620537</v>
+        <v>129610904</v>
       </c>
       <c r="B82" t="n">
-        <v>110858</v>
+        <v>110887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10259,17 +10254,21 @@
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>350764</v>
+        <v>350697</v>
       </c>
       <c r="R82" t="n">
-        <v>6532613</v>
+        <v>6532630</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10301,7 +10300,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10311,12 +10310,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Sårläka finns relativt allmänt i skogsbeståndet omkring fyndplatsen.</t>
+          <t>Gott om blad av sårläka på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10349,10 +10348,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129624198</v>
+        <v>129620537</v>
       </c>
       <c r="B83" t="n">
-        <v>100916</v>
+        <v>110887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10360,21 +10359,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10385,21 +10384,17 @@
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>350658</v>
+        <v>350764</v>
       </c>
       <c r="R83" t="n">
-        <v>6532492</v>
+        <v>6532613</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10431,7 +10426,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10441,7 +10436,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Sårläka finns relativt allmänt i skogsbeståndet omkring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10477,7 +10477,7 @@
         <v>129624823</v>
       </c>
       <c r="B84" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -9348,10 +9348,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129624906</v>
+        <v>129620970</v>
       </c>
       <c r="B75" t="n">
-        <v>110887</v>
+        <v>100945</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9359,21 +9359,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9391,14 +9391,14 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>350786</v>
+        <v>350563</v>
       </c>
       <c r="R75" t="n">
-        <v>6532704</v>
+        <v>6532299</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9440,12 +9440,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Sårläka förekommer allmänt i skogsbeståndet omkring fyndplatsen.</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9478,10 +9473,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129620970</v>
+        <v>129624906</v>
       </c>
       <c r="B76" t="n">
-        <v>100945</v>
+        <v>110887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9489,21 +9484,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9521,14 +9516,14 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>350563</v>
+        <v>350786</v>
       </c>
       <c r="R76" t="n">
-        <v>6532299</v>
+        <v>6532704</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9560,7 +9555,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9570,7 +9565,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Sårläka förekommer allmänt i skogsbeståndet omkring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9603,10 +9603,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129623874</v>
+        <v>129620718</v>
       </c>
       <c r="B77" t="n">
-        <v>100945</v>
+        <v>110887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9614,21 +9614,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9646,14 +9646,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>350602</v>
+        <v>350751</v>
       </c>
       <c r="R77" t="n">
-        <v>6532393</v>
+        <v>6532634</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9728,7 +9728,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129622650</v>
+        <v>129623874</v>
       </c>
       <c r="B78" t="n">
         <v>100945</v>
@@ -9775,10 +9775,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>350557</v>
+        <v>350602</v>
       </c>
       <c r="R78" t="n">
-        <v>6532357</v>
+        <v>6532393</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9853,10 +9853,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129620718</v>
+        <v>129622650</v>
       </c>
       <c r="B79" t="n">
-        <v>110887</v>
+        <v>100945</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9864,21 +9864,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9896,14 +9896,14 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>350751</v>
+        <v>350557</v>
       </c>
       <c r="R79" t="n">
-        <v>6532634</v>
+        <v>6532357</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9978,10 +9978,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129610907</v>
+        <v>129610904</v>
       </c>
       <c r="B80" t="n">
-        <v>100945</v>
+        <v>110887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9989,21 +9989,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10025,10 +10025,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>350725</v>
+        <v>350697</v>
       </c>
       <c r="R80" t="n">
-        <v>6532715</v>
+        <v>6532630</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10058,9 +10058,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Gott om blad av sårläka på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10093,10 +10108,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129624198</v>
+        <v>129620537</v>
       </c>
       <c r="B81" t="n">
-        <v>100945</v>
+        <v>110887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10104,21 +10119,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10129,21 +10144,17 @@
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>350658</v>
+        <v>350764</v>
       </c>
       <c r="R81" t="n">
-        <v>6532492</v>
+        <v>6532613</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10175,7 +10186,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10185,7 +10196,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Sårläka finns relativt allmänt i skogsbeståndet omkring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10218,10 +10234,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129610904</v>
+        <v>129610907</v>
       </c>
       <c r="B82" t="n">
-        <v>110887</v>
+        <v>100945</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10229,21 +10245,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10265,10 +10281,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>350697</v>
+        <v>350725</v>
       </c>
       <c r="R82" t="n">
-        <v>6532630</v>
+        <v>6532715</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10298,24 +10314,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Gott om blad av sårläka på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10348,10 +10349,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129620537</v>
+        <v>129624198</v>
       </c>
       <c r="B83" t="n">
-        <v>110887</v>
+        <v>100945</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10359,21 +10360,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10384,17 +10385,21 @@
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>350764</v>
+        <v>350658</v>
       </c>
       <c r="R83" t="n">
-        <v>6532613</v>
+        <v>6532492</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10426,7 +10431,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10436,12 +10441,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Sårläka finns relativt allmänt i skogsbeståndet omkring fyndplatsen.</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -5980,7 +5980,7 @@
         <v>129624004</v>
       </c>
       <c r="B48" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>129610899</v>
       </c>
       <c r="B49" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6223,10 +6223,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129624719</v>
+        <v>129602112</v>
       </c>
       <c r="B50" t="n">
-        <v>92536</v>
+        <v>110899</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6234,41 +6234,53 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4769</v>
+        <v>219711</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>350681</v>
+        <v>350772</v>
       </c>
       <c r="R50" t="n">
-        <v>6532544</v>
+        <v>6532666</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6300,7 +6312,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6310,7 +6322,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt med blad av sårläka och gott om fröställningar på ca 2 m2 yta strax under kraftledningen.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6319,13 +6336,12 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6343,10 +6359,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129602112</v>
+        <v>129624719</v>
       </c>
       <c r="B51" t="n">
-        <v>110887</v>
+        <v>92542</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6354,53 +6370,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219711</v>
+        <v>4769</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>350772</v>
+        <v>350681</v>
       </c>
       <c r="R51" t="n">
-        <v>6532666</v>
+        <v>6532544</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6432,7 +6436,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6442,12 +6446,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt med blad av sårläka och gott om fröställningar på ca 2 m2 yta strax under kraftledningen.</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6456,12 +6455,13 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6482,7 +6482,7 @@
         <v>129621322</v>
       </c>
       <c r="B52" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>129624476</v>
       </c>
       <c r="B53" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>129626202</v>
       </c>
       <c r="B54" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>129610901</v>
       </c>
       <c r="B55" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>129620583</v>
       </c>
       <c r="B56" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>129618156</v>
       </c>
       <c r="B57" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>129620964</v>
       </c>
       <c r="B58" t="n">
-        <v>110887</v>
+        <v>110899</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7343,10 +7343,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129621973</v>
+        <v>129617882</v>
       </c>
       <c r="B59" t="n">
-        <v>110887</v>
+        <v>100957</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7354,21 +7354,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7386,14 +7386,14 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>350525</v>
+        <v>350809</v>
       </c>
       <c r="R59" t="n">
-        <v>6532325</v>
+        <v>6532638</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7423,24 +7423,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Rikligt med vintergröna blad av sårläka på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7455,12 +7440,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med stor dimensionsspridning bland stammarna.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7478,10 +7458,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129617882</v>
+        <v>129621973</v>
       </c>
       <c r="B60" t="n">
-        <v>100945</v>
+        <v>110899</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7489,21 +7469,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7521,14 +7501,14 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>350809</v>
+        <v>350525</v>
       </c>
       <c r="R60" t="n">
-        <v>6532638</v>
+        <v>6532325</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7558,9 +7538,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt med vintergröna blad av sårläka på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7575,7 +7570,12 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med stor dimensionsspridning bland stammarna.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7596,7 +7596,7 @@
         <v>129625617</v>
       </c>
       <c r="B61" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>129622093</v>
       </c>
       <c r="B62" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>129624940</v>
       </c>
       <c r="B63" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>129623862</v>
       </c>
       <c r="B64" t="n">
-        <v>110887</v>
+        <v>110899</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>129621217</v>
       </c>
       <c r="B65" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>129610906</v>
       </c>
       <c r="B66" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>129610910</v>
       </c>
       <c r="B67" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>129622188</v>
       </c>
       <c r="B68" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>129620774</v>
       </c>
       <c r="B69" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8728,10 +8728,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129617827</v>
+        <v>129610909</v>
       </c>
       <c r="B70" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8764,21 +8764,17 @@
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>350825</v>
+        <v>350738</v>
       </c>
       <c r="R70" t="n">
-        <v>6532643</v>
+        <v>6532692</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8808,19 +8804,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>13:47</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8835,7 +8821,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8853,10 +8839,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129624665</v>
+        <v>129617827</v>
       </c>
       <c r="B71" t="n">
-        <v>110887</v>
+        <v>100957</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8864,21 +8850,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8896,14 +8882,14 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>350682</v>
+        <v>350825</v>
       </c>
       <c r="R71" t="n">
-        <v>6532570</v>
+        <v>6532643</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8935,7 +8921,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8945,7 +8931,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8960,7 +8946,7 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8978,10 +8964,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129621165</v>
+        <v>129624665</v>
       </c>
       <c r="B72" t="n">
-        <v>110887</v>
+        <v>110899</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9014,17 +9000,21 @@
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>350534</v>
+        <v>350682</v>
       </c>
       <c r="R72" t="n">
-        <v>6532292</v>
+        <v>6532570</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9056,7 +9046,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9066,7 +9056,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9081,7 +9071,7 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9099,10 +9089,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129610909</v>
+        <v>129621165</v>
       </c>
       <c r="B73" t="n">
-        <v>100945</v>
+        <v>110899</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9110,21 +9100,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9138,14 +9128,14 @@
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>350738</v>
+        <v>350534</v>
       </c>
       <c r="R73" t="n">
-        <v>6532692</v>
+        <v>6532292</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9175,9 +9165,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9213,7 +9213,7 @@
         <v>129610894</v>
       </c>
       <c r="B74" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>129620970</v>
       </c>
       <c r="B75" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>129624906</v>
       </c>
       <c r="B76" t="n">
-        <v>110887</v>
+        <v>110899</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129620718</v>
+        <v>129623874</v>
       </c>
       <c r="B77" t="n">
-        <v>110887</v>
+        <v>100957</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9614,21 +9614,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9646,14 +9646,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>350751</v>
+        <v>350602</v>
       </c>
       <c r="R77" t="n">
-        <v>6532634</v>
+        <v>6532393</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9728,10 +9728,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129623874</v>
+        <v>129622650</v>
       </c>
       <c r="B78" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9775,10 +9775,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>350602</v>
+        <v>350557</v>
       </c>
       <c r="R78" t="n">
-        <v>6532393</v>
+        <v>6532357</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9853,10 +9853,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129622650</v>
+        <v>129620718</v>
       </c>
       <c r="B79" t="n">
-        <v>100945</v>
+        <v>110899</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9864,21 +9864,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9896,14 +9896,14 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>350557</v>
+        <v>350751</v>
       </c>
       <c r="R79" t="n">
-        <v>6532357</v>
+        <v>6532634</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9978,10 +9978,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129610904</v>
+        <v>129610907</v>
       </c>
       <c r="B80" t="n">
-        <v>110887</v>
+        <v>100957</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9989,21 +9989,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10025,10 +10025,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>350697</v>
+        <v>350725</v>
       </c>
       <c r="R80" t="n">
-        <v>6532630</v>
+        <v>6532715</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10058,24 +10058,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Gott om blad av sårläka på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10108,10 +10093,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129620537</v>
+        <v>129624198</v>
       </c>
       <c r="B81" t="n">
-        <v>110887</v>
+        <v>100957</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10119,21 +10104,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10144,17 +10129,21 @@
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>350764</v>
+        <v>350658</v>
       </c>
       <c r="R81" t="n">
-        <v>6532613</v>
+        <v>6532492</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10186,7 +10175,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10196,12 +10185,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Sårläka finns relativt allmänt i skogsbeståndet omkring fyndplatsen.</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10234,10 +10218,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129610907</v>
+        <v>129610904</v>
       </c>
       <c r="B82" t="n">
-        <v>100945</v>
+        <v>110899</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10245,21 +10229,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10281,10 +10265,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>350725</v>
+        <v>350697</v>
       </c>
       <c r="R82" t="n">
-        <v>6532715</v>
+        <v>6532630</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10314,9 +10298,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Gott om blad av sårläka på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10349,10 +10348,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129624198</v>
+        <v>129620537</v>
       </c>
       <c r="B83" t="n">
-        <v>100945</v>
+        <v>110899</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10360,21 +10359,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10385,21 +10384,17 @@
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>350658</v>
+        <v>350764</v>
       </c>
       <c r="R83" t="n">
-        <v>6532492</v>
+        <v>6532613</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10431,7 +10426,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10441,7 +10436,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Sårläka finns relativt allmänt i skogsbeståndet omkring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10477,7 +10477,7 @@
         <v>129624823</v>
       </c>
       <c r="B84" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -5980,7 +5980,7 @@
         <v>129624004</v>
       </c>
       <c r="B48" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>129610899</v>
       </c>
       <c r="B49" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>129602112</v>
       </c>
       <c r="B50" t="n">
-        <v>110899</v>
+        <v>110900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>129624719</v>
       </c>
       <c r="B51" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>129621322</v>
       </c>
       <c r="B52" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>129624476</v>
       </c>
       <c r="B53" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>129626202</v>
       </c>
       <c r="B54" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>129610901</v>
       </c>
       <c r="B55" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>129620583</v>
       </c>
       <c r="B56" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>129618156</v>
       </c>
       <c r="B57" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7213,10 +7213,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129620964</v>
+        <v>129617882</v>
       </c>
       <c r="B58" t="n">
-        <v>110899</v>
+        <v>100958</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7224,21 +7224,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7256,14 +7256,14 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>350563</v>
+        <v>350809</v>
       </c>
       <c r="R58" t="n">
-        <v>6532299</v>
+        <v>6532638</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7293,24 +7293,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Sårläka förekommer relativt allmänt i skogsbeståndet där fyndplatsen ligger och arten har troligen funnits i området mycket länge.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7325,7 +7310,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7343,10 +7328,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129617882</v>
+        <v>129620964</v>
       </c>
       <c r="B59" t="n">
-        <v>100957</v>
+        <v>110900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7354,21 +7339,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7386,14 +7371,14 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>350809</v>
+        <v>350563</v>
       </c>
       <c r="R59" t="n">
-        <v>6532638</v>
+        <v>6532299</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7423,9 +7408,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Sårläka förekommer relativt allmänt i skogsbeståndet där fyndplatsen ligger och arten har troligen funnits i området mycket länge.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7461,7 +7461,7 @@
         <v>129621973</v>
       </c>
       <c r="B60" t="n">
-        <v>110899</v>
+        <v>110900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>129625617</v>
       </c>
       <c r="B61" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>129622093</v>
       </c>
       <c r="B62" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>129624940</v>
       </c>
       <c r="B63" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>129623862</v>
       </c>
       <c r="B64" t="n">
-        <v>110899</v>
+        <v>110900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>129621217</v>
       </c>
       <c r="B65" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>129610906</v>
       </c>
       <c r="B66" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>129610910</v>
       </c>
       <c r="B67" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>129622188</v>
       </c>
       <c r="B68" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>129620774</v>
       </c>
       <c r="B69" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8728,10 +8728,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129610909</v>
+        <v>129624665</v>
       </c>
       <c r="B70" t="n">
-        <v>100957</v>
+        <v>110900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8739,21 +8739,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8764,17 +8764,21 @@
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>350738</v>
+        <v>350682</v>
       </c>
       <c r="R70" t="n">
-        <v>6532692</v>
+        <v>6532570</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8804,9 +8808,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8839,10 +8853,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129617827</v>
+        <v>129621165</v>
       </c>
       <c r="B71" t="n">
-        <v>100957</v>
+        <v>110900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8850,21 +8864,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8875,21 +8889,17 @@
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>350825</v>
+        <v>350534</v>
       </c>
       <c r="R71" t="n">
-        <v>6532643</v>
+        <v>6532292</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8921,7 +8931,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8931,7 +8941,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8964,10 +8974,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129624665</v>
+        <v>129610909</v>
       </c>
       <c r="B72" t="n">
-        <v>110899</v>
+        <v>100958</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8975,21 +8985,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9000,21 +9010,17 @@
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>350682</v>
+        <v>350738</v>
       </c>
       <c r="R72" t="n">
-        <v>6532570</v>
+        <v>6532692</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9044,19 +9050,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9089,10 +9085,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129621165</v>
+        <v>129617827</v>
       </c>
       <c r="B73" t="n">
-        <v>110899</v>
+        <v>100958</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9100,21 +9096,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9125,17 +9121,21 @@
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>350534</v>
+        <v>350825</v>
       </c>
       <c r="R73" t="n">
-        <v>6532292</v>
+        <v>6532643</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9167,7 +9167,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9210,46 +9210,42 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129610894</v>
+        <v>129620970</v>
       </c>
       <c r="B74" t="n">
-        <v>57895</v>
+        <v>100958</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9257,17 +9253,17 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Långkasen, Tisselskog, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>350716</v>
+        <v>350563</v>
       </c>
       <c r="R74" t="n">
-        <v>6532562</v>
+        <v>6532299</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9296,7 +9292,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9306,12 +9302,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Minst 1 talltita hördes men ev. var det två individer. Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9320,17 +9311,13 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>Äldre granskog med olikåldriga träd med stor dimensionsspridning. Inslag av partier med tall och enstaka björk, lönn, rönn, sälg och ek.</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9348,10 +9335,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129620970</v>
+        <v>129624906</v>
       </c>
       <c r="B75" t="n">
-        <v>100957</v>
+        <v>110900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9359,21 +9346,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9391,14 +9378,14 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>350563</v>
+        <v>350786</v>
       </c>
       <c r="R75" t="n">
-        <v>6532299</v>
+        <v>6532704</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9430,7 +9417,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9440,7 +9427,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Sårläka förekommer allmänt i skogsbeståndet omkring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9473,42 +9465,46 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129624906</v>
+        <v>129610894</v>
       </c>
       <c r="B76" t="n">
-        <v>110899</v>
+        <v>57896</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219711</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9516,17 +9512,17 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Tisselskog, Dls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>350786</v>
+        <v>350716</v>
       </c>
       <c r="R76" t="n">
-        <v>6532704</v>
+        <v>6532562</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9555,7 +9551,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9565,12 +9561,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Sårläka förekommer allmänt i skogsbeståndet omkring fyndplatsen.</t>
+          <t>Minst 1 talltita hördes men ev. var det två individer. Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9579,13 +9575,17 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Äldre granskog med olikåldriga träd med stor dimensionsspridning. Inslag av partier med tall och enstaka björk, lönn, rönn, sälg och ek.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9606,7 +9606,7 @@
         <v>129623874</v>
       </c>
       <c r="B77" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>129622650</v>
       </c>
       <c r="B78" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>129620718</v>
       </c>
       <c r="B79" t="n">
-        <v>110899</v>
+        <v>110900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>129610907</v>
       </c>
       <c r="B80" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>129624198</v>
       </c>
       <c r="B81" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>129610904</v>
       </c>
       <c r="B82" t="n">
-        <v>110899</v>
+        <v>110900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>129620537</v>
       </c>
       <c r="B83" t="n">
-        <v>110899</v>
+        <v>110900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>129624823</v>
       </c>
       <c r="B84" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -8728,10 +8728,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129624665</v>
+        <v>129610909</v>
       </c>
       <c r="B70" t="n">
-        <v>110900</v>
+        <v>100958</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8739,21 +8739,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8764,21 +8764,17 @@
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>350682</v>
+        <v>350738</v>
       </c>
       <c r="R70" t="n">
-        <v>6532570</v>
+        <v>6532692</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8808,19 +8804,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8853,10 +8839,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129621165</v>
+        <v>129617827</v>
       </c>
       <c r="B71" t="n">
-        <v>110900</v>
+        <v>100958</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8864,21 +8850,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8889,17 +8875,21 @@
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>350534</v>
+        <v>350825</v>
       </c>
       <c r="R71" t="n">
-        <v>6532292</v>
+        <v>6532643</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8931,7 +8921,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8941,7 +8931,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8974,10 +8964,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129610909</v>
+        <v>129624665</v>
       </c>
       <c r="B72" t="n">
-        <v>100958</v>
+        <v>110900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8985,21 +8975,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9010,17 +9000,21 @@
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>350738</v>
+        <v>350682</v>
       </c>
       <c r="R72" t="n">
-        <v>6532692</v>
+        <v>6532570</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9050,9 +9044,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9085,10 +9089,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129617827</v>
+        <v>129621165</v>
       </c>
       <c r="B73" t="n">
-        <v>100958</v>
+        <v>110900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9096,21 +9100,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9121,21 +9125,17 @@
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>350825</v>
+        <v>350534</v>
       </c>
       <c r="R73" t="n">
-        <v>6532643</v>
+        <v>6532292</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9167,7 +9167,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9210,42 +9210,46 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129620970</v>
+        <v>129610894</v>
       </c>
       <c r="B74" t="n">
-        <v>100958</v>
+        <v>57896</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9253,17 +9257,17 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Långkasen, Tisselskog, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>350563</v>
+        <v>350716</v>
       </c>
       <c r="R74" t="n">
-        <v>6532299</v>
+        <v>6532562</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9292,7 +9296,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9302,7 +9306,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Minst 1 talltita hördes men ev. var det två individer. Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9311,13 +9320,17 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Äldre granskog med olikåldriga träd med stor dimensionsspridning. Inslag av partier med tall och enstaka björk, lönn, rönn, sälg och ek.</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9335,10 +9348,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129624906</v>
+        <v>129620970</v>
       </c>
       <c r="B75" t="n">
-        <v>110900</v>
+        <v>100958</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9346,21 +9359,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9378,14 +9391,14 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>350786</v>
+        <v>350563</v>
       </c>
       <c r="R75" t="n">
-        <v>6532704</v>
+        <v>6532299</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9417,7 +9430,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9427,12 +9440,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Sårläka förekommer allmänt i skogsbeståndet omkring fyndplatsen.</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9465,46 +9473,42 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129610894</v>
+        <v>129624906</v>
       </c>
       <c r="B76" t="n">
-        <v>57896</v>
+        <v>110900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>219711</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9512,17 +9516,17 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Långkasen, Tisselskog, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>350716</v>
+        <v>350786</v>
       </c>
       <c r="R76" t="n">
-        <v>6532562</v>
+        <v>6532704</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9551,7 +9555,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9561,12 +9565,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Minst 1 talltita hördes men ev. var det två individer. Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>Sårläka förekommer allmänt i skogsbeståndet omkring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9575,17 +9579,13 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>Äldre granskog med olikåldriga träd med stor dimensionsspridning. Inslag av partier med tall och enstaka björk, lönn, rönn, sälg och ek.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -5977,10 +5977,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129624004</v>
+        <v>129610899</v>
       </c>
       <c r="B48" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6013,21 +6013,17 @@
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>350639</v>
+        <v>350713</v>
       </c>
       <c r="R48" t="n">
-        <v>6532442</v>
+        <v>6532571</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6059,7 +6055,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6069,7 +6065,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6102,10 +6098,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129610899</v>
+        <v>129624004</v>
       </c>
       <c r="B49" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6138,17 +6134,21 @@
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>350713</v>
+        <v>350639</v>
       </c>
       <c r="R49" t="n">
-        <v>6532571</v>
+        <v>6532442</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6223,10 +6223,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129602112</v>
+        <v>129624719</v>
       </c>
       <c r="B50" t="n">
-        <v>110900</v>
+        <v>92548</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6234,53 +6234,41 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219711</v>
+        <v>4769</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>350772</v>
+        <v>350681</v>
       </c>
       <c r="R50" t="n">
-        <v>6532666</v>
+        <v>6532544</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6312,7 +6300,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6322,12 +6310,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt med blad av sårläka och gott om fröställningar på ca 2 m2 yta strax under kraftledningen.</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6336,12 +6319,13 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6359,10 +6343,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129624719</v>
+        <v>129602112</v>
       </c>
       <c r="B51" t="n">
-        <v>92543</v>
+        <v>110905</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6370,41 +6354,53 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4769</v>
+        <v>219711</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>350681</v>
+        <v>350772</v>
       </c>
       <c r="R51" t="n">
-        <v>6532544</v>
+        <v>6532666</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6436,7 +6432,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6446,7 +6442,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt med blad av sårläka och gott om fröställningar på ca 2 m2 yta strax under kraftledningen.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6455,13 +6456,12 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6479,10 +6479,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129621322</v>
+        <v>129624476</v>
       </c>
       <c r="B52" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6515,17 +6515,21 @@
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>350500</v>
+        <v>350698</v>
       </c>
       <c r="R52" t="n">
-        <v>6532306</v>
+        <v>6532504</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6557,7 +6561,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6567,7 +6571,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6582,7 +6586,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6600,10 +6604,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129624476</v>
+        <v>129610901</v>
       </c>
       <c r="B53" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6636,21 +6640,17 @@
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>350698</v>
+        <v>350704</v>
       </c>
       <c r="R53" t="n">
-        <v>6532504</v>
+        <v>6532603</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6725,10 +6725,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129626202</v>
+        <v>129621322</v>
       </c>
       <c r="B54" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6761,21 +6761,17 @@
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>350886</v>
+        <v>350500</v>
       </c>
       <c r="R54" t="n">
-        <v>6532805</v>
+        <v>6532306</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6807,7 +6803,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6817,7 +6813,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6850,10 +6846,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129610901</v>
+        <v>129626202</v>
       </c>
       <c r="B55" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6886,17 +6882,21 @@
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>350704</v>
+        <v>350886</v>
       </c>
       <c r="R55" t="n">
-        <v>6532603</v>
+        <v>6532805</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6971,10 +6971,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129620583</v>
+        <v>129618156</v>
       </c>
       <c r="B56" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7014,10 +7014,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>350764</v>
+        <v>350773</v>
       </c>
       <c r="R56" t="n">
-        <v>6532613</v>
+        <v>6532648</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7092,10 +7092,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129618156</v>
+        <v>129620583</v>
       </c>
       <c r="B57" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>350773</v>
+        <v>350764</v>
       </c>
       <c r="R57" t="n">
-        <v>6532648</v>
+        <v>6532613</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7216,7 +7216,7 @@
         <v>129617882</v>
       </c>
       <c r="B58" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>129620964</v>
       </c>
       <c r="B59" t="n">
-        <v>110900</v>
+        <v>110905</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>129621973</v>
       </c>
       <c r="B60" t="n">
-        <v>110900</v>
+        <v>110905</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>129625617</v>
       </c>
       <c r="B61" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>129622093</v>
       </c>
       <c r="B62" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>129624940</v>
       </c>
       <c r="B63" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>129623862</v>
       </c>
       <c r="B64" t="n">
-        <v>110900</v>
+        <v>110905</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>129621217</v>
       </c>
       <c r="B65" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>129610906</v>
       </c>
       <c r="B66" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8340,10 +8340,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129610910</v>
+        <v>129620774</v>
       </c>
       <c r="B67" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8387,10 +8387,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>350756</v>
+        <v>350751</v>
       </c>
       <c r="R67" t="n">
-        <v>6532668</v>
+        <v>6532634</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8465,10 +8465,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129622188</v>
+        <v>129610910</v>
       </c>
       <c r="B68" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8493,16 +8493,8 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -8516,14 +8508,14 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>350455</v>
+        <v>350756</v>
       </c>
       <c r="R68" t="n">
-        <v>6532318</v>
+        <v>6532668</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8555,7 +8547,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8565,12 +8557,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På fyndplatsen finns rikligt med blåsippa.</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8585,7 +8572,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8603,10 +8590,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129620774</v>
+        <v>129622188</v>
       </c>
       <c r="B69" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8631,8 +8618,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -8646,14 +8641,14 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>350751</v>
+        <v>350455</v>
       </c>
       <c r="R69" t="n">
-        <v>6532634</v>
+        <v>6532318</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8685,7 +8680,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8695,7 +8690,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På fyndplatsen finns rikligt med blåsippa.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8728,10 +8728,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129610909</v>
+        <v>129624665</v>
       </c>
       <c r="B70" t="n">
-        <v>100958</v>
+        <v>110905</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8739,21 +8739,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8764,17 +8764,21 @@
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>350738</v>
+        <v>350682</v>
       </c>
       <c r="R70" t="n">
-        <v>6532692</v>
+        <v>6532570</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8804,9 +8808,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8839,10 +8853,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129617827</v>
+        <v>129621165</v>
       </c>
       <c r="B71" t="n">
-        <v>100958</v>
+        <v>110905</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8850,21 +8864,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8875,21 +8889,17 @@
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>350825</v>
+        <v>350534</v>
       </c>
       <c r="R71" t="n">
-        <v>6532643</v>
+        <v>6532292</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8921,7 +8931,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8931,7 +8941,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8964,10 +8974,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129624665</v>
+        <v>129610909</v>
       </c>
       <c r="B72" t="n">
-        <v>110900</v>
+        <v>100963</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8975,21 +8985,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9000,21 +9010,17 @@
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>350682</v>
+        <v>350738</v>
       </c>
       <c r="R72" t="n">
-        <v>6532570</v>
+        <v>6532692</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9044,19 +9050,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9089,10 +9085,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129621165</v>
+        <v>129617827</v>
       </c>
       <c r="B73" t="n">
-        <v>110900</v>
+        <v>100963</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9100,21 +9096,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9125,17 +9121,21 @@
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>350534</v>
+        <v>350825</v>
       </c>
       <c r="R73" t="n">
-        <v>6532292</v>
+        <v>6532643</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9167,7 +9167,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9210,46 +9210,42 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129610894</v>
+        <v>129624906</v>
       </c>
       <c r="B74" t="n">
-        <v>57896</v>
+        <v>110905</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103021</v>
+        <v>219711</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9257,17 +9253,17 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Långkasen, Tisselskog, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>350716</v>
+        <v>350786</v>
       </c>
       <c r="R74" t="n">
-        <v>6532562</v>
+        <v>6532704</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9296,7 +9292,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9306,12 +9302,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 1 talltita hördes men ev. var det två individer. Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>Sårläka förekommer allmänt i skogsbeståndet omkring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9320,17 +9316,13 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>Äldre granskog med olikåldriga träd med stor dimensionsspridning. Inslag av partier med tall och enstaka björk, lönn, rönn, sälg och ek.</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9351,7 +9343,7 @@
         <v>129620970</v>
       </c>
       <c r="B75" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9473,42 +9465,46 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129624906</v>
+        <v>129610894</v>
       </c>
       <c r="B76" t="n">
-        <v>110900</v>
+        <v>57896</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219711</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9516,17 +9512,17 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Tisselskog, Dls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>350786</v>
+        <v>350716</v>
       </c>
       <c r="R76" t="n">
-        <v>6532704</v>
+        <v>6532562</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9555,7 +9551,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9565,12 +9561,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Sårläka förekommer allmänt i skogsbeståndet omkring fyndplatsen.</t>
+          <t>Minst 1 talltita hördes men ev. var det två individer. Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9579,13 +9575,17 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Äldre granskog med olikåldriga träd med stor dimensionsspridning. Inslag av partier med tall och enstaka björk, lönn, rönn, sälg och ek.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129623874</v>
+        <v>129620718</v>
       </c>
       <c r="B77" t="n">
-        <v>100958</v>
+        <v>110905</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9614,21 +9614,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9646,14 +9646,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>350602</v>
+        <v>350751</v>
       </c>
       <c r="R77" t="n">
-        <v>6532393</v>
+        <v>6532634</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9728,10 +9728,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129622650</v>
+        <v>129623874</v>
       </c>
       <c r="B78" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9775,10 +9775,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>350557</v>
+        <v>350602</v>
       </c>
       <c r="R78" t="n">
-        <v>6532357</v>
+        <v>6532393</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9853,10 +9853,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129620718</v>
+        <v>129622650</v>
       </c>
       <c r="B79" t="n">
-        <v>110900</v>
+        <v>100963</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9864,21 +9864,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9896,14 +9896,14 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>350751</v>
+        <v>350557</v>
       </c>
       <c r="R79" t="n">
-        <v>6532634</v>
+        <v>6532357</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9978,10 +9978,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129610907</v>
+        <v>129624198</v>
       </c>
       <c r="B80" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10021,14 +10021,14 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>350725</v>
+        <v>350658</v>
       </c>
       <c r="R80" t="n">
-        <v>6532715</v>
+        <v>6532492</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10058,9 +10058,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10093,10 +10103,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129624198</v>
+        <v>129610904</v>
       </c>
       <c r="B81" t="n">
-        <v>100958</v>
+        <v>110905</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10104,21 +10114,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10136,14 +10146,14 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>350658</v>
+        <v>350697</v>
       </c>
       <c r="R81" t="n">
-        <v>6532492</v>
+        <v>6532630</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10175,7 +10185,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10185,7 +10195,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Gott om blad av sårläka på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10218,10 +10233,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129610904</v>
+        <v>129620537</v>
       </c>
       <c r="B82" t="n">
-        <v>110900</v>
+        <v>110905</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10254,21 +10269,17 @@
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>350697</v>
+        <v>350764</v>
       </c>
       <c r="R82" t="n">
-        <v>6532630</v>
+        <v>6532613</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10300,7 +10311,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10310,12 +10321,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Gott om blad av sårläka på fyndplatsen.</t>
+          <t>Sårläka finns relativt allmänt i skogsbeståndet omkring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10348,10 +10359,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129620537</v>
+        <v>129610907</v>
       </c>
       <c r="B83" t="n">
-        <v>110900</v>
+        <v>100963</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10359,21 +10370,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10384,17 +10395,21 @@
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>350764</v>
+        <v>350725</v>
       </c>
       <c r="R83" t="n">
-        <v>6532613</v>
+        <v>6532715</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10424,24 +10439,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Sårläka finns relativt allmänt i skogsbeståndet omkring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10477,7 +10477,7 @@
         <v>129624823</v>
       </c>
       <c r="B84" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -5977,7 +5977,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129610899</v>
+        <v>129624004</v>
       </c>
       <c r="B48" t="n">
         <v>100963</v>
@@ -6013,17 +6013,21 @@
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>350713</v>
+        <v>350639</v>
       </c>
       <c r="R48" t="n">
-        <v>6532571</v>
+        <v>6532442</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6055,7 +6059,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6065,7 +6069,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6098,7 +6102,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129624004</v>
+        <v>129610899</v>
       </c>
       <c r="B49" t="n">
         <v>100963</v>
@@ -6134,21 +6138,17 @@
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>350639</v>
+        <v>350713</v>
       </c>
       <c r="R49" t="n">
-        <v>6532442</v>
+        <v>6532571</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6223,10 +6223,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129624719</v>
+        <v>129602112</v>
       </c>
       <c r="B50" t="n">
-        <v>92548</v>
+        <v>110905</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6234,41 +6234,53 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4769</v>
+        <v>219711</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>350681</v>
+        <v>350772</v>
       </c>
       <c r="R50" t="n">
-        <v>6532544</v>
+        <v>6532666</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6300,7 +6312,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6310,7 +6322,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt med blad av sårläka och gott om fröställningar på ca 2 m2 yta strax under kraftledningen.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6319,13 +6336,12 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6343,10 +6359,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129602112</v>
+        <v>129624719</v>
       </c>
       <c r="B51" t="n">
-        <v>110905</v>
+        <v>92548</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6354,53 +6370,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219711</v>
+        <v>4769</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>350772</v>
+        <v>350681</v>
       </c>
       <c r="R51" t="n">
-        <v>6532666</v>
+        <v>6532544</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6432,7 +6436,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6442,12 +6446,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt med blad av sårläka och gott om fröställningar på ca 2 m2 yta strax under kraftledningen.</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6456,12 +6455,13 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6479,7 +6479,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129624476</v>
+        <v>129621322</v>
       </c>
       <c r="B52" t="n">
         <v>100963</v>
@@ -6515,21 +6515,17 @@
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>350698</v>
+        <v>350500</v>
       </c>
       <c r="R52" t="n">
-        <v>6532504</v>
+        <v>6532306</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6561,7 +6557,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6571,7 +6567,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6586,7 +6582,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6604,7 +6600,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129610901</v>
+        <v>129624476</v>
       </c>
       <c r="B53" t="n">
         <v>100963</v>
@@ -6640,17 +6636,21 @@
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>350704</v>
+        <v>350698</v>
       </c>
       <c r="R53" t="n">
-        <v>6532603</v>
+        <v>6532504</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6725,7 +6725,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129621322</v>
+        <v>129626202</v>
       </c>
       <c r="B54" t="n">
         <v>100963</v>
@@ -6761,17 +6761,21 @@
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>350500</v>
+        <v>350886</v>
       </c>
       <c r="R54" t="n">
-        <v>6532306</v>
+        <v>6532805</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6803,7 +6807,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6813,7 +6817,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6846,7 +6850,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129626202</v>
+        <v>129610901</v>
       </c>
       <c r="B55" t="n">
         <v>100963</v>
@@ -6882,21 +6886,17 @@
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>350886</v>
+        <v>350704</v>
       </c>
       <c r="R55" t="n">
-        <v>6532805</v>
+        <v>6532603</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6971,7 +6971,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129618156</v>
+        <v>129620583</v>
       </c>
       <c r="B56" t="n">
         <v>100963</v>
@@ -7014,10 +7014,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>350773</v>
+        <v>350764</v>
       </c>
       <c r="R56" t="n">
-        <v>6532648</v>
+        <v>6532613</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7092,7 +7092,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129620583</v>
+        <v>129618156</v>
       </c>
       <c r="B57" t="n">
         <v>100963</v>
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>350764</v>
+        <v>350773</v>
       </c>
       <c r="R57" t="n">
-        <v>6532613</v>
+        <v>6532648</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7213,10 +7213,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129617882</v>
+        <v>129620964</v>
       </c>
       <c r="B58" t="n">
-        <v>100963</v>
+        <v>110905</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7224,21 +7224,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7256,14 +7256,14 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>350809</v>
+        <v>350563</v>
       </c>
       <c r="R58" t="n">
-        <v>6532638</v>
+        <v>6532299</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7293,9 +7293,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Sårläka förekommer relativt allmänt i skogsbeståndet där fyndplatsen ligger och arten har troligen funnits i området mycket länge.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7310,7 +7325,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7328,7 +7343,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129620964</v>
+        <v>129621973</v>
       </c>
       <c r="B59" t="n">
         <v>110905</v>
@@ -7375,10 +7390,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>350563</v>
+        <v>350525</v>
       </c>
       <c r="R59" t="n">
-        <v>6532299</v>
+        <v>6532325</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7410,7 +7425,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7420,12 +7435,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Sårläka förekommer relativt allmänt i skogsbeståndet där fyndplatsen ligger och arten har troligen funnits i området mycket länge.</t>
+          <t>Rikligt med vintergröna blad av sårläka på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7441,6 +7456,11 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med stor dimensionsspridning bland stammarna.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7458,10 +7478,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129621973</v>
+        <v>129617882</v>
       </c>
       <c r="B60" t="n">
-        <v>110905</v>
+        <v>100963</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7469,21 +7489,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7501,14 +7521,14 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>350525</v>
+        <v>350809</v>
       </c>
       <c r="R60" t="n">
-        <v>6532325</v>
+        <v>6532638</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7538,24 +7558,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt med vintergröna blad av sårläka på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7570,12 +7575,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med stor dimensionsspridning bland stammarna.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8340,7 +8340,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129620774</v>
+        <v>129610910</v>
       </c>
       <c r="B67" t="n">
         <v>100963</v>
@@ -8387,10 +8387,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>350751</v>
+        <v>350756</v>
       </c>
       <c r="R67" t="n">
-        <v>6532634</v>
+        <v>6532668</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8465,7 +8465,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129610910</v>
+        <v>129622188</v>
       </c>
       <c r="B68" t="n">
         <v>100963</v>
@@ -8493,8 +8493,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -8508,14 +8516,14 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>350756</v>
+        <v>350455</v>
       </c>
       <c r="R68" t="n">
-        <v>6532668</v>
+        <v>6532318</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8547,7 +8555,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8557,7 +8565,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På fyndplatsen finns rikligt med blåsippa.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8572,7 +8585,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8590,7 +8603,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129622188</v>
+        <v>129620774</v>
       </c>
       <c r="B69" t="n">
         <v>100963</v>
@@ -8618,16 +8631,8 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -8641,14 +8646,14 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>350455</v>
+        <v>350751</v>
       </c>
       <c r="R69" t="n">
-        <v>6532318</v>
+        <v>6532634</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8680,7 +8685,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8690,12 +8695,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På fyndplatsen finns rikligt med blåsippa.</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8728,7 +8728,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129624665</v>
+        <v>129621165</v>
       </c>
       <c r="B70" t="n">
         <v>110905</v>
@@ -8764,21 +8764,17 @@
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>350682</v>
+        <v>350534</v>
       </c>
       <c r="R70" t="n">
-        <v>6532570</v>
+        <v>6532292</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8810,7 +8806,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8820,7 +8816,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8835,7 +8831,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8853,7 +8849,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129621165</v>
+        <v>129624665</v>
       </c>
       <c r="B71" t="n">
         <v>110905</v>
@@ -8889,17 +8885,21 @@
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>350534</v>
+        <v>350682</v>
       </c>
       <c r="R71" t="n">
-        <v>6532292</v>
+        <v>6532570</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9210,42 +9210,46 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129624906</v>
+        <v>129610894</v>
       </c>
       <c r="B74" t="n">
-        <v>110905</v>
+        <v>57896</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219711</v>
+        <v>103021</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9253,17 +9257,17 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Tisselskog, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>350786</v>
+        <v>350716</v>
       </c>
       <c r="R74" t="n">
-        <v>6532704</v>
+        <v>6532562</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9292,7 +9296,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9302,12 +9306,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Sårläka förekommer allmänt i skogsbeståndet omkring fyndplatsen.</t>
+          <t>Minst 1 talltita hördes men ev. var det två individer. Fyndplatsen finns i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9316,13 +9320,17 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Äldre granskog med olikåldriga träd med stor dimensionsspridning. Inslag av partier med tall och enstaka björk, lönn, rönn, sälg och ek.</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9465,46 +9473,42 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129610894</v>
+        <v>129624906</v>
       </c>
       <c r="B76" t="n">
-        <v>57896</v>
+        <v>110905</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>219711</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9512,17 +9516,17 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Långkasen, Tisselskog, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>350716</v>
+        <v>350786</v>
       </c>
       <c r="R76" t="n">
-        <v>6532562</v>
+        <v>6532704</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9551,7 +9555,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9561,12 +9565,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Minst 1 talltita hördes men ev. var det två individer. Fyndplatsen finns i äldre flerskiktad granskog.</t>
+          <t>Sårläka förekommer allmänt i skogsbeståndet omkring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9575,17 +9579,13 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>Äldre granskog med olikåldriga träd med stor dimensionsspridning. Inslag av partier med tall och enstaka björk, lönn, rönn, sälg och ek.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129620718</v>
+        <v>129623874</v>
       </c>
       <c r="B77" t="n">
-        <v>110905</v>
+        <v>100963</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9614,21 +9614,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9646,14 +9646,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>350751</v>
+        <v>350602</v>
       </c>
       <c r="R77" t="n">
-        <v>6532634</v>
+        <v>6532393</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9728,7 +9728,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129623874</v>
+        <v>129622650</v>
       </c>
       <c r="B78" t="n">
         <v>100963</v>
@@ -9775,10 +9775,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>350602</v>
+        <v>350557</v>
       </c>
       <c r="R78" t="n">
-        <v>6532393</v>
+        <v>6532357</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9853,10 +9853,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129622650</v>
+        <v>129620718</v>
       </c>
       <c r="B79" t="n">
-        <v>100963</v>
+        <v>110905</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9864,21 +9864,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9896,14 +9896,14 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>350557</v>
+        <v>350751</v>
       </c>
       <c r="R79" t="n">
-        <v>6532357</v>
+        <v>6532634</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9978,7 +9978,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129624198</v>
+        <v>129610907</v>
       </c>
       <c r="B80" t="n">
         <v>100963</v>
@@ -10021,14 +10021,14 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>350658</v>
+        <v>350725</v>
       </c>
       <c r="R80" t="n">
-        <v>6532492</v>
+        <v>6532715</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10058,19 +10058,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>15:17</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10103,10 +10093,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129610904</v>
+        <v>129624198</v>
       </c>
       <c r="B81" t="n">
-        <v>110905</v>
+        <v>100963</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10114,21 +10104,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10146,14 +10136,14 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>350697</v>
+        <v>350658</v>
       </c>
       <c r="R81" t="n">
-        <v>6532630</v>
+        <v>6532492</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10185,7 +10175,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10195,12 +10185,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Gott om blad av sårläka på fyndplatsen.</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10233,7 +10218,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129620537</v>
+        <v>129610904</v>
       </c>
       <c r="B82" t="n">
         <v>110905</v>
@@ -10269,17 +10254,21 @@
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>350764</v>
+        <v>350697</v>
       </c>
       <c r="R82" t="n">
-        <v>6532613</v>
+        <v>6532630</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10311,7 +10300,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10321,12 +10310,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Sårläka finns relativt allmänt i skogsbeståndet omkring fyndplatsen.</t>
+          <t>Gott om blad av sårläka på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10359,10 +10348,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129610907</v>
+        <v>129620537</v>
       </c>
       <c r="B83" t="n">
-        <v>100963</v>
+        <v>110905</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10370,21 +10359,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10395,21 +10384,17 @@
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>350725</v>
+        <v>350764</v>
       </c>
       <c r="R83" t="n">
-        <v>6532715</v>
+        <v>6532613</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10439,9 +10424,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Sårläka finns relativt allmänt i skogsbeståndet omkring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 39700-2025 artfynd.xlsx
+++ b/artfynd/A 39700-2025 artfynd.xlsx
@@ -6223,10 +6223,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129602112</v>
+        <v>129624719</v>
       </c>
       <c r="B50" t="n">
-        <v>110905</v>
+        <v>92548</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6234,53 +6234,41 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219711</v>
+        <v>4769</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källan, Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>350772</v>
+        <v>350681</v>
       </c>
       <c r="R50" t="n">
-        <v>6532666</v>
+        <v>6532544</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6312,7 +6300,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6322,12 +6310,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt med blad av sårläka och gott om fröställningar på ca 2 m2 yta strax under kraftledningen.</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6336,12 +6319,13 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6359,10 +6343,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129624719</v>
+        <v>129602112</v>
       </c>
       <c r="B51" t="n">
-        <v>92548</v>
+        <v>110905</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6370,41 +6354,53 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4769</v>
+        <v>219711</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Källan, Dls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>350681</v>
+        <v>350772</v>
       </c>
       <c r="R51" t="n">
-        <v>6532544</v>
+        <v>6532666</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6436,7 +6432,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6446,7 +6442,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt med blad av sårläka och gott om fröställningar på ca 2 m2 yta strax under kraftledningen.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6455,13 +6456,12 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -8728,7 +8728,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129621165</v>
+        <v>129624665</v>
       </c>
       <c r="B70" t="n">
         <v>110905</v>
@@ -8764,17 +8764,21 @@
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>350534</v>
+        <v>350682</v>
       </c>
       <c r="R70" t="n">
-        <v>6532292</v>
+        <v>6532570</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8806,7 +8810,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8816,7 +8820,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8831,7 +8835,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8849,7 +8853,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129624665</v>
+        <v>129621165</v>
       </c>
       <c r="B71" t="n">
         <v>110905</v>
@@ -8885,21 +8889,17 @@
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>350682</v>
+        <v>350534</v>
       </c>
       <c r="R71" t="n">
-        <v>6532570</v>
+        <v>6532292</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9348,10 +9348,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129620970</v>
+        <v>129624906</v>
       </c>
       <c r="B75" t="n">
-        <v>100963</v>
+        <v>110905</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9359,21 +9359,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9391,14 +9391,14 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>350563</v>
+        <v>350786</v>
       </c>
       <c r="R75" t="n">
-        <v>6532299</v>
+        <v>6532704</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9440,7 +9440,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Sårläka förekommer allmänt i skogsbeståndet omkring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9473,10 +9478,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129624906</v>
+        <v>129620970</v>
       </c>
       <c r="B76" t="n">
-        <v>110905</v>
+        <v>100963</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9484,21 +9489,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9516,14 +9521,14 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>350786</v>
+        <v>350563</v>
       </c>
       <c r="R76" t="n">
-        <v>6532704</v>
+        <v>6532299</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9555,7 +9560,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9565,12 +9570,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Sårläka förekommer allmänt i skogsbeståndet omkring fyndplatsen.</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9603,10 +9603,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129623874</v>
+        <v>129620718</v>
       </c>
       <c r="B77" t="n">
-        <v>100963</v>
+        <v>110905</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9614,21 +9614,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9646,14 +9646,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>350602</v>
+        <v>350751</v>
       </c>
       <c r="R77" t="n">
-        <v>6532393</v>
+        <v>6532634</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9728,7 +9728,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129622650</v>
+        <v>129623874</v>
       </c>
       <c r="B78" t="n">
         <v>100963</v>
@@ -9775,10 +9775,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>350557</v>
+        <v>350602</v>
       </c>
       <c r="R78" t="n">
-        <v>6532357</v>
+        <v>6532393</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9853,10 +9853,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129620718</v>
+        <v>129622650</v>
       </c>
       <c r="B79" t="n">
-        <v>110905</v>
+        <v>100963</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9864,21 +9864,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9896,14 +9896,14 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>350751</v>
+        <v>350557</v>
       </c>
       <c r="R79" t="n">
-        <v>6532634</v>
+        <v>6532357</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9978,10 +9978,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129610907</v>
+        <v>129610904</v>
       </c>
       <c r="B80" t="n">
-        <v>100963</v>
+        <v>110905</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9989,21 +9989,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10025,10 +10025,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>350725</v>
+        <v>350697</v>
       </c>
       <c r="R80" t="n">
-        <v>6532715</v>
+        <v>6532630</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10058,9 +10058,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Gott om blad av sårläka på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10093,10 +10108,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129624198</v>
+        <v>129620537</v>
       </c>
       <c r="B81" t="n">
-        <v>100963</v>
+        <v>110905</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10104,21 +10119,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10129,21 +10144,17 @@
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Långkasen, Dls</t>
+          <t>Källan, Dls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>350658</v>
+        <v>350764</v>
       </c>
       <c r="R81" t="n">
-        <v>6532492</v>
+        <v>6532613</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10175,7 +10186,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10185,7 +10196,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Sårläka finns relativt allmänt i skogsbeståndet omkring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10218,10 +10234,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129610904</v>
+        <v>129610907</v>
       </c>
       <c r="B82" t="n">
-        <v>110905</v>
+        <v>100963</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10229,21 +10245,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10265,10 +10281,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>350697</v>
+        <v>350725</v>
       </c>
       <c r="R82" t="n">
-        <v>6532630</v>
+        <v>6532715</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10298,24 +10314,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Gott om blad av sårläka på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10348,10 +10349,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129620537</v>
+        <v>129624198</v>
       </c>
       <c r="B83" t="n">
-        <v>110905</v>
+        <v>100963</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10359,21 +10360,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10384,17 +10385,21 @@
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Källan, Dls</t>
+          <t>Långkasen, Dls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>350764</v>
+        <v>350658</v>
       </c>
       <c r="R83" t="n">
-        <v>6532613</v>
+        <v>6532492</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10426,7 +10431,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10436,12 +10441,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Sårläka finns relativt allmänt i skogsbeståndet omkring fyndplatsen.</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD83" t="b">
